--- a/Aktie_Utdelning.xlsx
+++ b/Aktie_Utdelning.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\inte porr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E32714F-A0DB-4828-ADA0-FEC4C16ED5B4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E81506-2922-4C83-9ECE-83F955DD0944}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -238,7 +238,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
   <si>
     <t>Feb</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>ASTRAZENECA PLC (XSTO:AZN)</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -1012,6 +1015,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1031,6 +1039,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1050,6 +1063,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1069,6 +1087,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1088,6 +1111,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1107,6 +1135,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1128,6 +1161,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1149,6 +1187,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1170,6 +1213,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1191,6 +1239,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1212,6 +1265,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -1233,6 +1291,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -1255,6 +1318,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -1277,6 +1345,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -1299,6 +1372,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -1321,6 +1399,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -1343,6 +1426,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
@@ -1365,6 +1453,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-61D9-4F1A-81C9-44595E30DBB3}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -1779,6 +1872,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1798,6 +1896,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1817,6 +1920,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1836,6 +1944,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -1855,6 +1968,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -1874,6 +1992,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -1895,6 +2018,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -1916,6 +2044,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -1937,6 +2070,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -1958,6 +2096,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
@@ -1979,6 +2122,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
@@ -2000,6 +2148,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
@@ -2022,6 +2175,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
@@ -2044,6 +2202,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
@@ -2066,6 +2229,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
@@ -2088,6 +2256,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
@@ -2110,6 +2283,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
@@ -2132,6 +2310,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-6E1F-4A13-AA9F-C5566D94650A}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -6885,7 +7068,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Blad1"/>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
@@ -6903,7 +7086,7 @@
     <col min="16" max="16" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
@@ -6953,7 +7136,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -6977,7 +7160,7 @@
         <v>28</v>
       </c>
       <c r="O2" s="2">
-        <f>SUM(B2:M2)*N2</f>
+        <f t="shared" ref="O2:O9" si="0">SUM(B2:M2)*N2</f>
         <v>42</v>
       </c>
       <c r="P2" s="14" cm="1">
@@ -6985,7 +7168,7 @@
         <v>86.46</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -7009,7 +7192,7 @@
         <v>17</v>
       </c>
       <c r="O3" s="1">
-        <f>SUM(B3:M3)*N3</f>
+        <f t="shared" si="0"/>
         <v>164.89999999999998</v>
       </c>
       <c r="P3" s="14" cm="1">
@@ -7017,7 +7200,7 @@
         <v>137.65</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -7041,7 +7224,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="2">
-        <f>SUM(B4:M4)*N4</f>
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="P4" s="14" cm="1">
@@ -7049,7 +7232,7 @@
         <v>506.2</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
@@ -7071,7 +7254,7 @@
         <v>34</v>
       </c>
       <c r="O5" s="1">
-        <f>SUM(B5:M5)*N5</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="P5" s="14" cm="1">
@@ -7079,7 +7262,7 @@
         <v>26.46</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
@@ -7103,7 +7286,7 @@
         <v>9</v>
       </c>
       <c r="O6" s="2">
-        <f>SUM(B6:M6)*N6</f>
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
       <c r="P6" s="14" cm="1">
@@ -7111,7 +7294,7 @@
         <v>263.3</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
@@ -7139,7 +7322,7 @@
         <v>11</v>
       </c>
       <c r="O7" s="1">
-        <f>SUM(B7:M7)*N7</f>
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
       <c r="P7" s="14" cm="1">
@@ -7147,7 +7330,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
@@ -7175,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="2">
-        <f>SUM(B8:M8)*N8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P8" s="13" cm="1">
@@ -7183,7 +7366,7 @@
         <v>305.7</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
@@ -7211,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="O9" s="1">
-        <f>SUM(B9:M9)*N9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P9" s="13" cm="1">
@@ -7219,7 +7402,7 @@
         <v>301.3</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
@@ -7241,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" ref="O10:O18" si="0">SUM(B10:M10)*N10</f>
+        <f t="shared" ref="O10:O18" si="1">SUM(B10:M10)*N10</f>
         <v>0</v>
       </c>
       <c r="P10" s="14" cm="1">
@@ -7249,7 +7432,7 @@
         <v>172.3</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -7277,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P11" s="14" cm="1">
@@ -7285,7 +7468,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
@@ -7309,7 +7492,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P12" s="14" cm="1">
@@ -7317,7 +7500,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
@@ -7341,7 +7524,7 @@
         <v>0</v>
       </c>
       <c r="O13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P13" s="14" cm="1">
@@ -7349,7 +7532,7 @@
         <v>184.4</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
@@ -7373,15 +7556,18 @@
         <v>0</v>
       </c>
       <c r="O14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P14" s="14" cm="1">
         <f t="array" ref="P14">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>359</v>
       </c>
+      <c r="W14" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
@@ -7405,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P15" s="14" cm="1">
@@ -7413,7 +7599,7 @@
         <v>176.2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
@@ -7437,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="O16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P16" s="14" cm="1">
@@ -7467,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P17" s="14" cm="1">
@@ -7499,7 +7685,7 @@
         <v>0</v>
       </c>
       <c r="O18" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P18" s="14" cm="1">

--- a/Aktie_Utdelning.xlsx
+++ b/Aktie_Utdelning.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E81506-2922-4C83-9ECE-83F955DD0944}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D38F473-C509-43D9-B2B0-9A2499B9747D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Python" sheetId="2" r:id="rId2"/>
+    <sheet name="Blad1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -238,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>Feb</t>
   </si>
@@ -340,9 +341,6 @@
   </si>
   <si>
     <t>ASTRAZENECA PLC (XSTO:AZN)</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
 </sst>
 </file>
@@ -7068,7 +7066,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Blad1"/>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
@@ -7086,7 +7084,7 @@
     <col min="16" max="16" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
@@ -7136,7 +7134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -7168,7 +7166,7 @@
         <v>86.46</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -7200,7 +7198,7 @@
         <v>137.65</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -7232,7 +7230,7 @@
         <v>506.2</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
@@ -7262,7 +7260,7 @@
         <v>26.46</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
@@ -7294,7 +7292,7 @@
         <v>263.3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
@@ -7330,7 +7328,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
@@ -7366,7 +7364,7 @@
         <v>305.7</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
@@ -7402,7 +7400,7 @@
         <v>301.3</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
@@ -7432,7 +7430,7 @@
         <v>172.3</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -7468,7 +7466,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
@@ -7500,7 +7498,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
@@ -7532,7 +7530,7 @@
         <v>184.4</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
@@ -7563,11 +7561,8 @@
         <f t="array" ref="P14">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>359</v>
       </c>
-      <c r="W14" t="s">
-        <v>34</v>
-      </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
@@ -7599,7 +7594,7 @@
         <v>176.2</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
@@ -8987,4 +8982,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1485E3A-19D0-47B9-867F-49E3EDE141F8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Aktie_Utdelning.xlsx
+++ b/Aktie_Utdelning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D38F473-C509-43D9-B2B0-9A2499B9747D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECA3A90-19F2-4F41-8AE5-9299D587C145}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Python" sheetId="2" r:id="rId2"/>
     <sheet name="Blad1" sheetId="3" r:id="rId3"/>
+    <sheet name="Blad2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -239,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="36">
   <si>
     <t>Feb</t>
   </si>
@@ -341,6 +342,12 @@
   </si>
   <si>
     <t>ASTRAZENECA PLC (XSTO:AZN)</t>
+  </si>
+  <si>
+    <t>årlig utd.</t>
+  </si>
+  <si>
+    <t>2020-07-29 bank=4000 magic=1, ordning 1</t>
   </si>
 </sst>
 </file>
@@ -1597,40 +1604,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>42</c:v>
+                  <c:v>1.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>164.89999999999998</c:v>
+                  <c:v>9.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>36</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>68</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>72</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>77</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>2.2000000000000002</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -1642,13 +1649,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>26.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2454,40 +2461,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>28</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>17</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>11</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -2499,13 +2506,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4018,6 +4025,9 @@
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
       <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
         <flag name="ExcludeFromCalcComparison" value="1"/>
       </key>
     </keyFlags>
@@ -7155,11 +7165,11 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="O2" s="2">
         <f t="shared" ref="O2:O9" si="0">SUM(B2:M2)*N2</f>
-        <v>42</v>
+        <v>1.5</v>
       </c>
       <c r="P2" s="14" cm="1">
         <f t="array" ref="P2">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7187,11 +7197,11 @@
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="O3" s="1">
         <f t="shared" si="0"/>
-        <v>164.89999999999998</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="P3" s="14" cm="1">
         <f t="array" ref="P3">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7219,11 +7229,11 @@
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O4" s="2">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="P4" s="14" cm="1">
         <f t="array" ref="P4">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7249,11 +7259,11 @@
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="O5" s="1">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="P5" s="14" cm="1">
         <f t="array" ref="P5">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7281,11 +7291,11 @@
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O6" s="2">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="P6" s="14" cm="1">
         <f t="array" ref="P6">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7317,11 +7327,11 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O7" s="1">
         <f t="shared" si="0"/>
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="P7" s="14" cm="1">
         <f t="array" ref="P7">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7353,11 +7363,11 @@
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P8" s="13" cm="1">
         <f t="array" ref="P8">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)*10</f>
@@ -7389,11 +7399,11 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="P9" s="13" cm="1">
         <f t="array" ref="P9">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)*10</f>
@@ -7419,11 +7429,11 @@
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="2">
         <f t="shared" ref="O10:O18" si="1">SUM(B10:M10)*N10</f>
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P10" s="14" cm="1">
         <f t="array" ref="P10">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7455,11 +7465,11 @@
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="P11" s="14" cm="1">
         <f t="array" ref="P11">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7487,11 +7497,11 @@
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P12" s="14" cm="1">
         <f t="array" ref="P12">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7519,11 +7529,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="P13" s="14" cm="1">
         <f t="array" ref="P13">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7645,11 +7655,11 @@
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P17" s="14" cm="1">
         <f t="array" ref="P17">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7677,11 +7687,11 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>26.5</v>
       </c>
       <c r="P18" s="14" cm="1">
         <f t="array" ref="P18">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7713,11 +7723,11 @@
         <v>0.46</v>
       </c>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" s="1">
         <f>SUM(B19:M19)*N19</f>
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="P19" s="12" cm="1">
         <f t="array" ref="P19">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7748,59 +7758,59 @@
       </c>
       <c r="B21" s="20">
         <f>B2*N2+B3*N3+B4*N4+B5*N5+B6*N6+B7*N7+B8*N8+B9*N9+B10*N10+B11*N11+B12*N12+B13*N13+B14*N14+B15*N15+B16*N16+B17*N17+B18*N18+B19*N19</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C21" s="3">
         <f>C2*N2+C3*N3+C4*N4+C5*N5+C6*N6+C7*N7+C8*N8+C9*N9+C10*N10+C11*N11+C12*N12+C13*N13+C14*N14+C15*N15+C16*N16+C17*N17+C18*N18+C19*N19</f>
-        <v>19.25</v>
+        <v>13.25</v>
       </c>
       <c r="D21" s="3">
         <f>D2*N2+D3*N3+D4*N4+D5*N5+D6*N6+D7*N7+D8*N8+D9*N9+D10*N10+D11*N11+D12*N12+D13*N13+D14*N14+D15*N15+D16*N16+D17*N17+D18*N18+D19*N19</f>
-        <v>0</v>
+        <v>18.46</v>
       </c>
       <c r="E21" s="3">
         <f>E2*N2+E3*N3+E4*N4+E5*N5+E6*N6+E7*N7+E8*N8+E9*N9+E10*N10+E11*N11+E12*N12+E13*N13+E14*N14+E15*N15+E16*N16+E17*N17+E18*N18+E19*N19</f>
-        <v>21</v>
+        <v>23.75</v>
       </c>
       <c r="F21" s="3">
         <f>F2*N2+F3*N3+F4*N4+F5*N5+F6*N6+F7*N7+F8*N8+F9*N9+F10*N10+F11*N11+F12*N12+F13*N13+F14*N14+F15*N15+F16*N16+F17*N17+F18*N18+F19*N19</f>
-        <v>229.7</v>
+        <v>34.35</v>
       </c>
       <c r="G21" s="3">
         <f>G2*N2+G3*N3+G4*N4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+G13*N13+G14*N14+G15*N15+G16*N16+G17*N17+G18*N18+G19*N19</f>
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="H21" s="3">
         <f>H2*N2+H3*N3+H4*N4+H5*N5+H6*N6+H7*N7+H8*N8+H9*N9+H10*N10+H11*N11+H12*N12+H13*N13+H14*N14+H15*N15+H16*N16+H17*N17+H18*N18+H19*N19</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3">
         <f>I2*N2+I3*N3+I4*N4+I5*N5+I6*N6+I7*N7+I8*N8+I9*N9+I10*N10+I11*N11+I12*N12+I13*N13+I14*N14+I15*N15+I16*N16+I17*N17+I18*N18+I19*N19</f>
-        <v>19.25</v>
+        <v>13.25</v>
       </c>
       <c r="J21" s="3">
         <f>J2*N2+J3*N3+J4*N4+J5*N5+J6*N6+J7*N7+J8*N8+J9*N9+J10*N10+J11*N11+J12*N12+J13*N13+J14*N14+J15*N15+J16*N16+J17*N17+J18*N18+J19*N19</f>
-        <v>0</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="K21" s="3">
         <f>K2*N2+K3*N3+K4*N4+K5*N5+K6*N6+K7*N7+K8*N8+K9*N9+K10*N10+K11*N11+K12*N12+K13*N13+K14*N14+K15*N15+K16*N16+K17*N17+K18*N18+K19*N19</f>
-        <v>21</v>
+        <v>5.75</v>
       </c>
       <c r="L21" s="3">
         <f>L2*N2+L3*N3+L4*N4+L5*N5+L6*N6+L7*N7+L8*N8+L9*N9+L10*N10+L11*N11+L12*N12+L13*N13+L14*N14+L15*N15+L16*N16+L17*N17+L18*N18+L19*N19</f>
-        <v>149.69999999999999</v>
+        <v>30.1</v>
       </c>
       <c r="M21" s="3">
         <f>M2*N2+M3*N3+M4*N4+M5*N5+M6*N6+M7*N7+M8*N8+M9*N9+M10*N10+M11*N11+M12*N12+M13*N13+M14*N14+M15*N15+M16*N16+M17*N17+M18*N18+M19*N19</f>
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="N21" s="3">
         <f>SUM(N2:N20)</f>
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="O21" s="3">
         <f>SUM(O2:O19)</f>
-        <v>459.9</v>
+        <v>160.99</v>
       </c>
     </row>
   </sheetData>
@@ -7820,7 +7830,6 @@
   <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7876,1107 +7885,1107 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="16">
-        <f>Overview!B3</f>
+        <f>Overview!B5</f>
         <v>0</v>
       </c>
       <c r="C2" s="16">
-        <f>Overview!C3</f>
+        <f>Overview!C5</f>
         <v>0</v>
       </c>
       <c r="D2" s="16">
-        <f>Overview!D3</f>
+        <f>Overview!D5</f>
         <v>0</v>
       </c>
       <c r="E2" s="16">
-        <f>Overview!E3</f>
+        <f>Overview!E5</f>
         <v>0</v>
       </c>
       <c r="F2" s="16">
-        <f>Overview!F3</f>
-        <v>4.8499999999999996</v>
+        <f>Overview!F5</f>
+        <v>2</v>
       </c>
       <c r="G2" s="16">
-        <f>Overview!G3</f>
+        <f>Overview!G5</f>
         <v>0</v>
       </c>
       <c r="H2" s="16">
-        <f>Overview!H3</f>
+        <f>Overview!H5</f>
         <v>0</v>
       </c>
       <c r="I2" s="16">
-        <f>Overview!I3</f>
+        <f>Overview!I5</f>
         <v>0</v>
       </c>
       <c r="J2" s="16">
-        <f>Overview!J3</f>
+        <f>Overview!J5</f>
         <v>0</v>
       </c>
       <c r="K2" s="16">
-        <f>Overview!K3</f>
+        <f>Overview!K5</f>
         <v>0</v>
       </c>
       <c r="L2" s="16">
-        <f>Overview!L3</f>
-        <v>4.8499999999999996</v>
+        <f>Overview!L5</f>
+        <v>0</v>
       </c>
       <c r="M2" s="16">
-        <f>Overview!M3</f>
+        <f>Overview!M5</f>
         <v>0</v>
       </c>
       <c r="N2" s="16">
-        <f>Overview!N3</f>
-        <v>17</v>
+        <f>Overview!N5</f>
+        <v>1</v>
       </c>
       <c r="O2" s="16">
-        <f>Overview!O3</f>
-        <v>164.89999999999998</v>
+        <f>Overview!O5</f>
+        <v>2</v>
       </c>
       <c r="P2" s="14">
-        <f>Overview!P3</f>
-        <v>137.65</v>
+        <f>Overview!P5</f>
+        <v>26.46</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B3" s="18">
-        <f>Overview!B18</f>
+        <f>Overview!B10</f>
         <v>0</v>
       </c>
       <c r="C3" s="18">
-        <f>Overview!C18</f>
+        <f>Overview!C10</f>
         <v>0</v>
       </c>
       <c r="D3" s="18">
-        <f>Overview!D18</f>
-        <v>18</v>
+        <f>Overview!D10</f>
+        <v>0</v>
       </c>
       <c r="E3" s="18">
-        <f>Overview!E18</f>
+        <f>Overview!E10</f>
         <v>0</v>
       </c>
       <c r="F3" s="18">
-        <f>Overview!F18</f>
-        <v>0</v>
+        <f>Overview!F10</f>
+        <v>2.25</v>
       </c>
       <c r="G3" s="18">
-        <f>Overview!G18</f>
+        <f>Overview!G10</f>
         <v>0</v>
       </c>
       <c r="H3" s="18">
-        <f>Overview!H18</f>
+        <f>Overview!H10</f>
         <v>0</v>
       </c>
       <c r="I3" s="18">
-        <f>Overview!I18</f>
+        <f>Overview!I10</f>
         <v>0</v>
       </c>
       <c r="J3" s="18">
-        <f>Overview!J18</f>
-        <v>8.5</v>
+        <f>Overview!J10</f>
+        <v>0</v>
       </c>
       <c r="K3" s="18">
-        <f>Overview!K18</f>
+        <f>Overview!K10</f>
         <v>0</v>
       </c>
       <c r="L3" s="18">
-        <f>Overview!L18</f>
+        <f>Overview!L10</f>
         <v>0</v>
       </c>
       <c r="M3" s="18">
-        <f>Overview!M18</f>
+        <f>Overview!M10</f>
         <v>0</v>
       </c>
       <c r="N3" s="18">
-        <f>Overview!N18</f>
-        <v>0</v>
+        <f>Overview!N10</f>
+        <v>1</v>
       </c>
       <c r="O3" s="18">
-        <f>Overview!O18</f>
-        <v>0</v>
+        <f>Overview!O10</f>
+        <v>2.25</v>
       </c>
       <c r="P3" s="14">
-        <f>Overview!P18</f>
-        <v>991.4</v>
+        <f>Overview!P10</f>
+        <v>172.3</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="18">
-        <f>Overview!B8</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="18">
-        <f>Overview!C8</f>
-        <v>6</v>
-      </c>
-      <c r="D4" s="18">
-        <f>Overview!D8</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="18">
-        <f>Overview!E8</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="18">
-        <f>Overview!F8</f>
-        <v>6</v>
-      </c>
-      <c r="G4" s="18">
-        <f>Overview!G8</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="18">
-        <f>Overview!H8</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="18">
-        <f>Overview!I8</f>
-        <v>6</v>
-      </c>
-      <c r="J4" s="18">
-        <f>Overview!J8</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="18">
-        <f>Overview!K8</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="18">
-        <f>Overview!L8</f>
-        <v>6</v>
-      </c>
-      <c r="M4" s="18">
-        <f>Overview!M8</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="18">
-        <f>Overview!N8</f>
-        <v>0</v>
-      </c>
-      <c r="O4" s="18">
-        <f>Overview!O8</f>
-        <v>0</v>
+      <c r="A4" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="16">
+        <f>Overview!B9</f>
+        <v>5</v>
+      </c>
+      <c r="C4" s="16">
+        <f>Overview!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="16">
+        <f>Overview!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="16">
+        <f>Overview!E9</f>
+        <v>5</v>
+      </c>
+      <c r="F4" s="16">
+        <f>Overview!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="16">
+        <f>Overview!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="16">
+        <f>Overview!H9</f>
+        <v>5</v>
+      </c>
+      <c r="I4" s="16">
+        <f>Overview!I9</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="16">
+        <f>Overview!J9</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="16">
+        <f>Overview!K9</f>
+        <v>5</v>
+      </c>
+      <c r="L4" s="16">
+        <f>Overview!L9</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="16">
+        <f>Overview!M9</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="16">
+        <f>Overview!N9</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="16">
+        <f>Overview!O9</f>
+        <v>20</v>
       </c>
       <c r="P4" s="13">
-        <f>Overview!P8</f>
-        <v>305.7</v>
+        <f>Overview!P9</f>
+        <v>301.3</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B5" s="18">
-        <f>Overview!B2</f>
+        <f>Overview!B4</f>
         <v>0</v>
       </c>
       <c r="C5" s="18">
-        <f>Overview!C2</f>
+        <f>Overview!C4</f>
         <v>0</v>
       </c>
       <c r="D5" s="18">
-        <f>Overview!D2</f>
+        <f>Overview!D4</f>
         <v>0</v>
       </c>
       <c r="E5" s="18">
-        <f>Overview!E2</f>
-        <v>0.75</v>
+        <f>Overview!E4</f>
+        <v>0</v>
       </c>
       <c r="F5" s="18">
-        <f>Overview!F2</f>
-        <v>0</v>
+        <f>Overview!F4</f>
+        <v>8</v>
       </c>
       <c r="G5" s="18">
-        <f>Overview!G2</f>
+        <f>Overview!G4</f>
         <v>0</v>
       </c>
       <c r="H5" s="18">
-        <f>Overview!H2</f>
+        <f>Overview!H4</f>
         <v>0</v>
       </c>
       <c r="I5" s="18">
-        <f>Overview!I2</f>
+        <f>Overview!I4</f>
         <v>0</v>
       </c>
       <c r="J5" s="18">
-        <f>Overview!J2</f>
+        <f>Overview!J4</f>
         <v>0</v>
       </c>
       <c r="K5" s="18">
-        <f>Overview!K2</f>
-        <v>0.75</v>
+        <f>Overview!K4</f>
+        <v>0</v>
       </c>
       <c r="L5" s="18">
-        <f>Overview!L2</f>
-        <v>0</v>
+        <f>Overview!L4</f>
+        <v>4</v>
       </c>
       <c r="M5" s="18">
-        <f>Overview!M2</f>
+        <f>Overview!M4</f>
         <v>0</v>
       </c>
       <c r="N5" s="18">
-        <f>Overview!N2</f>
-        <v>28</v>
+        <f>Overview!N4</f>
+        <v>1</v>
       </c>
       <c r="O5" s="18">
-        <f>Overview!O2</f>
-        <v>42</v>
+        <f>Overview!O4</f>
+        <v>12</v>
       </c>
       <c r="P5" s="14">
-        <f>Overview!P2</f>
-        <v>86.46</v>
+        <f>Overview!P4</f>
+        <v>506.2</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B6" s="16">
-        <f>Overview!B5</f>
+        <f>Overview!B13</f>
         <v>0</v>
       </c>
       <c r="C6" s="16">
-        <f>Overview!C5</f>
+        <f>Overview!C13</f>
         <v>0</v>
       </c>
       <c r="D6" s="16">
-        <f>Overview!D5</f>
+        <f>Overview!D13</f>
         <v>0</v>
       </c>
       <c r="E6" s="16">
-        <f>Overview!E5</f>
+        <f>Overview!E13</f>
         <v>0</v>
       </c>
       <c r="F6" s="16">
-        <f>Overview!F5</f>
-        <v>2</v>
+        <f>Overview!F13</f>
+        <v>0</v>
       </c>
       <c r="G6" s="16">
-        <f>Overview!G5</f>
-        <v>0</v>
+        <f>Overview!G13</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H6" s="16">
-        <f>Overview!H5</f>
+        <f>Overview!H13</f>
         <v>0</v>
       </c>
       <c r="I6" s="16">
-        <f>Overview!I5</f>
+        <f>Overview!I13</f>
         <v>0</v>
       </c>
       <c r="J6" s="16">
-        <f>Overview!J5</f>
+        <f>Overview!J13</f>
         <v>0</v>
       </c>
       <c r="K6" s="16">
-        <f>Overview!K5</f>
+        <f>Overview!K13</f>
         <v>0</v>
       </c>
       <c r="L6" s="16">
-        <f>Overview!L5</f>
+        <f>Overview!L13</f>
         <v>0</v>
       </c>
       <c r="M6" s="16">
-        <f>Overview!M5</f>
-        <v>0</v>
+        <f>Overview!M13</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N6" s="16">
-        <f>Overview!N5</f>
-        <v>34</v>
+        <f>Overview!N13</f>
+        <v>1</v>
       </c>
       <c r="O6" s="16">
-        <f>Overview!O5</f>
-        <v>68</v>
+        <f>Overview!O13</f>
+        <v>2.2000000000000002</v>
       </c>
       <c r="P6" s="14">
-        <f>Overview!P5</f>
-        <v>26.46</v>
+        <f>Overview!P13</f>
+        <v>184.4</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="18">
-        <f>Overview!B10</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="18">
-        <f>Overview!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="18">
-        <f>Overview!D10</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="18">
-        <f>Overview!E10</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="18">
-        <f>Overview!F10</f>
-        <v>2.25</v>
-      </c>
-      <c r="G7" s="18">
-        <f>Overview!G10</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="18">
-        <f>Overview!H10</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="18">
-        <f>Overview!I10</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="18">
-        <f>Overview!J10</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="18">
-        <f>Overview!K10</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="18">
-        <f>Overview!L10</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="18">
-        <f>Overview!M10</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="18">
-        <f>Overview!N10</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="18">
-        <f>Overview!O10</f>
+      <c r="A7" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="16">
+        <f>Overview!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="16">
+        <f>Overview!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="16">
+        <f>Overview!D15</f>
+        <v>3.25</v>
+      </c>
+      <c r="E7" s="16">
+        <f>Overview!E15</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="16">
+        <f>Overview!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="16">
+        <f>Overview!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="16">
+        <f>Overview!H15</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="16">
+        <f>Overview!I15</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="16">
+        <f>Overview!J15</f>
+        <v>3.25</v>
+      </c>
+      <c r="K7" s="16">
+        <f>Overview!K15</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="16">
+        <f>Overview!L15</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="16">
+        <f>Overview!M15</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="16">
+        <f>Overview!N15</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="16">
+        <f>Overview!O15</f>
         <v>0</v>
       </c>
       <c r="P7" s="14">
-        <f>Overview!P10</f>
-        <v>172.3</v>
+        <f>Overview!P15</f>
+        <v>176.2</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="16">
-        <f>Overview!B9</f>
-        <v>5</v>
-      </c>
-      <c r="C8" s="16">
-        <f>Overview!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="16">
-        <f>Overview!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="16">
-        <f>Overview!E9</f>
-        <v>5</v>
-      </c>
-      <c r="F8" s="16">
-        <f>Overview!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="16">
-        <f>Overview!G9</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="16">
-        <f>Overview!H9</f>
-        <v>5</v>
-      </c>
-      <c r="I8" s="16">
-        <f>Overview!I9</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="16">
-        <f>Overview!J9</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="16">
-        <f>Overview!K9</f>
-        <v>5</v>
-      </c>
-      <c r="L8" s="16">
-        <f>Overview!L9</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="16">
-        <f>Overview!M9</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="16">
-        <f>Overview!N9</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="16">
-        <f>Overview!O9</f>
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
-        <f>Overview!P9</f>
-        <v>301.3</v>
+      <c r="A8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="18">
+        <f>Overview!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="18">
+        <f>Overview!C16</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="18">
+        <f>Overview!D16</f>
+        <v>3.5</v>
+      </c>
+      <c r="E8" s="18">
+        <f>Overview!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="18">
+        <f>Overview!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="18">
+        <f>Overview!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="18">
+        <f>Overview!H16</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="18">
+        <f>Overview!I16</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="18">
+        <f>Overview!J16</f>
+        <v>3.5</v>
+      </c>
+      <c r="K8" s="18">
+        <f>Overview!K16</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="18">
+        <f>Overview!L16</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="18">
+        <f>Overview!M16</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="18">
+        <f>Overview!N16</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="18">
+        <f>Overview!O16</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="14">
+        <f>Overview!P16</f>
+        <v>201.8</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B9" s="18">
-        <f>Overview!B4</f>
+        <f>Overview!B6</f>
         <v>0</v>
       </c>
       <c r="C9" s="18">
-        <f>Overview!C4</f>
+        <f>Overview!C6</f>
         <v>0</v>
       </c>
       <c r="D9" s="18">
-        <f>Overview!D4</f>
+        <f>Overview!D6</f>
         <v>0</v>
       </c>
       <c r="E9" s="18">
-        <f>Overview!E4</f>
+        <f>Overview!E6</f>
         <v>0</v>
       </c>
       <c r="F9" s="18">
-        <f>Overview!F4</f>
+        <f>Overview!F6</f>
+        <v>4</v>
+      </c>
+      <c r="G9" s="18">
+        <f>Overview!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="18">
+        <f>Overview!H6</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="18">
+        <f>Overview!I6</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="18">
+        <f>Overview!J6</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <f>Overview!K6</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="18">
+        <f>Overview!L6</f>
+        <v>4</v>
+      </c>
+      <c r="M9" s="18">
+        <f>Overview!M6</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="18">
+        <f>Overview!N6</f>
+        <v>1</v>
+      </c>
+      <c r="O9" s="18">
+        <f>Overview!O6</f>
         <v>8</v>
       </c>
-      <c r="G9" s="18">
-        <f>Overview!G4</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="18">
-        <f>Overview!H4</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="18">
-        <f>Overview!I4</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="18">
-        <f>Overview!J4</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="18">
-        <f>Overview!K4</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="18">
-        <f>Overview!L4</f>
-        <v>4</v>
-      </c>
-      <c r="M9" s="18">
-        <f>Overview!M4</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="18">
-        <f>Overview!N4</f>
-        <v>3</v>
-      </c>
-      <c r="O9" s="18">
-        <f>Overview!O4</f>
-        <v>36</v>
-      </c>
       <c r="P9" s="14">
-        <f>Overview!P4</f>
-        <v>506.2</v>
+        <f>Overview!P6</f>
+        <v>263.3</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="18">
+        <f>Overview!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="18">
+        <f>Overview!C14</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="18">
+        <f>Overview!D14</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="18">
+        <f>Overview!E14</f>
+        <v>3.15</v>
+      </c>
+      <c r="F10" s="18">
+        <f>Overview!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="18">
+        <f>Overview!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <f>Overview!H14</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18">
+        <f>Overview!I14</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="18">
+        <f>Overview!J14</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="18">
+        <f>Overview!K14</f>
+        <v>3.15</v>
+      </c>
+      <c r="L10" s="18">
+        <f>Overview!L14</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="18">
+        <f>Overview!M14</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="18">
+        <f>Overview!N14</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="18">
+        <f>Overview!O14</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="14">
+        <f>Overview!P14</f>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B11" s="16">
         <f>Overview!B11</f>
         <v>0</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C11" s="16">
         <f>Overview!C11</f>
         <v>5.5</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D11" s="16">
         <f>Overview!D11</f>
         <v>0</v>
       </c>
-      <c r="E10" s="16">
+      <c r="E11" s="16">
         <f>Overview!E11</f>
         <v>0</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F11" s="16">
         <f>Overview!F11</f>
         <v>5.5</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G11" s="16">
         <f>Overview!G11</f>
         <v>0</v>
       </c>
-      <c r="H10" s="16">
+      <c r="H11" s="16">
         <f>Overview!H11</f>
         <v>0</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I11" s="16">
         <f>Overview!I11</f>
         <v>5.5</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J11" s="16">
         <f>Overview!J11</f>
         <v>0</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K11" s="16">
         <f>Overview!K11</f>
         <v>0</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L11" s="16">
         <f>Overview!L11</f>
         <v>5.5</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M11" s="16">
         <f>Overview!M11</f>
         <v>0</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N11" s="16">
         <f>Overview!N11</f>
-        <v>0</v>
-      </c>
-      <c r="O10" s="16">
+        <v>1</v>
+      </c>
+      <c r="O11" s="16">
         <f>Overview!O11</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="14">
+        <v>22</v>
+      </c>
+      <c r="P11" s="14">
         <f>Overview!P11</f>
         <v>595</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="18">
-        <f>Overview!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="18">
-        <f>Overview!C6</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="18">
-        <f>Overview!D6</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="18">
-        <f>Overview!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="18">
-        <f>Overview!F6</f>
-        <v>4</v>
-      </c>
-      <c r="G11" s="18">
-        <f>Overview!G6</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="18">
-        <f>Overview!H6</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="18">
-        <f>Overview!I6</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="18">
-        <f>Overview!J6</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="18">
-        <f>Overview!K6</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="18">
-        <f>Overview!L6</f>
-        <v>4</v>
-      </c>
-      <c r="M11" s="18">
-        <f>Overview!M6</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="18">
-        <f>Overview!N6</f>
-        <v>9</v>
-      </c>
-      <c r="O11" s="18">
-        <f>Overview!O6</f>
-        <v>72</v>
-      </c>
-      <c r="P11" s="14">
-        <f>Overview!P6</f>
-        <v>263.3</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B12" s="16">
-        <f>Overview!B7</f>
+        <f>Overview!B17</f>
         <v>0</v>
       </c>
       <c r="C12" s="16">
-        <f>Overview!C7</f>
-        <v>1.75</v>
+        <f>Overview!C17</f>
+        <v>0</v>
       </c>
       <c r="D12" s="16">
-        <f>Overview!D7</f>
+        <f>Overview!D17</f>
         <v>0</v>
       </c>
       <c r="E12" s="16">
-        <f>Overview!E7</f>
-        <v>0</v>
+        <f>Overview!E17</f>
+        <v>14</v>
       </c>
       <c r="F12" s="16">
-        <f>Overview!F7</f>
-        <v>1.75</v>
+        <f>Overview!F17</f>
+        <v>0</v>
       </c>
       <c r="G12" s="16">
-        <f>Overview!G7</f>
+        <f>Overview!G17</f>
         <v>0</v>
       </c>
       <c r="H12" s="16">
-        <f>Overview!H7</f>
+        <f>Overview!H17</f>
         <v>0</v>
       </c>
       <c r="I12" s="16">
-        <f>Overview!I7</f>
-        <v>1.75</v>
+        <f>Overview!I17</f>
+        <v>0</v>
       </c>
       <c r="J12" s="16">
-        <f>Overview!J7</f>
+        <f>Overview!J17</f>
         <v>0</v>
       </c>
       <c r="K12" s="16">
-        <f>Overview!K7</f>
+        <f>Overview!K17</f>
         <v>0</v>
       </c>
       <c r="L12" s="16">
-        <f>Overview!L7</f>
-        <v>1.75</v>
+        <f>Overview!L17</f>
+        <v>0</v>
       </c>
       <c r="M12" s="16">
-        <f>Overview!M7</f>
+        <f>Overview!M17</f>
         <v>0</v>
       </c>
       <c r="N12" s="16">
-        <f>Overview!N7</f>
-        <v>11</v>
+        <f>Overview!N17</f>
+        <v>1</v>
       </c>
       <c r="O12" s="16">
-        <f>Overview!O7</f>
-        <v>77</v>
+        <f>Overview!O17</f>
+        <v>14</v>
       </c>
       <c r="P12" s="14">
-        <f>Overview!P7</f>
-        <v>80</v>
+        <f>Overview!P17</f>
+        <v>133.38</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="18">
-        <f>Overview!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="18">
-        <f>Overview!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="18">
-        <f>Overview!D12</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="18">
-        <f>Overview!E12</f>
-        <v>4</v>
-      </c>
-      <c r="F13" s="18">
-        <f>Overview!F12</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="18">
-        <f>Overview!G12</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="18">
-        <f>Overview!H12</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="18">
-        <f>Overview!I12</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="18">
-        <f>Overview!J12</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="18">
-        <f>Overview!K12</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="18">
-        <f>Overview!L12</f>
-        <v>4</v>
-      </c>
-      <c r="M13" s="18">
-        <f>Overview!M12</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="18">
-        <f>Overview!N12</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="18">
-        <f>Overview!O12</f>
-        <v>0</v>
+      <c r="A13" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="16">
+        <f>Overview!B3</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="16">
+        <f>Overview!C3</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="16">
+        <f>Overview!D3</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16">
+        <f>Overview!E3</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <f>Overview!F3</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G13" s="16">
+        <f>Overview!G3</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="16">
+        <f>Overview!H3</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <f>Overview!I3</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="16">
+        <f>Overview!J3</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="16">
+        <f>Overview!K3</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="16">
+        <f>Overview!L3</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="M13" s="16">
+        <f>Overview!M3</f>
+        <v>0</v>
+      </c>
+      <c r="N13" s="16">
+        <f>Overview!N3</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="16">
+        <f>Overview!O3</f>
+        <v>9.6999999999999993</v>
       </c>
       <c r="P13" s="14">
-        <f>Overview!P12</f>
-        <v>161</v>
+        <f>Overview!P3</f>
+        <v>137.65</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="16">
-        <f>Overview!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="16">
-        <f>Overview!C13</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="16">
-        <f>Overview!D13</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="16">
-        <f>Overview!E13</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="16">
-        <f>Overview!F13</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="16">
-        <f>Overview!G13</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H14" s="16">
-        <f>Overview!H13</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="16">
-        <f>Overview!I13</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="16">
-        <f>Overview!J13</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="16">
-        <f>Overview!K13</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="16">
-        <f>Overview!L13</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="16">
-        <f>Overview!M13</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="N14" s="16">
-        <f>Overview!N13</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="16">
-        <f>Overview!O13</f>
-        <v>0</v>
+      <c r="A14" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="18">
+        <f>Overview!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="18">
+        <f>Overview!C18</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="18">
+        <f>Overview!D18</f>
+        <v>18</v>
+      </c>
+      <c r="E14" s="18">
+        <f>Overview!E18</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="18">
+        <f>Overview!F18</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="18">
+        <f>Overview!G18</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="18">
+        <f>Overview!H18</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="18">
+        <f>Overview!I18</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="18">
+        <f>Overview!J18</f>
+        <v>8.5</v>
+      </c>
+      <c r="K14" s="18">
+        <f>Overview!K18</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="18">
+        <f>Overview!L18</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="18">
+        <f>Overview!M18</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="18">
+        <f>Overview!N18</f>
+        <v>1</v>
+      </c>
+      <c r="O14" s="18">
+        <f>Overview!O18</f>
+        <v>26.5</v>
       </c>
       <c r="P14" s="14">
-        <f>Overview!P13</f>
-        <v>184.4</v>
+        <f>Overview!P18</f>
+        <v>991.4</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B15" s="18">
-        <f>Overview!B14</f>
+        <f>Overview!B8</f>
         <v>0</v>
       </c>
       <c r="C15" s="18">
-        <f>Overview!C14</f>
-        <v>0</v>
+        <f>Overview!C8</f>
+        <v>6</v>
       </c>
       <c r="D15" s="18">
-        <f>Overview!D14</f>
+        <f>Overview!D8</f>
         <v>0</v>
       </c>
       <c r="E15" s="18">
-        <f>Overview!E14</f>
-        <v>3.15</v>
+        <f>Overview!E8</f>
+        <v>0</v>
       </c>
       <c r="F15" s="18">
-        <f>Overview!F14</f>
-        <v>0</v>
+        <f>Overview!F8</f>
+        <v>6</v>
       </c>
       <c r="G15" s="18">
-        <f>Overview!G14</f>
+        <f>Overview!G8</f>
         <v>0</v>
       </c>
       <c r="H15" s="18">
-        <f>Overview!H14</f>
+        <f>Overview!H8</f>
         <v>0</v>
       </c>
       <c r="I15" s="18">
-        <f>Overview!I14</f>
-        <v>0</v>
+        <f>Overview!I8</f>
+        <v>6</v>
       </c>
       <c r="J15" s="18">
-        <f>Overview!J14</f>
+        <f>Overview!J8</f>
         <v>0</v>
       </c>
       <c r="K15" s="18">
-        <f>Overview!K14</f>
-        <v>3.15</v>
+        <f>Overview!K8</f>
+        <v>0</v>
       </c>
       <c r="L15" s="18">
-        <f>Overview!L14</f>
-        <v>0</v>
+        <f>Overview!L8</f>
+        <v>6</v>
       </c>
       <c r="M15" s="18">
-        <f>Overview!M14</f>
+        <f>Overview!M8</f>
         <v>0</v>
       </c>
       <c r="N15" s="18">
-        <f>Overview!N14</f>
-        <v>0</v>
+        <f>Overview!N8</f>
+        <v>1</v>
       </c>
       <c r="O15" s="18">
-        <f>Overview!O14</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="14">
-        <f>Overview!P14</f>
-        <v>359</v>
+        <f>Overview!O8</f>
+        <v>24</v>
+      </c>
+      <c r="P15" s="13">
+        <f>Overview!P8</f>
+        <v>305.7</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="16">
-        <f>Overview!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="16">
-        <f>Overview!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="16">
-        <f>Overview!D15</f>
-        <v>3.25</v>
-      </c>
-      <c r="E16" s="16">
-        <f>Overview!E15</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="16">
-        <f>Overview!F15</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="16">
-        <f>Overview!G15</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="16">
-        <f>Overview!H15</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="16">
-        <f>Overview!I15</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="16">
-        <f>Overview!J15</f>
-        <v>3.25</v>
-      </c>
-      <c r="K16" s="16">
-        <f>Overview!K15</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="16">
-        <f>Overview!L15</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="16">
-        <f>Overview!M15</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="16">
-        <f>Overview!N15</f>
-        <v>0</v>
-      </c>
-      <c r="O16" s="16">
-        <f>Overview!O15</f>
-        <v>0</v>
+      <c r="A16" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="18">
+        <f>Overview!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="18">
+        <f>Overview!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="18">
+        <f>Overview!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="18">
+        <f>Overview!E12</f>
+        <v>4</v>
+      </c>
+      <c r="F16" s="18">
+        <f>Overview!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="18">
+        <f>Overview!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <f>Overview!H12</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="18">
+        <f>Overview!I12</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="18">
+        <f>Overview!J12</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="18">
+        <f>Overview!K12</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <f>Overview!L12</f>
+        <v>4</v>
+      </c>
+      <c r="M16" s="18">
+        <f>Overview!M12</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="18">
+        <f>Overview!N12</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="18">
+        <f>Overview!O12</f>
+        <v>8</v>
       </c>
       <c r="P16" s="14">
-        <f>Overview!P15</f>
-        <v>176.2</v>
+        <f>Overview!P12</f>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="B17" s="18">
-        <f>Overview!B16</f>
+        <f>Overview!B2</f>
         <v>0</v>
       </c>
       <c r="C17" s="18">
-        <f>Overview!C16</f>
+        <f>Overview!C2</f>
         <v>0</v>
       </c>
       <c r="D17" s="18">
-        <f>Overview!D16</f>
-        <v>3.5</v>
+        <f>Overview!D2</f>
+        <v>0</v>
       </c>
       <c r="E17" s="18">
-        <f>Overview!E16</f>
-        <v>0</v>
+        <f>Overview!E2</f>
+        <v>0.75</v>
       </c>
       <c r="F17" s="18">
-        <f>Overview!F16</f>
+        <f>Overview!F2</f>
         <v>0</v>
       </c>
       <c r="G17" s="18">
-        <f>Overview!G16</f>
+        <f>Overview!G2</f>
         <v>0</v>
       </c>
       <c r="H17" s="18">
-        <f>Overview!H16</f>
+        <f>Overview!H2</f>
         <v>0</v>
       </c>
       <c r="I17" s="18">
-        <f>Overview!I16</f>
+        <f>Overview!I2</f>
         <v>0</v>
       </c>
       <c r="J17" s="18">
-        <f>Overview!J16</f>
-        <v>3.5</v>
+        <f>Overview!J2</f>
+        <v>0</v>
       </c>
       <c r="K17" s="18">
-        <f>Overview!K16</f>
-        <v>0</v>
+        <f>Overview!K2</f>
+        <v>0.75</v>
       </c>
       <c r="L17" s="18">
-        <f>Overview!L16</f>
+        <f>Overview!L2</f>
         <v>0</v>
       </c>
       <c r="M17" s="18">
-        <f>Overview!M16</f>
+        <f>Overview!M2</f>
         <v>0</v>
       </c>
       <c r="N17" s="18">
-        <f>Overview!N16</f>
-        <v>0</v>
+        <f>Overview!N2</f>
+        <v>1</v>
       </c>
       <c r="O17" s="18">
-        <f>Overview!O16</f>
-        <v>0</v>
+        <f>Overview!O2</f>
+        <v>1.5</v>
       </c>
       <c r="P17" s="14">
-        <f>Overview!P16</f>
-        <v>201.8</v>
+        <f>Overview!P2</f>
+        <v>86.46</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B18" s="16">
-        <f>Overview!B17</f>
+        <f>Overview!B7</f>
         <v>0</v>
       </c>
       <c r="C18" s="16">
-        <f>Overview!C17</f>
-        <v>0</v>
+        <f>Overview!C7</f>
+        <v>1.75</v>
       </c>
       <c r="D18" s="16">
-        <f>Overview!D17</f>
+        <f>Overview!D7</f>
         <v>0</v>
       </c>
       <c r="E18" s="16">
-        <f>Overview!E17</f>
-        <v>14</v>
+        <f>Overview!E7</f>
+        <v>0</v>
       </c>
       <c r="F18" s="16">
-        <f>Overview!F17</f>
-        <v>0</v>
+        <f>Overview!F7</f>
+        <v>1.75</v>
       </c>
       <c r="G18" s="16">
-        <f>Overview!G17</f>
+        <f>Overview!G7</f>
         <v>0</v>
       </c>
       <c r="H18" s="16">
-        <f>Overview!H17</f>
+        <f>Overview!H7</f>
         <v>0</v>
       </c>
       <c r="I18" s="16">
-        <f>Overview!I17</f>
-        <v>0</v>
+        <f>Overview!I7</f>
+        <v>1.75</v>
       </c>
       <c r="J18" s="16">
-        <f>Overview!J17</f>
+        <f>Overview!J7</f>
         <v>0</v>
       </c>
       <c r="K18" s="16">
-        <f>Overview!K17</f>
+        <f>Overview!K7</f>
         <v>0</v>
       </c>
       <c r="L18" s="16">
-        <f>Overview!L17</f>
-        <v>0</v>
+        <f>Overview!L7</f>
+        <v>1.75</v>
       </c>
       <c r="M18" s="16">
-        <f>Overview!M17</f>
+        <f>Overview!M7</f>
         <v>0</v>
       </c>
       <c r="N18" s="16">
-        <f>Overview!N17</f>
-        <v>0</v>
+        <f>Overview!N7</f>
+        <v>1</v>
       </c>
       <c r="O18" s="16">
-        <f>Overview!O17</f>
-        <v>0</v>
+        <f>Overview!O7</f>
+        <v>7</v>
       </c>
       <c r="P18" s="14">
-        <f>Overview!P17</f>
-        <v>133.38</v>
+        <f>Overview!P7</f>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -8986,9 +8995,1327 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1485E3A-19D0-47B9-867F-49E3EDE141F8}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="16">
+        <f>Overview!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="16">
+        <f>Overview!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="16">
+        <f>Overview!D17</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="16">
+        <f>Overview!E17</f>
+        <v>14</v>
+      </c>
+      <c r="F2" s="16">
+        <f>Overview!F17</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="16">
+        <f>Overview!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="16">
+        <f>Overview!H17</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="16">
+        <f>Overview!I17</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="16">
+        <f>Overview!J17</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="16">
+        <f>Overview!K17</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="16">
+        <f>Overview!L17</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="16">
+        <f>Overview!M17</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="16">
+        <f>Overview!N17</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="16">
+        <f>Overview!O17</f>
+        <v>14</v>
+      </c>
+      <c r="P2" s="14">
+        <f>Overview!P17</f>
+        <v>133.38</v>
+      </c>
+      <c r="U2">
+        <f>SUM(O2:O18)</f>
+        <v>159.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="16">
+        <f>Overview!B3</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="16">
+        <f>Overview!C3</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="16">
+        <f>Overview!D3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="16">
+        <f>Overview!E3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="16">
+        <f>Overview!F3</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G3" s="16">
+        <f>Overview!G3</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <f>Overview!H3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="16">
+        <f>Overview!I3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="16">
+        <f>Overview!J3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="16">
+        <f>Overview!K3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="16">
+        <f>Overview!L3</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="M3" s="16">
+        <f>Overview!M3</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="16">
+        <f>Overview!N3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="16">
+        <f>Overview!O3</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="P3" s="14">
+        <f>Overview!P3</f>
+        <v>137.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="18">
+        <f>Overview!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="18">
+        <f>Overview!C18</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="18">
+        <f>Overview!D18</f>
+        <v>18</v>
+      </c>
+      <c r="E4" s="18">
+        <f>Overview!E18</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="18">
+        <f>Overview!F18</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
+        <f>Overview!G18</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="18">
+        <f>Overview!H18</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="18">
+        <f>Overview!I18</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="18">
+        <f>Overview!J18</f>
+        <v>8.5</v>
+      </c>
+      <c r="K4" s="18">
+        <f>Overview!K18</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="18">
+        <f>Overview!L18</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="18">
+        <f>Overview!M18</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="18">
+        <f>Overview!N18</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="18">
+        <f>Overview!O18</f>
+        <v>26.5</v>
+      </c>
+      <c r="P4" s="14">
+        <f>Overview!P18</f>
+        <v>991.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="18">
+        <f>Overview!B8</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="18">
+        <f>Overview!C8</f>
+        <v>6</v>
+      </c>
+      <c r="D5" s="18">
+        <f>Overview!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="18">
+        <f>Overview!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="18">
+        <f>Overview!F8</f>
+        <v>6</v>
+      </c>
+      <c r="G5" s="18">
+        <f>Overview!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="18">
+        <f>Overview!H8</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="18">
+        <f>Overview!I8</f>
+        <v>6</v>
+      </c>
+      <c r="J5" s="18">
+        <f>Overview!J8</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="18">
+        <f>Overview!K8</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="18">
+        <f>Overview!L8</f>
+        <v>6</v>
+      </c>
+      <c r="M5" s="18">
+        <f>Overview!M8</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="18">
+        <f>Overview!N8</f>
+        <v>1</v>
+      </c>
+      <c r="O5" s="18">
+        <f>Overview!O8</f>
+        <v>24</v>
+      </c>
+      <c r="P5" s="13">
+        <f>Overview!P8</f>
+        <v>305.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="18">
+        <f>Overview!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="18">
+        <f>Overview!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="18">
+        <f>Overview!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="18">
+        <f>Overview!E12</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="18">
+        <f>Overview!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="18">
+        <f>Overview!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <f>Overview!H12</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="18">
+        <f>Overview!I12</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="18">
+        <f>Overview!J12</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="18">
+        <f>Overview!K12</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="18">
+        <f>Overview!L12</f>
+        <v>4</v>
+      </c>
+      <c r="M6" s="18">
+        <f>Overview!M12</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="18">
+        <f>Overview!N12</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="18">
+        <f>Overview!O12</f>
+        <v>8</v>
+      </c>
+      <c r="P6" s="14">
+        <f>Overview!P12</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="18">
+        <f>Overview!B2</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="18">
+        <f>Overview!C2</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="18">
+        <f>Overview!D2</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="18">
+        <f>Overview!E2</f>
+        <v>0.75</v>
+      </c>
+      <c r="F7" s="18">
+        <f>Overview!F2</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
+        <f>Overview!G2</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="18">
+        <f>Overview!H2</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="18">
+        <f>Overview!I2</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="18">
+        <f>Overview!J2</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="18">
+        <f>Overview!K2</f>
+        <v>0.75</v>
+      </c>
+      <c r="L7" s="18">
+        <f>Overview!L2</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="18">
+        <f>Overview!M2</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="18">
+        <f>Overview!N2</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="18">
+        <f>Overview!O2</f>
+        <v>1.5</v>
+      </c>
+      <c r="P7" s="14">
+        <f>Overview!P2</f>
+        <v>86.46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="16">
+        <f>Overview!B7</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="16">
+        <f>Overview!C7</f>
+        <v>1.75</v>
+      </c>
+      <c r="D8" s="16">
+        <f>Overview!D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="16">
+        <f>Overview!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="16">
+        <f>Overview!F7</f>
+        <v>1.75</v>
+      </c>
+      <c r="G8" s="16">
+        <f>Overview!G7</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f>Overview!H7</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="16">
+        <f>Overview!I7</f>
+        <v>1.75</v>
+      </c>
+      <c r="J8" s="16">
+        <f>Overview!J7</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="16">
+        <f>Overview!K7</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="16">
+        <f>Overview!L7</f>
+        <v>1.75</v>
+      </c>
+      <c r="M8" s="16">
+        <f>Overview!M7</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="16">
+        <f>Overview!N7</f>
+        <v>1</v>
+      </c>
+      <c r="O8" s="16">
+        <f>Overview!O7</f>
+        <v>7</v>
+      </c>
+      <c r="P8" s="14">
+        <f>Overview!P7</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="16">
+        <f>Overview!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="16">
+        <f>Overview!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="16">
+        <f>Overview!D5</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="16">
+        <f>Overview!E5</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="16">
+        <f>Overview!F5</f>
+        <v>2</v>
+      </c>
+      <c r="G9" s="16">
+        <f>Overview!G5</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="16">
+        <f>Overview!H5</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="16">
+        <f>Overview!I5</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="16">
+        <f>Overview!J5</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="16">
+        <f>Overview!K5</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="16">
+        <f>Overview!L5</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="16">
+        <f>Overview!M5</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="16">
+        <f>Overview!N5</f>
+        <v>1</v>
+      </c>
+      <c r="O9" s="16">
+        <f>Overview!O5</f>
+        <v>2</v>
+      </c>
+      <c r="P9" s="14">
+        <f>Overview!P5</f>
+        <v>26.46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="18">
+        <f>Overview!B10</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="18">
+        <f>Overview!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="18">
+        <f>Overview!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="18">
+        <f>Overview!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="18">
+        <f>Overview!F10</f>
+        <v>2.25</v>
+      </c>
+      <c r="G10" s="18">
+        <f>Overview!G10</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="18">
+        <f>Overview!H10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="18">
+        <f>Overview!I10</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="18">
+        <f>Overview!J10</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="18">
+        <f>Overview!K10</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="18">
+        <f>Overview!L10</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="18">
+        <f>Overview!M10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="18">
+        <f>Overview!N10</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="18">
+        <f>Overview!O10</f>
+        <v>2.25</v>
+      </c>
+      <c r="P10" s="14">
+        <f>Overview!P10</f>
+        <v>172.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="16">
+        <f>Overview!B9</f>
+        <v>5</v>
+      </c>
+      <c r="C11" s="16">
+        <f>Overview!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="16">
+        <f>Overview!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
+        <f>Overview!E9</f>
+        <v>5</v>
+      </c>
+      <c r="F11" s="16">
+        <f>Overview!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <f>Overview!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="16">
+        <f>Overview!H9</f>
+        <v>5</v>
+      </c>
+      <c r="I11" s="16">
+        <f>Overview!I9</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="16">
+        <f>Overview!J9</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="16">
+        <f>Overview!K9</f>
+        <v>5</v>
+      </c>
+      <c r="L11" s="16">
+        <f>Overview!L9</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="16">
+        <f>Overview!M9</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="16">
+        <f>Overview!N9</f>
+        <v>1</v>
+      </c>
+      <c r="O11" s="16">
+        <f>Overview!O9</f>
+        <v>20</v>
+      </c>
+      <c r="P11" s="13">
+        <f>Overview!P9</f>
+        <v>301.3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="18">
+        <f>Overview!B4</f>
+        <v>0</v>
+      </c>
+      <c r="C12" s="18">
+        <f>Overview!C4</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="18">
+        <f>Overview!D4</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="18">
+        <f>Overview!E4</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="18">
+        <f>Overview!F4</f>
+        <v>8</v>
+      </c>
+      <c r="G12" s="18">
+        <f>Overview!G4</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="18">
+        <f>Overview!H4</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="18">
+        <f>Overview!I4</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="18">
+        <f>Overview!J4</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="18">
+        <f>Overview!K4</f>
+        <v>0</v>
+      </c>
+      <c r="L12" s="18">
+        <f>Overview!L4</f>
+        <v>4</v>
+      </c>
+      <c r="M12" s="18">
+        <f>Overview!M4</f>
+        <v>0</v>
+      </c>
+      <c r="N12" s="18">
+        <f>Overview!N4</f>
+        <v>1</v>
+      </c>
+      <c r="O12" s="18">
+        <f>Overview!O4</f>
+        <v>12</v>
+      </c>
+      <c r="P12" s="14">
+        <f>Overview!P4</f>
+        <v>506.2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="16">
+        <f>Overview!B13</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="16">
+        <f>Overview!C13</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="16">
+        <f>Overview!D13</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16">
+        <f>Overview!E13</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <f>Overview!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <f>Overview!G13</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H13" s="16">
+        <f>Overview!H13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="16">
+        <f>Overview!I13</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="16">
+        <f>Overview!J13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="16">
+        <f>Overview!K13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="16">
+        <f>Overview!L13</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="16">
+        <f>Overview!M13</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N13" s="16">
+        <f>Overview!N13</f>
+        <v>1</v>
+      </c>
+      <c r="O13" s="16">
+        <f>Overview!O13</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P13" s="14">
+        <f>Overview!P13</f>
+        <v>184.4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="16">
+        <f>Overview!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="16">
+        <f>Overview!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="16">
+        <f>Overview!D15</f>
+        <v>3.25</v>
+      </c>
+      <c r="E14" s="16">
+        <f>Overview!E15</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="16">
+        <f>Overview!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="16">
+        <f>Overview!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="16">
+        <f>Overview!H15</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="16">
+        <f>Overview!I15</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="16">
+        <f>Overview!J15</f>
+        <v>3.25</v>
+      </c>
+      <c r="K14" s="16">
+        <f>Overview!K15</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="16">
+        <f>Overview!L15</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="16">
+        <f>Overview!M15</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="16">
+        <f>Overview!N15</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="16">
+        <f>Overview!O15</f>
+        <v>0</v>
+      </c>
+      <c r="P14" s="14">
+        <f>Overview!P15</f>
+        <v>176.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="18">
+        <f>Overview!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="18">
+        <f>Overview!C16</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="18">
+        <f>Overview!D16</f>
+        <v>3.5</v>
+      </c>
+      <c r="E15" s="18">
+        <f>Overview!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="18">
+        <f>Overview!F16</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="18">
+        <f>Overview!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="18">
+        <f>Overview!H16</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="18">
+        <f>Overview!I16</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="18">
+        <f>Overview!J16</f>
+        <v>3.5</v>
+      </c>
+      <c r="K15" s="18">
+        <f>Overview!K16</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="18">
+        <f>Overview!L16</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="18">
+        <f>Overview!M16</f>
+        <v>0</v>
+      </c>
+      <c r="N15" s="18">
+        <f>Overview!N16</f>
+        <v>0</v>
+      </c>
+      <c r="O15" s="18">
+        <f>Overview!O16</f>
+        <v>0</v>
+      </c>
+      <c r="P15" s="14">
+        <f>Overview!P16</f>
+        <v>201.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="18">
+        <f>Overview!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="18">
+        <f>Overview!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="18">
+        <f>Overview!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="18">
+        <f>Overview!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="18">
+        <f>Overview!F6</f>
+        <v>4</v>
+      </c>
+      <c r="G16" s="18">
+        <f>Overview!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="18">
+        <f>Overview!H6</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="18">
+        <f>Overview!I6</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="18">
+        <f>Overview!J6</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="18">
+        <f>Overview!K6</f>
+        <v>0</v>
+      </c>
+      <c r="L16" s="18">
+        <f>Overview!L6</f>
+        <v>4</v>
+      </c>
+      <c r="M16" s="18">
+        <f>Overview!M6</f>
+        <v>0</v>
+      </c>
+      <c r="N16" s="18">
+        <f>Overview!N6</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="18">
+        <f>Overview!O6</f>
+        <v>8</v>
+      </c>
+      <c r="P16" s="14">
+        <f>Overview!P6</f>
+        <v>263.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" s="18">
+        <f>Overview!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="18">
+        <f>Overview!C14</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="18">
+        <f>Overview!D14</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="18">
+        <f>Overview!E14</f>
+        <v>3.15</v>
+      </c>
+      <c r="F17" s="18">
+        <f>Overview!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="18">
+        <f>Overview!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="18">
+        <f>Overview!H14</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="18">
+        <f>Overview!I14</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="18">
+        <f>Overview!J14</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="18">
+        <f>Overview!K14</f>
+        <v>3.15</v>
+      </c>
+      <c r="L17" s="18">
+        <f>Overview!L14</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="18">
+        <f>Overview!M14</f>
+        <v>0</v>
+      </c>
+      <c r="N17" s="18">
+        <f>Overview!N14</f>
+        <v>0</v>
+      </c>
+      <c r="O17" s="18">
+        <f>Overview!O14</f>
+        <v>0</v>
+      </c>
+      <c r="P17" s="14">
+        <f>Overview!P14</f>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="16">
+        <f>Overview!B11</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="16">
+        <f>Overview!C11</f>
+        <v>5.5</v>
+      </c>
+      <c r="D18" s="16">
+        <f>Overview!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="16">
+        <f>Overview!E11</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
+        <f>Overview!F11</f>
+        <v>5.5</v>
+      </c>
+      <c r="G18" s="16">
+        <f>Overview!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="16">
+        <f>Overview!H11</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="16">
+        <f>Overview!I11</f>
+        <v>5.5</v>
+      </c>
+      <c r="J18" s="16">
+        <f>Overview!J11</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="16">
+        <f>Overview!K11</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="16">
+        <f>Overview!L11</f>
+        <v>5.5</v>
+      </c>
+      <c r="M18" s="16">
+        <f>Overview!M11</f>
+        <v>0</v>
+      </c>
+      <c r="N18" s="16">
+        <f>Overview!N11</f>
+        <v>1</v>
+      </c>
+      <c r="O18" s="16">
+        <f>Overview!O11</f>
+        <v>22</v>
+      </c>
+      <c r="P18" s="14">
+        <f>Overview!P11</f>
+        <v>595</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E002DF-AADC-4AA9-9F65-638D87312B83}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aktie_Utdelning.xlsx
+++ b/Aktie_Utdelning.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AECA3A90-19F2-4F41-8AE5-9299D587C145}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9DDF89-CD8D-4443-820A-B45301FDE765}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Python" sheetId="2" r:id="rId2"/>
     <sheet name="Blad1" sheetId="3" r:id="rId3"/>
-    <sheet name="Blad2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -240,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
   <si>
     <t>Feb</t>
   </si>
@@ -345,9 +344,6 @@
   </si>
   <si>
     <t>årlig utd.</t>
-  </si>
-  <si>
-    <t>2020-07-29 bank=4000 magic=1, ordning 1</t>
   </si>
 </sst>
 </file>
@@ -10167,155 +10163,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9E002DF-AADC-4AA9-9F65-638D87312B83}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Aktie_Utdelning.xlsx
+++ b/Aktie_Utdelning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9DDF89-CD8D-4443-820A-B45301FDE765}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0235C184-E258-4F2E-9511-54714FD644A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
   <si>
     <t>Feb</t>
   </si>
@@ -7823,13 +7823,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10BA0FA-7F5A-4054-944A-818344D765CC}">
   <sheetPr codeName="Blad2"/>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="15" t="s">
         <v>14</v>
       </c>
@@ -7878,1110 +7879,1117 @@
       <c r="P1" s="15" t="s">
         <v>16</v>
       </c>
+      <c r="U1" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="16">
+        <f>Overview!B17</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="16">
+        <f>Overview!C17</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="16">
+        <f>Overview!D17</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="16">
+        <f>Overview!E17</f>
+        <v>14</v>
+      </c>
+      <c r="F2" s="16">
+        <f>Overview!F17</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="16">
+        <f>Overview!G17</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="16">
+        <f>Overview!H17</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="16">
+        <f>Overview!I17</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="16">
+        <f>Overview!J17</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="16">
+        <f>Overview!K17</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="16">
+        <f>Overview!L17</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="16">
+        <f>Overview!M17</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="16">
+        <f>Overview!N17</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="16">
+        <f>Overview!O17</f>
+        <v>14</v>
+      </c>
+      <c r="P2" s="14">
+        <f>Overview!P17</f>
+        <v>133.38</v>
+      </c>
+      <c r="U2">
+        <f>SUM(O2:O18)</f>
+        <v>159.15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="16">
+        <f>Overview!B3</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="16">
+        <f>Overview!C3</f>
+        <v>0</v>
+      </c>
+      <c r="D3" s="16">
+        <f>Overview!D3</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="16">
+        <f>Overview!E3</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="16">
+        <f>Overview!F3</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="G3" s="16">
+        <f>Overview!G3</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="16">
+        <f>Overview!H3</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="16">
+        <f>Overview!I3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="16">
+        <f>Overview!J3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="16">
+        <f>Overview!K3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="16">
+        <f>Overview!L3</f>
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="M3" s="16">
+        <f>Overview!M3</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="16">
+        <f>Overview!N3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="16">
+        <f>Overview!O3</f>
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="P3" s="14">
+        <f>Overview!P3</f>
+        <v>137.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="18">
+        <f>Overview!B18</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="18">
+        <f>Overview!C18</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="18">
+        <f>Overview!D18</f>
+        <v>18</v>
+      </c>
+      <c r="E4" s="18">
+        <f>Overview!E18</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="18">
+        <f>Overview!F18</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="18">
+        <f>Overview!G18</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="18">
+        <f>Overview!H18</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="18">
+        <f>Overview!I18</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="18">
+        <f>Overview!J18</f>
+        <v>8.5</v>
+      </c>
+      <c r="K4" s="18">
+        <f>Overview!K18</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="18">
+        <f>Overview!L18</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="18">
+        <f>Overview!M18</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="18">
+        <f>Overview!N18</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="18">
+        <f>Overview!O18</f>
+        <v>26.5</v>
+      </c>
+      <c r="P4" s="14">
+        <f>Overview!P18</f>
+        <v>991.4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="18">
+        <f>Overview!B8</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="18">
+        <f>Overview!C8</f>
+        <v>6</v>
+      </c>
+      <c r="D5" s="18">
+        <f>Overview!D8</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="18">
+        <f>Overview!E8</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="18">
+        <f>Overview!F8</f>
+        <v>6</v>
+      </c>
+      <c r="G5" s="18">
+        <f>Overview!G8</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="18">
+        <f>Overview!H8</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="18">
+        <f>Overview!I8</f>
+        <v>6</v>
+      </c>
+      <c r="J5" s="18">
+        <f>Overview!J8</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="18">
+        <f>Overview!K8</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="18">
+        <f>Overview!L8</f>
+        <v>6</v>
+      </c>
+      <c r="M5" s="18">
+        <f>Overview!M8</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="18">
+        <f>Overview!N8</f>
+        <v>1</v>
+      </c>
+      <c r="O5" s="18">
+        <f>Overview!O8</f>
+        <v>24</v>
+      </c>
+      <c r="P5" s="13">
+        <f>Overview!P8</f>
+        <v>305.7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="18">
+        <f>Overview!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="18">
+        <f>Overview!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="18">
+        <f>Overview!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="18">
+        <f>Overview!E12</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="18">
+        <f>Overview!F12</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="18">
+        <f>Overview!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="18">
+        <f>Overview!H12</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="18">
+        <f>Overview!I12</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="18">
+        <f>Overview!J12</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="18">
+        <f>Overview!K12</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="18">
+        <f>Overview!L12</f>
+        <v>4</v>
+      </c>
+      <c r="M6" s="18">
+        <f>Overview!M12</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="18">
+        <f>Overview!N12</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="18">
+        <f>Overview!O12</f>
+        <v>8</v>
+      </c>
+      <c r="P6" s="14">
+        <f>Overview!P12</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="18">
+        <f>Overview!B2</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="18">
+        <f>Overview!C2</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="18">
+        <f>Overview!D2</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="18">
+        <f>Overview!E2</f>
+        <v>0.75</v>
+      </c>
+      <c r="F7" s="18">
+        <f>Overview!F2</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="18">
+        <f>Overview!G2</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="18">
+        <f>Overview!H2</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="18">
+        <f>Overview!I2</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="18">
+        <f>Overview!J2</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="18">
+        <f>Overview!K2</f>
+        <v>0.75</v>
+      </c>
+      <c r="L7" s="18">
+        <f>Overview!L2</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="18">
+        <f>Overview!M2</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="18">
+        <f>Overview!N2</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="18">
+        <f>Overview!O2</f>
+        <v>1.5</v>
+      </c>
+      <c r="P7" s="14">
+        <f>Overview!P2</f>
+        <v>86.46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="16">
+        <f>Overview!B7</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="16">
+        <f>Overview!C7</f>
+        <v>1.75</v>
+      </c>
+      <c r="D8" s="16">
+        <f>Overview!D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="16">
+        <f>Overview!E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="16">
+        <f>Overview!F7</f>
+        <v>1.75</v>
+      </c>
+      <c r="G8" s="16">
+        <f>Overview!G7</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="16">
+        <f>Overview!H7</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="16">
+        <f>Overview!I7</f>
+        <v>1.75</v>
+      </c>
+      <c r="J8" s="16">
+        <f>Overview!J7</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="16">
+        <f>Overview!K7</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="16">
+        <f>Overview!L7</f>
+        <v>1.75</v>
+      </c>
+      <c r="M8" s="16">
+        <f>Overview!M7</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="16">
+        <f>Overview!N7</f>
+        <v>1</v>
+      </c>
+      <c r="O8" s="16">
+        <f>Overview!O7</f>
+        <v>7</v>
+      </c>
+      <c r="P8" s="14">
+        <f>Overview!P7</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B9" s="16">
         <f>Overview!B5</f>
         <v>0</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C9" s="16">
         <f>Overview!C5</f>
         <v>0</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D9" s="16">
         <f>Overview!D5</f>
         <v>0</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E9" s="16">
         <f>Overview!E5</f>
         <v>0</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F9" s="16">
         <f>Overview!F5</f>
         <v>2</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G9" s="16">
         <f>Overview!G5</f>
         <v>0</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H9" s="16">
         <f>Overview!H5</f>
         <v>0</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I9" s="16">
         <f>Overview!I5</f>
         <v>0</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J9" s="16">
         <f>Overview!J5</f>
         <v>0</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K9" s="16">
         <f>Overview!K5</f>
         <v>0</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L9" s="16">
         <f>Overview!L5</f>
         <v>0</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M9" s="16">
         <f>Overview!M5</f>
         <v>0</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N9" s="16">
         <f>Overview!N5</f>
         <v>1</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O9" s="16">
         <f>Overview!O5</f>
         <v>2</v>
       </c>
-      <c r="P2" s="14">
+      <c r="P9" s="14">
         <f>Overview!P5</f>
         <v>26.46</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B10" s="18">
         <f>Overview!B10</f>
         <v>0</v>
       </c>
-      <c r="C3" s="18">
+      <c r="C10" s="18">
         <f>Overview!C10</f>
         <v>0</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D10" s="18">
         <f>Overview!D10</f>
         <v>0</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E10" s="18">
         <f>Overview!E10</f>
         <v>0</v>
       </c>
-      <c r="F3" s="18">
+      <c r="F10" s="18">
         <f>Overview!F10</f>
         <v>2.25</v>
       </c>
-      <c r="G3" s="18">
+      <c r="G10" s="18">
         <f>Overview!G10</f>
         <v>0</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H10" s="18">
         <f>Overview!H10</f>
         <v>0</v>
       </c>
-      <c r="I3" s="18">
+      <c r="I10" s="18">
         <f>Overview!I10</f>
         <v>0</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J10" s="18">
         <f>Overview!J10</f>
         <v>0</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K10" s="18">
         <f>Overview!K10</f>
         <v>0</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L10" s="18">
         <f>Overview!L10</f>
         <v>0</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M10" s="18">
         <f>Overview!M10</f>
         <v>0</v>
       </c>
-      <c r="N3" s="18">
+      <c r="N10" s="18">
         <f>Overview!N10</f>
         <v>1</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O10" s="18">
         <f>Overview!O10</f>
         <v>2.25</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P10" s="14">
         <f>Overview!P10</f>
         <v>172.3</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B11" s="16">
         <f>Overview!B9</f>
         <v>5</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C11" s="16">
         <f>Overview!C9</f>
         <v>0</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D11" s="16">
         <f>Overview!D9</f>
         <v>0</v>
       </c>
-      <c r="E4" s="16">
+      <c r="E11" s="16">
         <f>Overview!E9</f>
         <v>5</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F11" s="16">
         <f>Overview!F9</f>
         <v>0</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G11" s="16">
         <f>Overview!G9</f>
         <v>0</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H11" s="16">
         <f>Overview!H9</f>
         <v>5</v>
       </c>
-      <c r="I4" s="16">
+      <c r="I11" s="16">
         <f>Overview!I9</f>
         <v>0</v>
       </c>
-      <c r="J4" s="16">
+      <c r="J11" s="16">
         <f>Overview!J9</f>
         <v>0</v>
       </c>
-      <c r="K4" s="16">
+      <c r="K11" s="16">
         <f>Overview!K9</f>
         <v>5</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L11" s="16">
         <f>Overview!L9</f>
         <v>0</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M11" s="16">
         <f>Overview!M9</f>
         <v>0</v>
       </c>
-      <c r="N4" s="16">
+      <c r="N11" s="16">
         <f>Overview!N9</f>
         <v>1</v>
       </c>
-      <c r="O4" s="16">
+      <c r="O11" s="16">
         <f>Overview!O9</f>
         <v>20</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P11" s="13">
         <f>Overview!P9</f>
         <v>301.3</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B12" s="18">
         <f>Overview!B4</f>
         <v>0</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C12" s="18">
         <f>Overview!C4</f>
         <v>0</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D12" s="18">
         <f>Overview!D4</f>
         <v>0</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E12" s="18">
         <f>Overview!E4</f>
         <v>0</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F12" s="18">
         <f>Overview!F4</f>
         <v>8</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G12" s="18">
         <f>Overview!G4</f>
         <v>0</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H12" s="18">
         <f>Overview!H4</f>
         <v>0</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I12" s="18">
         <f>Overview!I4</f>
         <v>0</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J12" s="18">
         <f>Overview!J4</f>
         <v>0</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K12" s="18">
         <f>Overview!K4</f>
         <v>0</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L12" s="18">
         <f>Overview!L4</f>
         <v>4</v>
       </c>
-      <c r="M5" s="18">
+      <c r="M12" s="18">
         <f>Overview!M4</f>
         <v>0</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N12" s="18">
         <f>Overview!N4</f>
         <v>1</v>
       </c>
-      <c r="O5" s="18">
+      <c r="O12" s="18">
         <f>Overview!O4</f>
         <v>12</v>
       </c>
-      <c r="P5" s="14">
+      <c r="P12" s="14">
         <f>Overview!P4</f>
         <v>506.2</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B13" s="16">
         <f>Overview!B13</f>
         <v>0</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C13" s="16">
         <f>Overview!C13</f>
         <v>0</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D13" s="16">
         <f>Overview!D13</f>
         <v>0</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E13" s="16">
         <f>Overview!E13</f>
         <v>0</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F13" s="16">
         <f>Overview!F13</f>
         <v>0</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G13" s="16">
         <f>Overview!G13</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="H6" s="16">
+      <c r="H13" s="16">
         <f>Overview!H13</f>
         <v>0</v>
       </c>
-      <c r="I6" s="16">
+      <c r="I13" s="16">
         <f>Overview!I13</f>
         <v>0</v>
       </c>
-      <c r="J6" s="16">
+      <c r="J13" s="16">
         <f>Overview!J13</f>
         <v>0</v>
       </c>
-      <c r="K6" s="16">
+      <c r="K13" s="16">
         <f>Overview!K13</f>
         <v>0</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L13" s="16">
         <f>Overview!L13</f>
         <v>0</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M13" s="16">
         <f>Overview!M13</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N13" s="16">
         <f>Overview!N13</f>
         <v>1</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O13" s="16">
         <f>Overview!O13</f>
         <v>2.2000000000000002</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P13" s="14">
         <f>Overview!P13</f>
         <v>184.4</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B14" s="16">
         <f>Overview!B15</f>
         <v>0</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C14" s="16">
         <f>Overview!C15</f>
         <v>0</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D14" s="16">
         <f>Overview!D15</f>
         <v>3.25</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E14" s="16">
         <f>Overview!E15</f>
         <v>0</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F14" s="16">
         <f>Overview!F15</f>
         <v>0</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G14" s="16">
         <f>Overview!G15</f>
         <v>0</v>
       </c>
-      <c r="H7" s="16">
+      <c r="H14" s="16">
         <f>Overview!H15</f>
         <v>0</v>
       </c>
-      <c r="I7" s="16">
+      <c r="I14" s="16">
         <f>Overview!I15</f>
         <v>0</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J14" s="16">
         <f>Overview!J15</f>
         <v>3.25</v>
       </c>
-      <c r="K7" s="16">
+      <c r="K14" s="16">
         <f>Overview!K15</f>
         <v>0</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L14" s="16">
         <f>Overview!L15</f>
         <v>0</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M14" s="16">
         <f>Overview!M15</f>
         <v>0</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N14" s="16">
         <f>Overview!N15</f>
         <v>0</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O14" s="16">
         <f>Overview!O15</f>
         <v>0</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P14" s="14">
         <f>Overview!P15</f>
         <v>176.2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B15" s="18">
         <f>Overview!B16</f>
         <v>0</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C15" s="18">
         <f>Overview!C16</f>
         <v>0</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D15" s="18">
         <f>Overview!D16</f>
         <v>3.5</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E15" s="18">
         <f>Overview!E16</f>
         <v>0</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F15" s="18">
         <f>Overview!F16</f>
         <v>0</v>
       </c>
-      <c r="G8" s="18">
+      <c r="G15" s="18">
         <f>Overview!G16</f>
         <v>0</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H15" s="18">
         <f>Overview!H16</f>
         <v>0</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I15" s="18">
         <f>Overview!I16</f>
         <v>0</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J15" s="18">
         <f>Overview!J16</f>
         <v>3.5</v>
       </c>
-      <c r="K8" s="18">
+      <c r="K15" s="18">
         <f>Overview!K16</f>
         <v>0</v>
       </c>
-      <c r="L8" s="18">
+      <c r="L15" s="18">
         <f>Overview!L16</f>
         <v>0</v>
       </c>
-      <c r="M8" s="18">
+      <c r="M15" s="18">
         <f>Overview!M16</f>
         <v>0</v>
       </c>
-      <c r="N8" s="18">
+      <c r="N15" s="18">
         <f>Overview!N16</f>
         <v>0</v>
       </c>
-      <c r="O8" s="18">
+      <c r="O15" s="18">
         <f>Overview!O16</f>
         <v>0</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P15" s="14">
         <f>Overview!P16</f>
         <v>201.8</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B16" s="18">
         <f>Overview!B6</f>
         <v>0</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C16" s="18">
         <f>Overview!C6</f>
         <v>0</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D16" s="18">
         <f>Overview!D6</f>
         <v>0</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E16" s="18">
         <f>Overview!E6</f>
         <v>0</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F16" s="18">
         <f>Overview!F6</f>
         <v>4</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G16" s="18">
         <f>Overview!G6</f>
         <v>0</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H16" s="18">
         <f>Overview!H6</f>
         <v>0</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I16" s="18">
         <f>Overview!I6</f>
         <v>0</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J16" s="18">
         <f>Overview!J6</f>
         <v>0</v>
       </c>
-      <c r="K9" s="18">
+      <c r="K16" s="18">
         <f>Overview!K6</f>
         <v>0</v>
       </c>
-      <c r="L9" s="18">
+      <c r="L16" s="18">
         <f>Overview!L6</f>
         <v>4</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M16" s="18">
         <f>Overview!M6</f>
         <v>0</v>
       </c>
-      <c r="N9" s="18">
+      <c r="N16" s="18">
         <f>Overview!N6</f>
         <v>1</v>
       </c>
-      <c r="O9" s="18">
+      <c r="O16" s="18">
         <f>Overview!O6</f>
         <v>8</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P16" s="14">
         <f>Overview!P6</f>
         <v>263.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="18">
-        <f>Overview!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="18">
-        <f>Overview!C14</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="18">
-        <f>Overview!D14</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="18">
-        <f>Overview!E14</f>
-        <v>3.15</v>
-      </c>
-      <c r="F10" s="18">
-        <f>Overview!F14</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="18">
-        <f>Overview!G14</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="18">
-        <f>Overview!H14</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
-        <f>Overview!I14</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="18">
-        <f>Overview!J14</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="18">
-        <f>Overview!K14</f>
-        <v>3.15</v>
-      </c>
-      <c r="L10" s="18">
-        <f>Overview!L14</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="18">
-        <f>Overview!M14</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="18">
-        <f>Overview!N14</f>
-        <v>0</v>
-      </c>
-      <c r="O10" s="18">
-        <f>Overview!O14</f>
-        <v>0</v>
-      </c>
-      <c r="P10" s="14">
-        <f>Overview!P14</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="16">
-        <f>Overview!B11</f>
-        <v>0</v>
-      </c>
-      <c r="C11" s="16">
-        <f>Overview!C11</f>
-        <v>5.5</v>
-      </c>
-      <c r="D11" s="16">
-        <f>Overview!D11</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="16">
-        <f>Overview!E11</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="16">
-        <f>Overview!F11</f>
-        <v>5.5</v>
-      </c>
-      <c r="G11" s="16">
-        <f>Overview!G11</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="16">
-        <f>Overview!H11</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="16">
-        <f>Overview!I11</f>
-        <v>5.5</v>
-      </c>
-      <c r="J11" s="16">
-        <f>Overview!J11</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="16">
-        <f>Overview!K11</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="16">
-        <f>Overview!L11</f>
-        <v>5.5</v>
-      </c>
-      <c r="M11" s="16">
-        <f>Overview!M11</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="16">
-        <f>Overview!N11</f>
-        <v>1</v>
-      </c>
-      <c r="O11" s="16">
-        <f>Overview!O11</f>
-        <v>22</v>
-      </c>
-      <c r="P11" s="14">
-        <f>Overview!P11</f>
-        <v>595</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="16">
-        <f>Overview!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="16">
-        <f>Overview!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="16">
-        <f>Overview!D17</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="16">
-        <f>Overview!E17</f>
-        <v>14</v>
-      </c>
-      <c r="F12" s="16">
-        <f>Overview!F17</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="16">
-        <f>Overview!G17</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="16">
-        <f>Overview!H17</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="16">
-        <f>Overview!I17</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="16">
-        <f>Overview!J17</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="16">
-        <f>Overview!K17</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="16">
-        <f>Overview!L17</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="16">
-        <f>Overview!M17</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="16">
-        <f>Overview!N17</f>
-        <v>1</v>
-      </c>
-      <c r="O12" s="16">
-        <f>Overview!O17</f>
-        <v>14</v>
-      </c>
-      <c r="P12" s="14">
-        <f>Overview!P17</f>
-        <v>133.38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="16">
-        <f>Overview!B3</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="16">
-        <f>Overview!C3</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="16">
-        <f>Overview!D3</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <f>Overview!E3</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
-        <f>Overview!F3</f>
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="G13" s="16">
-        <f>Overview!G3</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="16">
-        <f>Overview!H3</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="16">
-        <f>Overview!I3</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="16">
-        <f>Overview!J3</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="16">
-        <f>Overview!K3</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="16">
-        <f>Overview!L3</f>
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="M13" s="16">
-        <f>Overview!M3</f>
-        <v>0</v>
-      </c>
-      <c r="N13" s="16">
-        <f>Overview!N3</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="16">
-        <f>Overview!O3</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="P13" s="14">
-        <f>Overview!P3</f>
-        <v>137.65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="18">
-        <f>Overview!B18</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="18">
-        <f>Overview!C18</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="18">
-        <f>Overview!D18</f>
-        <v>18</v>
-      </c>
-      <c r="E14" s="18">
-        <f>Overview!E18</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="18">
-        <f>Overview!F18</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="18">
-        <f>Overview!G18</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="18">
-        <f>Overview!H18</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="18">
-        <f>Overview!I18</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="18">
-        <f>Overview!J18</f>
-        <v>8.5</v>
-      </c>
-      <c r="K14" s="18">
-        <f>Overview!K18</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="18">
-        <f>Overview!L18</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="18">
-        <f>Overview!M18</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="18">
-        <f>Overview!N18</f>
-        <v>1</v>
-      </c>
-      <c r="O14" s="18">
-        <f>Overview!O18</f>
-        <v>26.5</v>
-      </c>
-      <c r="P14" s="14">
-        <f>Overview!P18</f>
-        <v>991.4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="18">
-        <f>Overview!B8</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="18">
-        <f>Overview!C8</f>
-        <v>6</v>
-      </c>
-      <c r="D15" s="18">
-        <f>Overview!D8</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="18">
-        <f>Overview!E8</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="18">
-        <f>Overview!F8</f>
-        <v>6</v>
-      </c>
-      <c r="G15" s="18">
-        <f>Overview!G8</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="18">
-        <f>Overview!H8</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <f>Overview!I8</f>
-        <v>6</v>
-      </c>
-      <c r="J15" s="18">
-        <f>Overview!J8</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="18">
-        <f>Overview!K8</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <f>Overview!L8</f>
-        <v>6</v>
-      </c>
-      <c r="M15" s="18">
-        <f>Overview!M8</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <f>Overview!N8</f>
-        <v>1</v>
-      </c>
-      <c r="O15" s="18">
-        <f>Overview!O8</f>
-        <v>24</v>
-      </c>
-      <c r="P15" s="13">
-        <f>Overview!P8</f>
-        <v>305.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="18">
-        <f>Overview!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="18">
-        <f>Overview!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="18">
-        <f>Overview!D12</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="18">
-        <f>Overview!E12</f>
-        <v>4</v>
-      </c>
-      <c r="F16" s="18">
-        <f>Overview!F12</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="18">
-        <f>Overview!G12</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="18">
-        <f>Overview!H12</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="18">
-        <f>Overview!I12</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="18">
-        <f>Overview!J12</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="18">
-        <f>Overview!K12</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="18">
-        <f>Overview!L12</f>
-        <v>4</v>
-      </c>
-      <c r="M16" s="18">
-        <f>Overview!M12</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="18">
-        <f>Overview!N12</f>
-        <v>1</v>
-      </c>
-      <c r="O16" s="18">
-        <f>Overview!O12</f>
-        <v>8</v>
-      </c>
-      <c r="P16" s="14">
-        <f>Overview!P12</f>
-        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B17" s="18">
-        <f>Overview!B2</f>
+        <f>Overview!B14</f>
         <v>0</v>
       </c>
       <c r="C17" s="18">
-        <f>Overview!C2</f>
+        <f>Overview!C14</f>
         <v>0</v>
       </c>
       <c r="D17" s="18">
-        <f>Overview!D2</f>
+        <f>Overview!D14</f>
         <v>0</v>
       </c>
       <c r="E17" s="18">
-        <f>Overview!E2</f>
-        <v>0.75</v>
+        <f>Overview!E14</f>
+        <v>3.15</v>
       </c>
       <c r="F17" s="18">
-        <f>Overview!F2</f>
+        <f>Overview!F14</f>
         <v>0</v>
       </c>
       <c r="G17" s="18">
-        <f>Overview!G2</f>
+        <f>Overview!G14</f>
         <v>0</v>
       </c>
       <c r="H17" s="18">
-        <f>Overview!H2</f>
+        <f>Overview!H14</f>
         <v>0</v>
       </c>
       <c r="I17" s="18">
-        <f>Overview!I2</f>
+        <f>Overview!I14</f>
         <v>0</v>
       </c>
       <c r="J17" s="18">
-        <f>Overview!J2</f>
+        <f>Overview!J14</f>
         <v>0</v>
       </c>
       <c r="K17" s="18">
-        <f>Overview!K2</f>
-        <v>0.75</v>
+        <f>Overview!K14</f>
+        <v>3.15</v>
       </c>
       <c r="L17" s="18">
-        <f>Overview!L2</f>
+        <f>Overview!L14</f>
         <v>0</v>
       </c>
       <c r="M17" s="18">
-        <f>Overview!M2</f>
+        <f>Overview!M14</f>
         <v>0</v>
       </c>
       <c r="N17" s="18">
-        <f>Overview!N2</f>
-        <v>1</v>
+        <f>Overview!N14</f>
+        <v>0</v>
       </c>
       <c r="O17" s="18">
-        <f>Overview!O2</f>
-        <v>1.5</v>
+        <f>Overview!O14</f>
+        <v>0</v>
       </c>
       <c r="P17" s="14">
-        <f>Overview!P2</f>
-        <v>86.46</v>
+        <f>Overview!P14</f>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B18" s="16">
-        <f>Overview!B7</f>
+        <f>Overview!B11</f>
         <v>0</v>
       </c>
       <c r="C18" s="16">
-        <f>Overview!C7</f>
-        <v>1.75</v>
+        <f>Overview!C11</f>
+        <v>5.5</v>
       </c>
       <c r="D18" s="16">
-        <f>Overview!D7</f>
+        <f>Overview!D11</f>
         <v>0</v>
       </c>
       <c r="E18" s="16">
-        <f>Overview!E7</f>
+        <f>Overview!E11</f>
         <v>0</v>
       </c>
       <c r="F18" s="16">
-        <f>Overview!F7</f>
-        <v>1.75</v>
+        <f>Overview!F11</f>
+        <v>5.5</v>
       </c>
       <c r="G18" s="16">
-        <f>Overview!G7</f>
+        <f>Overview!G11</f>
         <v>0</v>
       </c>
       <c r="H18" s="16">
-        <f>Overview!H7</f>
+        <f>Overview!H11</f>
         <v>0</v>
       </c>
       <c r="I18" s="16">
-        <f>Overview!I7</f>
-        <v>1.75</v>
+        <f>Overview!I11</f>
+        <v>5.5</v>
       </c>
       <c r="J18" s="16">
-        <f>Overview!J7</f>
+        <f>Overview!J11</f>
         <v>0</v>
       </c>
       <c r="K18" s="16">
-        <f>Overview!K7</f>
+        <f>Overview!K11</f>
         <v>0</v>
       </c>
       <c r="L18" s="16">
-        <f>Overview!L7</f>
-        <v>1.75</v>
+        <f>Overview!L11</f>
+        <v>5.5</v>
       </c>
       <c r="M18" s="16">
-        <f>Overview!M7</f>
+        <f>Overview!M11</f>
         <v>0</v>
       </c>
       <c r="N18" s="16">
-        <f>Overview!N7</f>
+        <f>Overview!N11</f>
         <v>1</v>
       </c>
       <c r="O18" s="16">
-        <f>Overview!O7</f>
-        <v>7</v>
+        <f>Overview!O11</f>
+        <v>22</v>
       </c>
       <c r="P18" s="14">
-        <f>Overview!P7</f>
-        <v>80</v>
+        <f>Overview!P11</f>
+        <v>595</v>
       </c>
     </row>
   </sheetData>

--- a/Aktie_Utdelning.xlsx
+++ b/Aktie_Utdelning.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0235C184-E258-4F2E-9511-54714FD644A3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC3F2A8-FA06-4142-88E2-FA384C51E867}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Python" sheetId="2" r:id="rId2"/>
-    <sheet name="Blad1" sheetId="3" r:id="rId3"/>
+    <sheet name="Python2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -85,13 +85,6 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="31"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="34"/>
         </ext>
       </extLst>
@@ -99,7 +92,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="40"/>
+          <xlrd:rvb i="37"/>
         </ext>
       </extLst>
     </bk>
@@ -134,7 +127,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="61"/>
+          <xlrd:rvb i="58"/>
         </ext>
       </extLst>
     </bk>
@@ -148,7 +141,14 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="70"/>
+          <xlrd:rvb i="71"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="74"/>
         </ext>
       </extLst>
     </bk>
@@ -239,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
   <si>
     <t>Feb</t>
   </si>
@@ -343,7 +343,13 @@
     <t>ASTRAZENECA PLC (XSTO:AZN)</t>
   </si>
   <si>
-    <t>årlig utd.</t>
+    <t>Magic Number</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Klovern AB (XSTO:KLOV B)</t>
   </si>
 </sst>
 </file>
@@ -398,7 +404,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -428,8 +434,26 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -490,6 +514,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color auto="1"/>
@@ -497,7 +536,9 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -510,25 +551,27 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="5">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="4" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -537,12 +580,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="3" applyBorder="1"/>
-    <xf numFmtId="168" fontId="1" fillId="4" borderId="4" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="1" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -555,10 +592,64 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="6" borderId="1" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="6" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="6" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="7" borderId="7" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="6" borderId="4" xfId="5" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="6" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="1" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="7" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="5">
+  <cellStyles count="8">
     <cellStyle name="20 % - Dekorfärg4" xfId="4" builtinId="42"/>
+    <cellStyle name="20 % - Dekorfärg5" xfId="5" builtinId="46"/>
+    <cellStyle name="20 % - Dekorfärg6" xfId="7" builtinId="50"/>
     <cellStyle name="40 % - Dekorfärg3" xfId="2" builtinId="39"/>
+    <cellStyle name="40 % - Dekorfärg5" xfId="6" builtinId="47"/>
     <cellStyle name="60 % - Dekorfärg3" xfId="3" builtinId="40"/>
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1546,13 +1637,13 @@
                   <c:v>Investor AB (XSTO:INVE B)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Ratos AB (XSTO:RATO B)</c:v>
+                  <c:v>AUTOLIV, INC. (XSTO:ALIV SDB)</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Kinnevik AB (XSTO:KINV B)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</c:v>
+                  <c:v>Atlas Copco AB (XSTO:ATCO B)</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</c:v>
@@ -1561,28 +1652,28 @@
                   <c:v>AT&amp;T INC. (XNYS:T)</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>EQT AB (XSTO:EQT)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>NCC AB (XSTO:NCC B)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Castellum AB (XSTO:CAST)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Axfood AB (XSTO:AXFO)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Swedbank AB (XSTO:SWED A)</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>Investment AB Latour (XSTO:LATO B)</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>AUTOLIV, INC. (XSTO:ALIV SDB)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>NCC AB (XSTO:NCC B)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>EQT AB (XSTO:EQT)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Atlas Copco AB (XSTO:ATCO B)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Castellum AB (XSTO:CAST)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Axfood AB (XSTO:AXFO)</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>Swedbank AB (XSTO:SWED A)</c:v>
+                  <c:v>Ratos AB (XSTO:RATO B)</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>ASTRAZENECA PLC (XSTO:AZN)</c:v>
@@ -1609,13 +1700,13 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>24</c:v>
@@ -1624,28 +1715,28 @@
                   <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.25</c:v>
+                  <c:v>2.2000000000000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>22</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>8</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>2.2000000000000002</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>2.25</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>14</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>26.5</c:v>
@@ -2403,13 +2494,13 @@
                   <c:v>Investor AB (XSTO:INVE B)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Ratos AB (XSTO:RATO B)</c:v>
+                  <c:v>AUTOLIV, INC. (XSTO:ALIV SDB)</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Kinnevik AB (XSTO:KINV B)</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</c:v>
+                  <c:v>Atlas Copco AB (XSTO:ATCO B)</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</c:v>
@@ -2418,28 +2509,28 @@
                   <c:v>AT&amp;T INC. (XNYS:T)</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>EQT AB (XSTO:EQT)</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>NCC AB (XSTO:NCC B)</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Castellum AB (XSTO:CAST)</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Axfood AB (XSTO:AXFO)</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Swedbank AB (XSTO:SWED A)</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>Investment AB Latour (XSTO:LATO B)</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>AUTOLIV, INC. (XSTO:ALIV SDB)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>NCC AB (XSTO:NCC B)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>EQT AB (XSTO:EQT)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Atlas Copco AB (XSTO:ATCO B)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Castellum AB (XSTO:CAST)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Axfood AB (XSTO:AXFO)</c:v>
-                </c:pt>
                 <c:pt idx="15">
-                  <c:v>Swedbank AB (XSTO:SWED A)</c:v>
+                  <c:v>Ratos AB (XSTO:RATO B)</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>ASTRAZENECA PLC (XSTO:AZN)</c:v>
@@ -2472,7 +2563,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -2490,16 +2581,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>1</c:v>
@@ -4312,54 +4403,55 @@
     <v>17</v>
   </rv>
   <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=amx5rw&amp;q=XSTO%3aRATO+B&amp;form=skydnc</v>
+    <v>https://www.bing.com/financeapi/forcetrigger?t=amw4m7&amp;q=XSTO%3aALIV+SDB&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
   <rv s="6">
     <v>en-US</v>
-    <v>amx5rw</v>
+    <v>amw4m7</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
     <v>9</v>
-    <v>Ratos AB (XSTO:RATO B)</v>
+    <v>AUTOLIV, INC. (XSTO:ALIV SDB)</v>
     <v>10</v>
     <v>11</v>
     <v>Finance</v>
     <v>5</v>
-    <v>37.72</v>
-    <v>16.43</v>
-    <v>1.2246999999999999</v>
-    <v>0.46</v>
+    <v>837.8</v>
+    <v>390</v>
+    <v>1.2009000000000001</v>
+    <v>9</v>
     <v>0</v>
-    <v>1.7384999999999998E-2</v>
+    <v>1.5125999999999999E-2</v>
     <v>0</v>
     <v>SEK</v>
-    <v>Ratos AB is a Sweden-based private equity company. It owns and develops over 10 unlisted medium-sized enterprises in Nordic region. Enterprises are active in various sectors, such as industry, consumer goods, services and life science, among others. The Company’s portfolio comprises Aibel, the supplier of maintenance and modification services for production platforms and onshore installations within oil and gas industry; Bisnode, the data and analytics company; HENT, the construction company with focus on public and commercial real estate; Plantasjen, the chain for sales of plants and gardening accessories; HL Display, the supplier of products and solutions for in-store communication and merchandising; and Diab, the manufacturer of materials for sandwich composite structures, among others enterprises.</v>
-    <v>8527</v>
+    <v>Autoliv, Inc. is a supplier of automotive safety systems with a range of product offerings, including passive safety systems and active safety systems. The Company operates through its Passive Safety segment. The Passive safety products include modules and components for passenger and driver-side airbags, side-impact airbag protection systems, seatbelts, steering wheels, inflator technologies, whiplash protection systems and child seats, and components for such systems, as well as passive safety electronic products, such as restraint electronics and crash sensors. The Active safety products include camera-based vision systems, night driving assist, automotive radars, brake controls, positioning systems, electronic control units, and other active safety systems. As of December 31, 2016, including joint venture operations, the Company had approximately 78 production facilities in 25 countries, consisting of both component factories and assembly factories.</v>
+    <v>65500</v>
     <v>NASDAQ Stockholm</v>
     <v>XSTO</v>
     <v>XSTO</v>
-    <v>Drottninggatan 2, STOCKHOLM, STOCKHOLM, 111 51 SE</v>
-    <v>26.92</v>
-    <v>Investment Banking &amp; Investment Services</v>
+    <v>Section B7, Klarabergsviadukten 70, STOCKHOLM, STOCKHOLM, 111 64 SE</v>
+    <v>613.6</v>
+    <v>Automobiles &amp; Auto Parts</v>
     <v>Stock</v>
     <v>44025.666666666664</v>
     <v>19</v>
-    <v>26.38</v>
-    <v>8715573000</v>
-    <v>Ratos AB</v>
-    <v>Ratos AB</v>
-    <v>26.5</v>
-    <v>71.510000000000005</v>
-    <v>26.46</v>
-    <v>26.92</v>
-    <v>26.92</v>
-    <v>324140900</v>
-    <v>RATO B</v>
-    <v>Ratos AB (XSTO:RATO B)</v>
-    <v>437940</v>
+    <v>600.20000000000005</v>
+    <v>52552960000</v>
+    <v>AUTOLIV, INC.</v>
+    <v>AUTOLIV, INC.</v>
+    <v>603</v>
+    <v>10.62</v>
+    <v>595</v>
+    <v>604</v>
+    <v>604</v>
+    <v>87331790</v>
+    <v>ALIV SDB</v>
+    <v>AUTOLIV, INC. (XSTO:ALIV SDB)</v>
+    <v>306862</v>
+    <v>1996</v>
   </rv>
   <rv s="4">
     <v>20</v>
@@ -4440,70 +4532,93 @@
     <v>27</v>
   </rv>
   <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=bho627&amp;q=XSTO%3aVASLOG&amp;form=skydnc</v>
+    <v>http://en.wikipedia.org/wiki/Atlas_Copco</v>
+    <v>Wikipedia</v>
+  </rv>
+  <rv s="1">
+    <v>0</v>
+    <v>29</v>
+  </rv>
+  <rv s="2">
+    <v>Powered by Refinitiv</v>
+    <v>6</v>
+    <v>https://www.bing.com/th?id=AMMS_f691da07efc984db49409ee18e3268d9&amp;qlt=95</v>
+    <v>30</v>
+    <v>https://www.bing.com/images/search?form=xlimg&amp;q=atlas+copco</v>
+    <v>Image of Atlas Copco AB</v>
+    <v/>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=amw6f2&amp;q=XSTO%3aATCO+B&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="3">
     <v>en-US</v>
-    <v>bho627</v>
+    <v>amw6f2</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>12</v>
-    <v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</v>
-    <v>10</v>
-    <v>13</v>
+    <v>0</v>
+    <v>Atlas Copco AB (XSTO:ATCO B)</v>
+    <v>3</v>
+    <v>4</v>
     <v>Finance</v>
-    <v>14</v>
-    <v>107</v>
-    <v>58</v>
-    <v>0.5</v>
-    <v>6.2500000000000003E-3</v>
+    <v>5</v>
+    <v>365.3</v>
+    <v>187.68</v>
+    <v>1.1702999999999999</v>
+    <v>5.3</v>
+    <v>0</v>
+    <v>1.4763E-2</v>
+    <v>0</v>
     <v>SEK</v>
-    <v>Vastsvensk Logistik AB (publ) is a Sweden-based company engaged in the real estate sector. The Company owns, manages and leases a non-residential property in Molndal, Sweden. The Company’s asset consists of logistics building and office building.</v>
+    <v>Atlas Copco AB is a Sweden-based holding company. The Company is a provider of various productivity solutions. It serves customers with compressors, vacuum solutions and air treatment systems, power tools and assembly systems, pumps and generators. The Company divides its activities into four segments: Compressor Technique, Vacuum Technique, Industrial Technique, and Power Technique. Compressor Technique provides industrial compressors, vacuum solutions, gas and process compressors and expanders, air and gas treatment equipment and air management systems. Vacuum Technique provides vacuum products, exhaust management systems, valves and related products. Industrial Technique provides industrial power tools and systems, industrial assembly solutions, quality assurance products, software and service. Power Technique provides air, power and flow solutions through products such as mobile compressors, pumps, light towers and generators.</v>
+    <v>39611</v>
     <v>NASDAQ Stockholm</v>
     <v>XSTO</v>
     <v>XSTO</v>
-    <v>c/o Hestia Fastighetsforvaltning AB, Box 239, VASTERAS, VASTMANLAND, 721 06 SE</v>
-    <v>80.5</v>
-    <v>Real Estate Operations</v>
+    <v>Sickla Industrivag 19, NACKA, STOCKHOLM, 105 23 SE</v>
+    <v>365.5</v>
+    <v>31</v>
+    <v>Machinery, Equipment &amp; Components</v>
     <v>Stock</v>
     <v>44025.666666666664</v>
-    <v>29</v>
-    <v>73</v>
-    <v>196000000</v>
-    <v>Vastsvensk Logistik AB (publ)</v>
-    <v>Vastsvensk Logistik AB (publ)</v>
-    <v>78</v>
-    <v>80</v>
-    <v>80.5</v>
-    <v>80.5</v>
-    <v>2450000</v>
-    <v>VASLOG</v>
-    <v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</v>
-    <v>736</v>
+    <v>32</v>
+    <v>358.5</v>
+    <v>482393500000</v>
+    <v>Atlas Copco AB</v>
+    <v>Atlas Copco AB</v>
+    <v>363.1</v>
+    <v>8.3800000000000008</v>
+    <v>359</v>
+    <v>364.3</v>
+    <v>364.3</v>
+    <v>1229613000</v>
+    <v>ATCO B</v>
+    <v>Atlas Copco AB (XSTO:ATCO B)</v>
+    <v>308133</v>
   </rv>
   <rv s="4">
-    <v>30</v>
+    <v>33</v>
   </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1z5cw&amp;q=XNYS%3aOHI&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="8">
+  <rv s="7">
     <v>en-US</v>
     <v>a1z5cw</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>12</v>
     <v>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</v>
     <v>10</v>
-    <v>16</v>
+    <v>13</v>
     <v>Finance</v>
-    <v>17</v>
+    <v>14</v>
     <v>45.22</v>
     <v>13.33</v>
     <v>0.83640000000000003</v>
@@ -4520,7 +4635,7 @@
     <v>Residential &amp; Commercial REIT</v>
     <v>Stock</v>
     <v>44025.748287037037</v>
-    <v>32</v>
+    <v>35</v>
     <v>30.02</v>
     <v>6936385000</v>
     <v>OMEGA HEALTHCARE INVESTORS, INC.</v>
@@ -4537,7 +4652,7 @@
     <v>1992</v>
   </rv>
   <rv s="4">
-    <v>33</v>
+    <v>36</v>
   </rv>
   <rv s="0">
     <v>http://tr.wikipedia.org/wiki/AT&amp;T</v>
@@ -4545,13 +4660,13 @@
   </rv>
   <rv s="1">
     <v>0</v>
-    <v>35</v>
+    <v>38</v>
   </rv>
   <rv s="2">
     <v>Powered by Refinitiv</v>
     <v>6</v>
     <v>https://www.bing.com/th?id=AMMS_22edc37b3d4ca713a66f23973844e621&amp;qlt=95</v>
-    <v>36</v>
+    <v>39</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=at%26t</v>
     <v>Image of AT&amp;T INC.</v>
     <v/>
@@ -4560,19 +4675,19 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=a23www&amp;q=XNYS%3aT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="9">
+  <rv s="8">
     <v>en-US</v>
     <v>a23www</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>18</v>
+    <v>15</v>
     <v>AT&amp;T INC. (XNYS:T)</v>
     <v>3</v>
-    <v>19</v>
+    <v>16</v>
     <v>Finance</v>
-    <v>17</v>
+    <v>14</v>
     <v>39.700000000000003</v>
     <v>26.08</v>
     <v>0.67849999999999999</v>
@@ -4586,11 +4701,11 @@
     <v>XNYS</v>
     <v>208 S Akard St, DALLAS, TX, 75202-4206 US</v>
     <v>30.17</v>
-    <v>37</v>
+    <v>40</v>
     <v>Telecommunications Services</v>
     <v>Stock</v>
     <v>44025.749424062502</v>
-    <v>38</v>
+    <v>41</v>
     <v>29.72</v>
     <v>214676300000</v>
     <v>AT&amp;T INC.</v>
@@ -4607,111 +4722,54 @@
     <v>1983</v>
   </rv>
   <rv s="4">
-    <v>39</v>
+    <v>42</v>
   </rv>
   <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=amwtcw&amp;q=XSTO%3aLATO+B&amp;form=skydnc</v>
+    <v>https://www.bing.com/financeapi/forcetrigger?t=brkdoc&amp;q=XSTO%3aEQT&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="9">
     <v>en-US</v>
-    <v>amwtcw</v>
+    <v>brkdoc</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>9</v>
-    <v>Investment AB Latour (XSTO:LATO B)</v>
+    <v>17</v>
+    <v>EQT AB (XSTO:EQT)</v>
     <v>10</v>
-    <v>11</v>
+    <v>18</v>
     <v>Finance</v>
     <v>5</v>
-    <v>183.8</v>
-    <v>103.9</v>
-    <v>0.7621</v>
-    <v>3.2</v>
+    <v>4.0999999999999996</v>
     <v>0</v>
-    <v>1.8571999999999998E-2</v>
+    <v>2.2233999999999997E-2</v>
     <v>0</v>
     <v>SEK</v>
-    <v>Investment AB Latour is a Sweden-based company. Its operations are divided into two business lines. One is made up of the wholly owned industrial and trading operations and the other is a portfolio with listed holdings. Its industrial and trading operations are organized into four business areas: Hultafors Group, Latour Industries, Specma Group and Swegon. The Company's investment portfolio comprises Assa Abloy, Fagerhult, HMS Networks, Loomis, Nederman, Nobia, Securitas, Sweco and Tomra. The Company’s operations are run by its two wholly owned subsidiaries, Nordiska Industri AB and Latour-Gruppen AB, trading with shares and securities is handled by the Karpalunds Angbryggeri AB, while administration of securities is managed by the wholly owned subsidiary, Saki Forvaltning AB.</v>
-    <v>6039</v>
+    <v>EQT AB is a Sweden-based differentiated global investment company. It manages and advises a range of specialized investment funds and other investment vehicles that invest across the world. The Company has three business segments: Private Capital, Real Assets and Credit. The Private Capital business segment invests in medium-sized to large companies in Europe and the United States, China and Southeast Asia, technology-driven companies across all industries and public companies. The Real Assets business segment invests in infrastructure and real estate businesses. The Credit segments offers an investment platform.</v>
+    <v>706</v>
     <v>NASDAQ Stockholm</v>
     <v>XSTO</v>
     <v>XSTO</v>
-    <v>J A Wettergrens Gata 7, Box 336, GOETEBORG, VASTRA GOTALANDS, 401 25 SE</v>
-    <v>175.5</v>
-    <v>Industrial Conglomerates</v>
-    <v>Stock</v>
-    <v>44025.666666666664</v>
-    <v>41</v>
-    <v>172.1</v>
-    <v>102035700000</v>
-    <v>Investment AB Latour</v>
-    <v>Investment AB Latour</v>
-    <v>173.8</v>
-    <v>30.34</v>
-    <v>172.3</v>
-    <v>175.5</v>
-    <v>175.5</v>
-    <v>592197800</v>
-    <v>LATO B</v>
-    <v>Investment AB Latour (XSTO:LATO B)</v>
-    <v>228496</v>
-  </rv>
-  <rv s="4">
-    <v>42</v>
-  </rv>
-  <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=amw4m7&amp;q=XSTO%3aALIV+SDB&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="10">
-    <v>en-US</v>
-    <v>amw4m7</v>
-    <v>268435456</v>
-    <v>268435457</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>20</v>
-    <v>AUTOLIV, INC. (XSTO:ALIV SDB)</v>
-    <v>10</v>
-    <v>21</v>
-    <v>Finance</v>
-    <v>5</v>
-    <v>837.8</v>
-    <v>390</v>
-    <v>1.2009000000000001</v>
-    <v>9</v>
-    <v>0</v>
-    <v>1.5125999999999999E-2</v>
-    <v>0</v>
-    <v>SEK</v>
-    <v>Autoliv, Inc. is a supplier of automotive safety systems with a range of product offerings, including passive safety systems and active safety systems. The Company operates through its Passive Safety segment. The Passive safety products include modules and components for passenger and driver-side airbags, side-impact airbag protection systems, seatbelts, steering wheels, inflator technologies, whiplash protection systems and child seats, and components for such systems, as well as passive safety electronic products, such as restraint electronics and crash sensors. The Active safety products include camera-based vision systems, night driving assist, automotive radars, brake controls, positioning systems, electronic control units, and other active safety systems. As of December 31, 2016, including joint venture operations, the Company had approximately 78 production facilities in 25 countries, consisting of both component factories and assembly factories.</v>
-    <v>65500</v>
-    <v>NASDAQ Stockholm</v>
-    <v>XSTO</v>
-    <v>XSTO</v>
-    <v>Section B7, Klarabergsviadukten 70, STOCKHOLM, STOCKHOLM, 111 64 SE</v>
-    <v>613.6</v>
-    <v>Automobiles &amp; Auto Parts</v>
+    <v>Regeringsgatan 25, STOCKHOLM, STOCKHOLM, 111 53 SE</v>
+    <v>188.9</v>
+    <v>Investment Banking &amp; Investment Services</v>
     <v>Stock</v>
     <v>44025.666666666664</v>
     <v>44</v>
-    <v>600.20000000000005</v>
-    <v>52552960000</v>
-    <v>AUTOLIV, INC.</v>
-    <v>AUTOLIV, INC.</v>
-    <v>603</v>
-    <v>10.62</v>
-    <v>595</v>
-    <v>604</v>
-    <v>604</v>
-    <v>87331790</v>
-    <v>ALIV SDB</v>
-    <v>AUTOLIV, INC. (XSTO:ALIV SDB)</v>
-    <v>306862</v>
-    <v>1996</v>
+    <v>183.2</v>
+    <v>175014600000</v>
+    <v>EQT AB</v>
+    <v>EQT AB</v>
+    <v>186</v>
+    <v>94.02</v>
+    <v>184.4</v>
+    <v>188.5</v>
+    <v>188.5</v>
+    <v>952983900</v>
+    <v>EQT</v>
+    <v>EQT AB (XSTO:EQT)</v>
+    <v>600826</v>
   </rv>
   <rv s="4">
     <v>45</v>
@@ -4788,141 +4846,68 @@
     <v>51</v>
   </rv>
   <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=brkdoc&amp;q=XSTO%3aEQT&amp;form=skydnc</v>
+    <v>https://www.bing.com/financeapi/forcetrigger?t=bho627&amp;q=XSTO%3aVASLOG&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="11">
+  <rv s="10">
     <v>en-US</v>
-    <v>brkdoc</v>
+    <v>bho627</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
-    <v>EQT AB (XSTO:EQT)</v>
+    <v>19</v>
+    <v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</v>
     <v>10</v>
-    <v>23</v>
+    <v>20</v>
     <v>Finance</v>
-    <v>5</v>
-    <v>4.0999999999999996</v>
-    <v>0</v>
-    <v>2.2233999999999997E-2</v>
-    <v>0</v>
+    <v>21</v>
+    <v>107</v>
+    <v>58</v>
+    <v>0.5</v>
+    <v>6.2500000000000003E-3</v>
     <v>SEK</v>
-    <v>EQT AB is a Sweden-based differentiated global investment company. It manages and advises a range of specialized investment funds and other investment vehicles that invest across the world. The Company has three business segments: Private Capital, Real Assets and Credit. The Private Capital business segment invests in medium-sized to large companies in Europe and the United States, China and Southeast Asia, technology-driven companies across all industries and public companies. The Real Assets business segment invests in infrastructure and real estate businesses. The Credit segments offers an investment platform.</v>
-    <v>706</v>
+    <v>Vastsvensk Logistik AB (publ) is a Sweden-based company engaged in the real estate sector. The Company owns, manages and leases a non-residential property in Molndal, Sweden. The Company’s asset consists of logistics building and office building.</v>
     <v>NASDAQ Stockholm</v>
     <v>XSTO</v>
     <v>XSTO</v>
-    <v>Regeringsgatan 25, STOCKHOLM, STOCKHOLM, 111 53 SE</v>
-    <v>188.9</v>
-    <v>Investment Banking &amp; Investment Services</v>
+    <v>c/o Hestia Fastighetsforvaltning AB, Box 239, VASTERAS, VASTMANLAND, 721 06 SE</v>
+    <v>80.5</v>
+    <v>Real Estate Operations</v>
     <v>Stock</v>
     <v>44025.666666666664</v>
     <v>53</v>
-    <v>183.2</v>
-    <v>175014600000</v>
-    <v>EQT AB</v>
-    <v>EQT AB</v>
-    <v>186</v>
-    <v>94.02</v>
-    <v>184.4</v>
-    <v>188.5</v>
-    <v>188.5</v>
-    <v>952983900</v>
-    <v>EQT</v>
-    <v>EQT AB (XSTO:EQT)</v>
-    <v>600826</v>
+    <v>73</v>
+    <v>196000000</v>
+    <v>Vastsvensk Logistik AB (publ)</v>
+    <v>Vastsvensk Logistik AB (publ)</v>
+    <v>78</v>
+    <v>80</v>
+    <v>80.5</v>
+    <v>80.5</v>
+    <v>2450000</v>
+    <v>VASLOG</v>
+    <v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</v>
+    <v>736</v>
   </rv>
   <rv s="4">
     <v>54</v>
   </rv>
   <rv s="0">
-    <v>http://en.wikipedia.org/wiki/Atlas_Copco</v>
-    <v>Wikipedia</v>
-  </rv>
-  <rv s="1">
-    <v>0</v>
-    <v>56</v>
-  </rv>
-  <rv s="2">
-    <v>Powered by Refinitiv</v>
-    <v>6</v>
-    <v>https://www.bing.com/th?id=AMMS_f691da07efc984db49409ee18e3268d9&amp;qlt=95</v>
-    <v>57</v>
-    <v>https://www.bing.com/images/search?form=xlimg&amp;q=atlas+copco</v>
-    <v>Image of Atlas Copco AB</v>
-    <v/>
-  </rv>
-  <rv s="0">
-    <v>https://www.bing.com/financeapi/forcetrigger?t=amw6f2&amp;q=XSTO%3aATCO+B&amp;form=skydnc</v>
-    <v>Learn more on Bing</v>
-  </rv>
-  <rv s="3">
-    <v>en-US</v>
-    <v>amw6f2</v>
-    <v>268435456</v>
-    <v>268435457</v>
-    <v>1</v>
-    <v>Powered by Refinitiv</v>
-    <v>0</v>
-    <v>Atlas Copco AB (XSTO:ATCO B)</v>
-    <v>3</v>
-    <v>4</v>
-    <v>Finance</v>
-    <v>5</v>
-    <v>365.3</v>
-    <v>187.68</v>
-    <v>1.1702999999999999</v>
-    <v>5.3</v>
-    <v>0</v>
-    <v>1.4763E-2</v>
-    <v>0</v>
-    <v>SEK</v>
-    <v>Atlas Copco AB is a Sweden-based holding company. The Company is a provider of various productivity solutions. It serves customers with compressors, vacuum solutions and air treatment systems, power tools and assembly systems, pumps and generators. The Company divides its activities into four segments: Compressor Technique, Vacuum Technique, Industrial Technique, and Power Technique. Compressor Technique provides industrial compressors, vacuum solutions, gas and process compressors and expanders, air and gas treatment equipment and air management systems. Vacuum Technique provides vacuum products, exhaust management systems, valves and related products. Industrial Technique provides industrial power tools and systems, industrial assembly solutions, quality assurance products, software and service. Power Technique provides air, power and flow solutions through products such as mobile compressors, pumps, light towers and generators.</v>
-    <v>39611</v>
-    <v>NASDAQ Stockholm</v>
-    <v>XSTO</v>
-    <v>XSTO</v>
-    <v>Sickla Industrivag 19, NACKA, STOCKHOLM, 105 23 SE</v>
-    <v>365.5</v>
-    <v>58</v>
-    <v>Machinery, Equipment &amp; Components</v>
-    <v>Stock</v>
-    <v>44025.666666666664</v>
-    <v>59</v>
-    <v>358.5</v>
-    <v>482393500000</v>
-    <v>Atlas Copco AB</v>
-    <v>Atlas Copco AB</v>
-    <v>363.1</v>
-    <v>8.3800000000000008</v>
-    <v>359</v>
-    <v>364.3</v>
-    <v>364.3</v>
-    <v>1229613000</v>
-    <v>ATCO B</v>
-    <v>Atlas Copco AB (XSTO:ATCO B)</v>
-    <v>308133</v>
-  </rv>
-  <rv s="4">
-    <v>60</v>
-  </rv>
-  <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=amwbpr&amp;q=XSTO%3aCAST&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="11">
     <v>en-US</v>
     <v>amwbpr</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>9</v>
+    <v>22</v>
     <v>Castellum AB (XSTO:CAST)</v>
     <v>10</v>
-    <v>11</v>
+    <v>23</v>
     <v>Finance</v>
     <v>5</v>
     <v>257</v>
@@ -4943,7 +4928,7 @@
     <v>Real Estate Operations</v>
     <v>Stock</v>
     <v>44025.666666666664</v>
-    <v>62</v>
+    <v>56</v>
     <v>175.4</v>
     <v>48138050000</v>
     <v>Castellum AB</v>
@@ -4959,7 +4944,7 @@
     <v>441236</v>
   </rv>
   <rv s="4">
-    <v>63</v>
+    <v>57</v>
   </rv>
   <rv s="0">
     <v>http://en.wikipedia.org/wiki/Axfood</v>
@@ -4967,13 +4952,13 @@
   </rv>
   <rv s="1">
     <v>0</v>
-    <v>65</v>
+    <v>59</v>
   </rv>
   <rv s="2">
     <v>Powered by Refinitiv</v>
     <v>6</v>
     <v>https://www.bing.com/th?id=AMMS_0fc289fa19d264b8292a937ab061bb33&amp;qlt=95</v>
-    <v>66</v>
+    <v>60</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=axfood</v>
     <v>Image of Axfood AB</v>
     <v/>
@@ -5010,11 +4995,11 @@
     <v>XSTO</v>
     <v>Norra stationsgatan 80 C, STOCKHOLM, STOCKHOLM, 107 69 SE</v>
     <v>202.4</v>
-    <v>67</v>
+    <v>61</v>
     <v>Food &amp; Drug Retailing</v>
     <v>Stock</v>
     <v>44025.666666666664</v>
-    <v>68</v>
+    <v>62</v>
     <v>199.5</v>
     <v>42351910000</v>
     <v>Axfood AB</v>
@@ -5030,7 +5015,7 @@
     <v>329310</v>
   </rv>
   <rv s="4">
-    <v>69</v>
+    <v>63</v>
   </rv>
   <rv s="0">
     <v>https://creativecommons.org/licenses/by-sa/4.0</v>
@@ -5041,14 +5026,14 @@
     <v>Wikipedia</v>
   </rv>
   <rv s="1">
-    <v>71</v>
-    <v>72</v>
+    <v>65</v>
+    <v>66</v>
   </rv>
   <rv s="2">
     <v>Powered by Refinitiv</v>
     <v>6</v>
     <v>https://www.bing.com/th?id=AMMS_813800af8ea77f18dfa72731ec0cc818&amp;qlt=95</v>
-    <v>73</v>
+    <v>67</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=swedbank</v>
     <v>Image of Swedbank AB</v>
     <v/>
@@ -5085,11 +5070,11 @@
     <v>XSTO</v>
     <v>Landsvagen 40, SUNDBYBERG, STOCKHOLM, 172 63 SE</v>
     <v>136.84</v>
-    <v>74</v>
+    <v>68</v>
     <v>Banking Services</v>
     <v>Stock</v>
     <v>44025.666666666664</v>
-    <v>75</v>
+    <v>69</v>
     <v>133.72</v>
     <v>150986900000</v>
     <v>Swedbank AB</v>
@@ -5105,6 +5090,112 @@
     <v>4899127</v>
   </rv>
   <rv s="4">
+    <v>70</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=amwtcw&amp;q=XSTO%3aLATO+B&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="11">
+    <v>en-US</v>
+    <v>amwtcw</v>
+    <v>268435456</v>
+    <v>268435457</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>22</v>
+    <v>Investment AB Latour (XSTO:LATO B)</v>
+    <v>10</v>
+    <v>23</v>
+    <v>Finance</v>
+    <v>5</v>
+    <v>183.8</v>
+    <v>103.9</v>
+    <v>0.7621</v>
+    <v>3.2</v>
+    <v>0</v>
+    <v>1.8571999999999998E-2</v>
+    <v>0</v>
+    <v>SEK</v>
+    <v>Investment AB Latour is a Sweden-based company. Its operations are divided into two business lines. One is made up of the wholly owned industrial and trading operations and the other is a portfolio with listed holdings. Its industrial and trading operations are organized into four business areas: Hultafors Group, Latour Industries, Specma Group and Swegon. The Company's investment portfolio comprises Assa Abloy, Fagerhult, HMS Networks, Loomis, Nederman, Nobia, Securitas, Sweco and Tomra. The Company’s operations are run by its two wholly owned subsidiaries, Nordiska Industri AB and Latour-Gruppen AB, trading with shares and securities is handled by the Karpalunds Angbryggeri AB, while administration of securities is managed by the wholly owned subsidiary, Saki Forvaltning AB.</v>
+    <v>6039</v>
+    <v>NASDAQ Stockholm</v>
+    <v>XSTO</v>
+    <v>XSTO</v>
+    <v>J A Wettergrens Gata 7, Box 336, GOETEBORG, VASTRA GOTALANDS, 401 25 SE</v>
+    <v>175.5</v>
+    <v>Industrial Conglomerates</v>
+    <v>Stock</v>
+    <v>44025.666666666664</v>
+    <v>72</v>
+    <v>172.1</v>
+    <v>102035700000</v>
+    <v>Investment AB Latour</v>
+    <v>Investment AB Latour</v>
+    <v>173.8</v>
+    <v>30.34</v>
+    <v>172.3</v>
+    <v>175.5</v>
+    <v>175.5</v>
+    <v>592197800</v>
+    <v>LATO B</v>
+    <v>Investment AB Latour (XSTO:LATO B)</v>
+    <v>228496</v>
+  </rv>
+  <rv s="4">
+    <v>73</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=amx5rw&amp;q=XSTO%3aRATO+B&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="11">
+    <v>en-US</v>
+    <v>amx5rw</v>
+    <v>268435456</v>
+    <v>268435457</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>22</v>
+    <v>Ratos AB (XSTO:RATO B)</v>
+    <v>10</v>
+    <v>23</v>
+    <v>Finance</v>
+    <v>5</v>
+    <v>37.72</v>
+    <v>16.43</v>
+    <v>1.2246999999999999</v>
+    <v>0.46</v>
+    <v>0</v>
+    <v>1.7384999999999998E-2</v>
+    <v>0</v>
+    <v>SEK</v>
+    <v>Ratos AB is a Sweden-based private equity company. It owns and develops over 10 unlisted medium-sized enterprises in Nordic region. Enterprises are active in various sectors, such as industry, consumer goods, services and life science, among others. The Company’s portfolio comprises Aibel, the supplier of maintenance and modification services for production platforms and onshore installations within oil and gas industry; Bisnode, the data and analytics company; HENT, the construction company with focus on public and commercial real estate; Plantasjen, the chain for sales of plants and gardening accessories; HL Display, the supplier of products and solutions for in-store communication and merchandising; and Diab, the manufacturer of materials for sandwich composite structures, among others enterprises.</v>
+    <v>8527</v>
+    <v>NASDAQ Stockholm</v>
+    <v>XSTO</v>
+    <v>XSTO</v>
+    <v>Drottninggatan 2, STOCKHOLM, STOCKHOLM, 111 51 SE</v>
+    <v>26.92</v>
+    <v>Investment Banking &amp; Investment Services</v>
+    <v>Stock</v>
+    <v>44025.666666666664</v>
+    <v>75</v>
+    <v>26.38</v>
+    <v>8715573000</v>
+    <v>Ratos AB</v>
+    <v>Ratos AB</v>
+    <v>26.5</v>
+    <v>71.510000000000005</v>
+    <v>26.46</v>
+    <v>26.92</v>
+    <v>26.92</v>
+    <v>324140900</v>
+    <v>RATO B</v>
+    <v>Ratos AB (XSTO:RATO B)</v>
+    <v>437940</v>
+  </rv>
+  <rv s="4">
     <v>76</v>
   </rv>
   <rv s="0">
@@ -5112,7 +5203,7 @@
     <v>Wikipedia</v>
   </rv>
   <rv s="1">
-    <v>71</v>
+    <v>65</v>
     <v>78</v>
   </rv>
   <rv s="2">
@@ -5183,17 +5274,17 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=amwsp2&amp;q=XSTO%3aKLOV+B&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="6">
+  <rv s="11">
     <v>en-US</v>
     <v>amwsp2</v>
     <v>268435456</v>
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>9</v>
+    <v>22</v>
     <v>Klovern AB (XSTO:KLOV B)</v>
     <v>10</v>
-    <v>11</v>
+    <v>23</v>
     <v>Finance</v>
     <v>5</v>
     <v>27.58</v>
@@ -5394,47 +5485,7 @@
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
     <k n="Volume"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%EntitySubDomainId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Change"/>
-    <k n="Change (%)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
+    <k n="Year incorporated"/>
   </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
@@ -5540,9 +5591,6 @@
     <k n="_Format" t="spb"/>
     <k n="_Icon" t="s"/>
     <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
     <k n="Change"/>
     <k n="Change % (Extended hours)"/>
     <k n="Change (%)"/>
@@ -5572,7 +5620,6 @@
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
     <k n="Volume"/>
-    <k n="Year incorporated"/>
   </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
@@ -5587,6 +5634,50 @@
     <k n="_Format" t="spb"/>
     <k n="_Icon" t="s"/>
     <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Price (Extended hours)"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%EntitySubDomainId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
     <k n="Change"/>
     <k n="Change % (Extended hours)"/>
     <k n="Change (%)"/>
@@ -5763,7 +5854,7 @@
       <v t="s">%ProviderInfo</v>
       <v t="s">_Display</v>
     </a>
-    <a count="44">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%EntitySubDomainId</v>
@@ -5801,47 +5892,7 @@
       <v t="s">Headquarters</v>
       <v t="s">Industry</v>
       <v t="s">Instrument type</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-      <v t="s">_Display</v>
-    </a>
-    <a count="39">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%EntitySubDomainId</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Market cap</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
       <v t="s">_Flags</v>
       <v t="s">UniqueName</v>
       <v t="s">_DisplayString</v>
@@ -5941,7 +5992,91 @@
       <v t="s">%ProviderInfo</v>
       <v t="s">_Display</v>
     </a>
-    <a count="45">
+    <a count="41">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%EntitySubDomainId</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">Volume</v>
+      <v t="s">Market cap</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+      <v t="s">_Display</v>
+    </a>
+    <a count="39">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%EntitySubDomainId</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Market cap</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+      <v t="s">_Display</v>
+    </a>
+    <a count="44">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%EntitySubDomainId</v>
@@ -5972,50 +6107,6 @@
       <v t="s">Volume</v>
       <v t="s">Market cap</v>
       <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-      <v t="s">_Display</v>
-    </a>
-    <a count="41">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%EntitySubDomainId</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">Volume</v>
-      <v t="s">Market cap</v>
       <v t="s">P/E</v>
       <v t="s">Shares outstanding</v>
       <v t="s">Description</v>
@@ -6185,9 +6276,97 @@
       <v>5</v>
       <v>5</v>
       <v>6</v>
-      <v>7</v>
+      <v>11</v>
       <v>1</v>
       <v>1</v>
+      <v>1</v>
+      <v>8</v>
+      <v>9</v>
+      <v>10</v>
+      <v>12</v>
+      <v>10</v>
+      <v>5</v>
+      <v>1</v>
+      <v>1</v>
+      <v>6</v>
+    </spb>
+    <spb s="0">
+      <v>3</v>
+    </spb>
+    <spb s="10">
+      <v>13</v>
+      <v>2</v>
+      <v>2</v>
+      <v>13</v>
+      <v>3</v>
+      <v>13</v>
+      <v>13</v>
+      <v>13</v>
+      <v>5</v>
+      <v>5</v>
+      <v>6</v>
+      <v>11</v>
+      <v>13</v>
+      <v>13</v>
+      <v>13</v>
+      <v>5</v>
+      <v>8</v>
+      <v>9</v>
+      <v>10</v>
+      <v>12</v>
+      <v>10</v>
+      <v>5</v>
+    </spb>
+    <spb s="11">
+      <v>Real-Time Nasdaq Last Sale</v>
+      <v>from previous close</v>
+      <v>from previous close</v>
+      <v>Source: Nasdaq Last Sale</v>
+      <v>GMT</v>
+    </spb>
+    <spb s="0">
+      <v>4</v>
+    </spb>
+    <spb s="12">
+      <v>13</v>
+      <v>2</v>
+      <v>2</v>
+      <v>13</v>
+      <v>3</v>
+      <v>13</v>
+      <v>4</v>
+      <v>13</v>
+      <v>13</v>
+      <v>5</v>
+      <v>5</v>
+      <v>6</v>
+      <v>11</v>
+      <v>13</v>
+      <v>13</v>
+      <v>13</v>
+      <v>5</v>
+      <v>8</v>
+      <v>9</v>
+      <v>10</v>
+      <v>12</v>
+      <v>10</v>
+      <v>5</v>
+    </spb>
+    <spb s="0">
+      <v>5</v>
+    </spb>
+    <spb s="13">
+      <v>1</v>
+      <v>2</v>
+      <v>1</v>
+      <v>3</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
+      <v>5</v>
+      <v>6</v>
+      <v>14</v>
       <v>1</v>
       <v>8</v>
       <v>9</v>
@@ -6199,9 +6378,9 @@
       <v>6</v>
     </spb>
     <spb s="0">
-      <v>3</v>
+      <v>6</v>
     </spb>
-    <spb s="10">
+    <spb s="14">
       <v>1</v>
       <v>1</v>
       <v>3</v>
@@ -6221,7 +6400,7 @@
       <v>5</v>
       <v>1</v>
     </spb>
-    <spb s="11">
+    <spb s="15">
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -6230,71 +6409,9 @@
       <v>Delayed 15 minutes</v>
     </spb>
     <spb s="0">
-      <v>4</v>
+      <v>7</v>
     </spb>
-    <spb s="12">
-      <v>11</v>
-      <v>2</v>
-      <v>2</v>
-      <v>11</v>
-      <v>3</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>5</v>
-      <v>5</v>
-      <v>6</v>
-      <v>12</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>5</v>
-      <v>8</v>
-      <v>9</v>
-      <v>10</v>
-      <v>13</v>
-      <v>10</v>
-      <v>5</v>
-    </spb>
-    <spb s="13">
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from previous close</v>
-      <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
-      <v>GMT</v>
-    </spb>
-    <spb s="0">
-      <v>5</v>
-    </spb>
-    <spb s="14">
-      <v>11</v>
-      <v>2</v>
-      <v>2</v>
-      <v>11</v>
-      <v>3</v>
-      <v>11</v>
-      <v>4</v>
-      <v>11</v>
-      <v>11</v>
-      <v>5</v>
-      <v>5</v>
-      <v>6</v>
-      <v>12</v>
-      <v>11</v>
-      <v>11</v>
-      <v>11</v>
-      <v>5</v>
-      <v>8</v>
-      <v>9</v>
-      <v>10</v>
-      <v>13</v>
-      <v>10</v>
-      <v>5</v>
-    </spb>
-    <spb s="0">
-      <v>6</v>
-    </spb>
-    <spb s="15">
+    <spb s="16">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -6306,35 +6423,9 @@
       <v>5</v>
       <v>5</v>
       <v>6</v>
-      <v>12</v>
+      <v>7</v>
       <v>1</v>
       <v>1</v>
-      <v>1</v>
-      <v>8</v>
-      <v>9</v>
-      <v>10</v>
-      <v>13</v>
-      <v>10</v>
-      <v>5</v>
-      <v>1</v>
-      <v>1</v>
-      <v>6</v>
-    </spb>
-    <spb s="0">
-      <v>7</v>
-    </spb>
-    <spb s="16">
-      <v>1</v>
-      <v>2</v>
-      <v>1</v>
-      <v>3</v>
-      <v>1</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
-      <v>5</v>
-      <v>6</v>
-      <v>14</v>
       <v>1</v>
       <v>8</v>
       <v>9</v>
@@ -6361,14 +6452,14 @@
       <v>5</v>
       <v>5</v>
       <v>6</v>
-      <v>12</v>
+      <v>11</v>
       <v>1</v>
       <v>1</v>
       <v>1</v>
       <v>8</v>
       <v>9</v>
       <v>10</v>
-      <v>13</v>
+      <v>12</v>
       <v>10</v>
       <v>5</v>
       <v>1</v>
@@ -6486,39 +6577,12 @@
     <k n="_DisplayString" t="i"/>
     <k n="Last trade time" t="i"/>
     <k n="%EntityServiceId" t="i"/>
+    <k n="Year incorporated" t="i"/>
     <k n="%EntitySubDomainId" t="i"/>
     <k n="Shares outstanding" t="i"/>
     <k n="Price (Extended hours)" t="i"/>
     <k n="Change (Extended hours)" t="i"/>
     <k n="Change % (Extended hours)" t="i"/>
-  </s>
-  <s>
-    <k n="Low" t="i"/>
-    <k n="High" t="i"/>
-    <k n="Name" t="i"/>
-    <k n="Open" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Volume" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
-    <k n="52 week low" t="i"/>
-    <k n="52 week high" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="_DisplayString" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="%EntitySubDomainId" t="i"/>
-    <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-  </s>
-  <s>
-    <k n="Price" t="s"/>
-    <k n="Change" t="s"/>
-    <k n="Change (%)" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="Low" t="i"/>
@@ -6579,6 +6643,56 @@
   <s>
     <k n="Low" t="i"/>
     <k n="P/E" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="_DisplayString" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="%EntityServiceId" t="i"/>
+    <k n="%EntitySubDomainId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="_DisplayString" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="%EntityServiceId" t="i"/>
+    <k n="%EntitySubDomainId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+  </s>
+  <s>
+    <k n="Price" t="s"/>
+    <k n="Change" t="s"/>
+    <k n="Change (%)" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="P/E" t="i"/>
     <k n="Beta" t="i"/>
     <k n="High" t="i"/>
     <k n="Name" t="i"/>
@@ -6591,29 +6705,6 @@
     <k n="Market cap" t="i"/>
     <k n="52 week low" t="i"/>
     <k n="52 week high" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="_DisplayString" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="%EntityServiceId" t="i"/>
-    <k n="Year incorporated" t="i"/>
-    <k n="%EntitySubDomainId" t="i"/>
-    <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
-  </s>
-  <s>
-    <k n="Low" t="i"/>
-    <k n="P/E" t="i"/>
-    <k n="High" t="i"/>
-    <k n="Name" t="i"/>
-    <k n="Open" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Volume" t="i"/>
-    <k n="Employees" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
     <k n="Previous close" t="i"/>
     <k n="_DisplayString" t="i"/>
     <k n="Last trade time" t="i"/>
@@ -6679,13 +6770,13 @@
       <x:numFmt numFmtId="2" formatCode="0.00"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="166" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
-    </x:dxf>
-    <x:dxf>
       <x:numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="1" formatCode="0"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="166" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;_);_(@_)"/>
@@ -7072,7 +7163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Blad1"/>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:DN21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
@@ -7090,58 +7181,58 @@
     <col min="16" max="16" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:118" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="e" vm="1">
+    <row r="2" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
       <c r="B2" s="2"/>
@@ -7167,13 +7258,13 @@
         <f t="shared" ref="O2:O9" si="0">SUM(B2:M2)*N2</f>
         <v>1.5</v>
       </c>
-      <c r="P2" s="14" cm="1">
+      <c r="P2" s="9" cm="1">
         <f t="array" ref="P2">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>86.46</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="e" vm="2">
+    <row r="3" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="B3" s="1"/>
@@ -7199,13 +7290,13 @@
         <f t="shared" si="0"/>
         <v>9.6999999999999993</v>
       </c>
-      <c r="P3" s="14" cm="1">
+      <c r="P3" s="39" cm="1">
         <f t="array" ref="P3">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>137.65</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="e" vm="3">
+    <row r="4" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
       <c r="B4" s="2"/>
@@ -7231,43 +7322,49 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="P4" s="14" cm="1">
+      <c r="P4" s="9" cm="1">
         <f t="array" ref="P4">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>506.2</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="e" vm="4">
+    <row r="5" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1">
+      <c r="B5" s="17"/>
+      <c r="C5" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17">
+        <v>5.5</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="17">
         <v>1</v>
       </c>
-      <c r="O5" s="1">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="P5" s="14" cm="1">
+      <c r="O5" s="17">
+        <f>SUM(B5:M5)*N5</f>
+        <v>22</v>
+      </c>
+      <c r="P5" s="41" cm="1">
         <f t="array" ref="P5">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>26.46</v>
+        <v>595</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="e" vm="5">
+    <row r="6" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="B6" s="2"/>
@@ -7293,49 +7390,147 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="P6" s="14" cm="1">
+      <c r="P6" s="9" cm="1">
         <f t="array" ref="P6">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>263.3</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="e" vm="6">
+    <row r="7" spans="1:118" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
       <c r="B7" s="1"/>
-      <c r="C7" s="1">
-        <v>1.75</v>
-      </c>
+      <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1">
-        <v>1.75</v>
-      </c>
+      <c r="E7" s="1">
+        <v>3.15</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="I7" s="1">
-        <v>1.75</v>
-      </c>
+      <c r="I7" s="1"/>
       <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1">
-        <v>1.75</v>
-      </c>
+      <c r="K7" s="1">
+        <v>3.15</v>
+      </c>
+      <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="P7" s="14" cm="1">
+        <f>SUM(B7:M7)*N7</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="39" cm="1">
         <f t="array" ref="P7">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>80</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7"/>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+      <c r="AR7"/>
+      <c r="AS7"/>
+      <c r="AT7"/>
+      <c r="AU7"/>
+      <c r="AV7"/>
+      <c r="AW7"/>
+      <c r="AX7"/>
+      <c r="AY7"/>
+      <c r="AZ7"/>
+      <c r="BA7"/>
+      <c r="BB7"/>
+      <c r="BC7"/>
+      <c r="BD7"/>
+      <c r="BE7"/>
+      <c r="BF7"/>
+      <c r="BG7"/>
+      <c r="BH7"/>
+      <c r="BI7"/>
+      <c r="BJ7"/>
+      <c r="BK7"/>
+      <c r="BL7"/>
+      <c r="BM7"/>
+      <c r="BN7"/>
+      <c r="BO7"/>
+      <c r="BP7"/>
+      <c r="BQ7"/>
+      <c r="BR7"/>
+      <c r="BS7"/>
+      <c r="BT7"/>
+      <c r="BU7"/>
+      <c r="BV7"/>
+      <c r="BW7"/>
+      <c r="BX7"/>
+      <c r="BY7"/>
+      <c r="BZ7"/>
+      <c r="CA7"/>
+      <c r="CB7"/>
+      <c r="CC7"/>
+      <c r="CD7"/>
+      <c r="CE7"/>
+      <c r="CF7"/>
+      <c r="CG7"/>
+      <c r="CH7"/>
+      <c r="CI7"/>
+      <c r="CJ7"/>
+      <c r="CK7"/>
+      <c r="CL7"/>
+      <c r="CM7"/>
+      <c r="CN7"/>
+      <c r="CO7"/>
+      <c r="CP7"/>
+      <c r="CQ7"/>
+      <c r="CR7"/>
+      <c r="CS7"/>
+      <c r="CT7"/>
+      <c r="CU7"/>
+      <c r="CV7"/>
+      <c r="CW7"/>
+      <c r="CX7"/>
+      <c r="CY7"/>
+      <c r="CZ7"/>
+      <c r="DA7"/>
+      <c r="DB7"/>
+      <c r="DC7"/>
+      <c r="DD7"/>
+      <c r="DE7"/>
+      <c r="DF7"/>
+      <c r="DG7"/>
+      <c r="DH7"/>
+      <c r="DI7"/>
+      <c r="DJ7"/>
+      <c r="DK7"/>
+      <c r="DL7"/>
+      <c r="DM7"/>
+      <c r="DN7"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="e" vm="7">
+    <row r="8" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
       <c r="B8" s="2"/>
@@ -7365,13 +7560,13 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="P8" s="13" cm="1">
+      <c r="P8" s="8" cm="1">
         <f t="array" ref="P8">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)*10</f>
         <v>305.7</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="e" vm="8">
+    <row r="9" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
       <c r="B9" s="1">
@@ -7401,403 +7596,1217 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="P9" s="13" cm="1">
+      <c r="P9" s="40" cm="1">
         <f t="array" ref="P9">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)*10</f>
         <v>301.3</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="e" vm="9">
+    <row r="10" spans="1:118" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2">
-        <v>2.25</v>
-      </c>
-      <c r="G10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="M10" s="2">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="N10" s="2">
         <v>1</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" ref="O10:O18" si="1">SUM(B10:M10)*N10</f>
-        <v>2.25</v>
-      </c>
-      <c r="P10" s="14" cm="1">
+        <f>SUM(B10:M10)*N10</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P10" s="9" cm="1">
         <f t="array" ref="P10">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>172.3</v>
-      </c>
+        <v>184.4</v>
+      </c>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10"/>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+      <c r="AI10"/>
+      <c r="AJ10"/>
+      <c r="AK10"/>
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+      <c r="AR10"/>
+      <c r="AS10"/>
+      <c r="AT10"/>
+      <c r="AU10"/>
+      <c r="AV10"/>
+      <c r="AW10"/>
+      <c r="AX10"/>
+      <c r="AY10"/>
+      <c r="AZ10"/>
+      <c r="BA10"/>
+      <c r="BB10"/>
+      <c r="BC10"/>
+      <c r="BD10"/>
+      <c r="BE10"/>
+      <c r="BF10"/>
+      <c r="BG10"/>
+      <c r="BH10"/>
+      <c r="BI10"/>
+      <c r="BJ10"/>
+      <c r="BK10"/>
+      <c r="BL10"/>
+      <c r="BM10"/>
+      <c r="BN10"/>
+      <c r="BO10"/>
+      <c r="BP10"/>
+      <c r="BQ10"/>
+      <c r="BR10"/>
+      <c r="BS10"/>
+      <c r="BT10"/>
+      <c r="BU10"/>
+      <c r="BV10"/>
+      <c r="BW10"/>
+      <c r="BX10"/>
+      <c r="BY10"/>
+      <c r="BZ10"/>
+      <c r="CA10"/>
+      <c r="CB10"/>
+      <c r="CC10"/>
+      <c r="CD10"/>
+      <c r="CE10"/>
+      <c r="CF10"/>
+      <c r="CG10"/>
+      <c r="CH10"/>
+      <c r="CI10"/>
+      <c r="CJ10"/>
+      <c r="CK10"/>
+      <c r="CL10"/>
+      <c r="CM10"/>
+      <c r="CN10"/>
+      <c r="CO10"/>
+      <c r="CP10"/>
+      <c r="CQ10"/>
+      <c r="CR10"/>
+      <c r="CS10"/>
+      <c r="CT10"/>
+      <c r="CU10"/>
+      <c r="CV10"/>
+      <c r="CW10"/>
+      <c r="CX10"/>
+      <c r="CY10"/>
+      <c r="CZ10"/>
+      <c r="DA10"/>
+      <c r="DB10"/>
+      <c r="DC10"/>
+      <c r="DD10"/>
+      <c r="DE10"/>
+      <c r="DF10"/>
+      <c r="DG10"/>
+      <c r="DH10"/>
+      <c r="DI10"/>
+      <c r="DJ10"/>
+      <c r="DK10"/>
+      <c r="DL10"/>
+      <c r="DM10"/>
+      <c r="DN10"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="e" vm="10">
+    <row r="11" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1">
-        <v>5.5</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1">
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19">
+        <v>4</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19">
+        <v>4</v>
+      </c>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19">
         <v>1</v>
       </c>
-      <c r="O11" s="1">
+      <c r="O11" s="19">
+        <f t="shared" ref="O11:O18" si="1">SUM(B11:M11)*N11</f>
+        <v>8</v>
+      </c>
+      <c r="P11" s="20" cm="1">
+        <f t="array" ref="P11">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A12" s="22" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23">
+        <v>1.75</v>
+      </c>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23">
+        <v>1.75</v>
+      </c>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23">
+        <v>1.75</v>
+      </c>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23">
+        <v>1.75</v>
+      </c>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23">
+        <v>1</v>
+      </c>
+      <c r="O12" s="23">
+        <f>SUM(B12:M12)*N12</f>
+        <v>7</v>
+      </c>
+      <c r="P12" s="24" cm="1">
+        <f t="array" ref="P12">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:118" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19">
+        <v>3.25</v>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19">
+        <v>3.25</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19">
+        <v>0</v>
+      </c>
+      <c r="O13" s="19">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-      <c r="P11" s="14" cm="1">
-        <f t="array" ref="P11">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>595</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P13" s="20" cm="1">
+        <f t="array" ref="P13">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
+        <v>176.2</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13"/>
+      <c r="AA13"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
+      <c r="AH13"/>
+      <c r="AI13"/>
+      <c r="AJ13"/>
+      <c r="AK13"/>
+      <c r="AL13"/>
+      <c r="AM13"/>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+      <c r="AR13"/>
+      <c r="AS13"/>
+      <c r="AT13"/>
+      <c r="AU13"/>
+      <c r="AV13"/>
+      <c r="AW13"/>
+      <c r="AX13"/>
+      <c r="AY13"/>
+      <c r="AZ13"/>
+      <c r="BA13"/>
+      <c r="BB13"/>
+      <c r="BC13"/>
+      <c r="BD13"/>
+      <c r="BE13"/>
+      <c r="BF13"/>
+      <c r="BG13"/>
+      <c r="BH13"/>
+      <c r="BI13"/>
+      <c r="BJ13"/>
+      <c r="BK13"/>
+      <c r="BL13"/>
+      <c r="BM13"/>
+      <c r="BN13"/>
+      <c r="BO13"/>
+      <c r="BP13"/>
+      <c r="BQ13"/>
+      <c r="BR13"/>
+      <c r="BS13"/>
+      <c r="BT13"/>
+      <c r="BU13"/>
+      <c r="BV13"/>
+      <c r="BW13"/>
+      <c r="BX13"/>
+      <c r="BY13"/>
+      <c r="BZ13"/>
+      <c r="CA13"/>
+      <c r="CB13"/>
+      <c r="CC13"/>
+      <c r="CD13"/>
+      <c r="CE13"/>
+      <c r="CF13"/>
+      <c r="CG13"/>
+      <c r="CH13"/>
+      <c r="CI13"/>
+      <c r="CJ13"/>
+      <c r="CK13"/>
+      <c r="CL13"/>
+      <c r="CM13"/>
+      <c r="CN13"/>
+      <c r="CO13"/>
+      <c r="CP13"/>
+      <c r="CQ13"/>
+      <c r="CR13"/>
+      <c r="CS13"/>
+      <c r="CT13"/>
+      <c r="CU13"/>
+      <c r="CV13"/>
+      <c r="CW13"/>
+      <c r="CX13"/>
+      <c r="CY13"/>
+      <c r="CZ13"/>
+      <c r="DA13"/>
+      <c r="DB13"/>
+      <c r="DC13"/>
+      <c r="DD13"/>
+      <c r="DE13"/>
+      <c r="DF13"/>
+      <c r="DG13"/>
+      <c r="DH13"/>
+      <c r="DI13"/>
+      <c r="DJ13"/>
+      <c r="DK13"/>
+      <c r="DL13"/>
+      <c r="DM13"/>
+      <c r="DN13"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="e" vm="11">
+    <row r="14" spans="1:118" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2">
-        <v>4</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2">
-        <v>4</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23">
+        <v>3.5</v>
+      </c>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23">
+        <v>3.5</v>
+      </c>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23">
+        <v>0</v>
+      </c>
+      <c r="O14" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="24" cm="1">
+        <f t="array" ref="P14">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
+        <v>201.8</v>
+      </c>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+      <c r="AG14"/>
+      <c r="AH14"/>
+      <c r="AI14"/>
+      <c r="AJ14"/>
+      <c r="AK14"/>
+      <c r="AL14"/>
+      <c r="AM14"/>
+      <c r="AN14"/>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+      <c r="AR14"/>
+      <c r="AS14"/>
+      <c r="AT14"/>
+      <c r="AU14"/>
+      <c r="AV14"/>
+      <c r="AW14"/>
+      <c r="AX14"/>
+      <c r="AY14"/>
+      <c r="AZ14"/>
+      <c r="BA14"/>
+      <c r="BB14"/>
+      <c r="BC14"/>
+      <c r="BD14"/>
+      <c r="BE14"/>
+      <c r="BF14"/>
+      <c r="BG14"/>
+      <c r="BH14"/>
+      <c r="BI14"/>
+      <c r="BJ14"/>
+      <c r="BK14"/>
+      <c r="BL14"/>
+      <c r="BM14"/>
+      <c r="BN14"/>
+      <c r="BO14"/>
+      <c r="BP14"/>
+      <c r="BQ14"/>
+      <c r="BR14"/>
+      <c r="BS14"/>
+      <c r="BT14"/>
+      <c r="BU14"/>
+      <c r="BV14"/>
+      <c r="BW14"/>
+      <c r="BX14"/>
+      <c r="BY14"/>
+      <c r="BZ14"/>
+      <c r="CA14"/>
+      <c r="CB14"/>
+      <c r="CC14"/>
+      <c r="CD14"/>
+      <c r="CE14"/>
+      <c r="CF14"/>
+      <c r="CG14"/>
+      <c r="CH14"/>
+      <c r="CI14"/>
+      <c r="CJ14"/>
+      <c r="CK14"/>
+      <c r="CL14"/>
+      <c r="CM14"/>
+      <c r="CN14"/>
+      <c r="CO14"/>
+      <c r="CP14"/>
+      <c r="CQ14"/>
+      <c r="CR14"/>
+      <c r="CS14"/>
+      <c r="CT14"/>
+      <c r="CU14"/>
+      <c r="CV14"/>
+      <c r="CW14"/>
+      <c r="CX14"/>
+      <c r="CY14"/>
+      <c r="CZ14"/>
+      <c r="DA14"/>
+      <c r="DB14"/>
+      <c r="DC14"/>
+      <c r="DD14"/>
+      <c r="DE14"/>
+      <c r="DF14"/>
+      <c r="DG14"/>
+      <c r="DH14"/>
+      <c r="DI14"/>
+      <c r="DJ14"/>
+      <c r="DK14"/>
+      <c r="DL14"/>
+      <c r="DM14"/>
+      <c r="DN14"/>
+    </row>
+    <row r="15" spans="1:118" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19">
+        <v>14</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="19">
         <v>1</v>
       </c>
-      <c r="O12" s="2">
-        <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-      <c r="P12" s="14" cm="1">
-        <f t="array" ref="P12">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="e" vm="12">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
-        <f t="shared" si="1"/>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P13" s="14" cm="1">
-        <f t="array" ref="P13">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>184.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="e" vm="13">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
-        <v>3.15</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2">
-        <v>3.15</v>
-      </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2">
-        <v>0</v>
-      </c>
-      <c r="O14" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14" cm="1">
-        <f t="array" ref="P14">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="e" vm="14">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1">
-        <v>3.25</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1">
-        <v>3.25</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1">
-        <v>0</v>
-      </c>
-      <c r="O15" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="14" cm="1">
-        <f t="array" ref="P15">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>176.2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="e" vm="15">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2">
-        <v>0</v>
-      </c>
-      <c r="O16" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="14" cm="1">
-        <f t="array" ref="P16">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>201.8</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="e" vm="16">
-        <v>#VALUE!</v>
-      </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1">
-        <v>14</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1">
-        <v>1</v>
-      </c>
-      <c r="O17" s="1">
+      <c r="O15" s="19">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="P17" s="14" cm="1">
+      <c r="P15" s="20" cm="1">
+        <f t="array" ref="P15">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
+        <v>133.38</v>
+      </c>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15"/>
+      <c r="AI15"/>
+      <c r="AJ15"/>
+      <c r="AK15"/>
+      <c r="AL15"/>
+      <c r="AM15"/>
+      <c r="AN15"/>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+      <c r="AR15"/>
+      <c r="AS15"/>
+      <c r="AT15"/>
+      <c r="AU15"/>
+      <c r="AV15"/>
+      <c r="AW15"/>
+      <c r="AX15"/>
+      <c r="AY15"/>
+      <c r="AZ15"/>
+      <c r="BA15"/>
+      <c r="BB15"/>
+      <c r="BC15"/>
+      <c r="BD15"/>
+      <c r="BE15"/>
+      <c r="BF15"/>
+      <c r="BG15"/>
+      <c r="BH15"/>
+      <c r="BI15"/>
+      <c r="BJ15"/>
+      <c r="BK15"/>
+      <c r="BL15"/>
+      <c r="BM15"/>
+      <c r="BN15"/>
+      <c r="BO15"/>
+      <c r="BP15"/>
+      <c r="BQ15"/>
+      <c r="BR15"/>
+      <c r="BS15"/>
+      <c r="BT15"/>
+      <c r="BU15"/>
+      <c r="BV15"/>
+      <c r="BW15"/>
+      <c r="BX15"/>
+      <c r="BY15"/>
+      <c r="BZ15"/>
+      <c r="CA15"/>
+      <c r="CB15"/>
+      <c r="CC15"/>
+      <c r="CD15"/>
+      <c r="CE15"/>
+      <c r="CF15"/>
+      <c r="CG15"/>
+      <c r="CH15"/>
+      <c r="CI15"/>
+      <c r="CJ15"/>
+      <c r="CK15"/>
+      <c r="CL15"/>
+      <c r="CM15"/>
+      <c r="CN15"/>
+      <c r="CO15"/>
+      <c r="CP15"/>
+      <c r="CQ15"/>
+      <c r="CR15"/>
+      <c r="CS15"/>
+      <c r="CT15"/>
+      <c r="CU15"/>
+      <c r="CV15"/>
+      <c r="CW15"/>
+      <c r="CX15"/>
+      <c r="CY15"/>
+      <c r="CZ15"/>
+      <c r="DA15"/>
+      <c r="DB15"/>
+      <c r="DC15"/>
+      <c r="DD15"/>
+      <c r="DE15"/>
+      <c r="DF15"/>
+      <c r="DG15"/>
+      <c r="DH15"/>
+      <c r="DI15"/>
+      <c r="DJ15"/>
+      <c r="DK15"/>
+      <c r="DL15"/>
+      <c r="DM15"/>
+      <c r="DN15"/>
+    </row>
+    <row r="16" spans="1:118" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27">
+        <v>2.25</v>
+      </c>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="27">
+        <v>1</v>
+      </c>
+      <c r="O16" s="27">
+        <f>SUM(B16:M16)*N16</f>
+        <v>2.25</v>
+      </c>
+      <c r="P16" s="28" cm="1">
+        <f t="array" ref="P16">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
+        <v>172.3</v>
+      </c>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+      <c r="AG16"/>
+      <c r="AH16"/>
+      <c r="AI16"/>
+      <c r="AJ16"/>
+      <c r="AK16"/>
+      <c r="AL16"/>
+      <c r="AM16"/>
+      <c r="AN16"/>
+      <c r="AO16"/>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+      <c r="AR16"/>
+      <c r="AS16"/>
+      <c r="AT16"/>
+      <c r="AU16"/>
+      <c r="AV16"/>
+      <c r="AW16"/>
+      <c r="AX16"/>
+      <c r="AY16"/>
+      <c r="AZ16"/>
+      <c r="BA16"/>
+      <c r="BB16"/>
+      <c r="BC16"/>
+      <c r="BD16"/>
+      <c r="BE16"/>
+      <c r="BF16"/>
+      <c r="BG16"/>
+      <c r="BH16"/>
+      <c r="BI16"/>
+      <c r="BJ16"/>
+      <c r="BK16"/>
+      <c r="BL16"/>
+      <c r="BM16"/>
+      <c r="BN16"/>
+      <c r="BO16"/>
+      <c r="BP16"/>
+      <c r="BQ16"/>
+      <c r="BR16"/>
+      <c r="BS16"/>
+      <c r="BT16"/>
+      <c r="BU16"/>
+      <c r="BV16"/>
+      <c r="BW16"/>
+      <c r="BX16"/>
+      <c r="BY16"/>
+      <c r="BZ16"/>
+      <c r="CA16"/>
+      <c r="CB16"/>
+      <c r="CC16"/>
+      <c r="CD16"/>
+      <c r="CE16"/>
+      <c r="CF16"/>
+      <c r="CG16"/>
+      <c r="CH16"/>
+      <c r="CI16"/>
+      <c r="CJ16"/>
+      <c r="CK16"/>
+      <c r="CL16"/>
+      <c r="CM16"/>
+      <c r="CN16"/>
+      <c r="CO16"/>
+      <c r="CP16"/>
+      <c r="CQ16"/>
+      <c r="CR16"/>
+      <c r="CS16"/>
+      <c r="CT16"/>
+      <c r="CU16"/>
+      <c r="CV16"/>
+      <c r="CW16"/>
+      <c r="CX16"/>
+      <c r="CY16"/>
+      <c r="CZ16"/>
+      <c r="DA16"/>
+      <c r="DB16"/>
+      <c r="DC16"/>
+      <c r="DD16"/>
+      <c r="DE16"/>
+      <c r="DF16"/>
+      <c r="DG16"/>
+      <c r="DH16"/>
+      <c r="DI16"/>
+      <c r="DJ16"/>
+      <c r="DK16"/>
+      <c r="DL16"/>
+      <c r="DM16"/>
+      <c r="DN16"/>
+    </row>
+    <row r="17" spans="1:118" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="e" vm="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19">
+        <v>2</v>
+      </c>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19">
+        <v>1</v>
+      </c>
+      <c r="O17" s="19">
+        <f>SUM(B17:M17)*N17</f>
+        <v>2</v>
+      </c>
+      <c r="P17" s="20" cm="1">
         <f t="array" ref="P17">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
-        <v>133.38</v>
-      </c>
+        <v>26.46</v>
+      </c>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17"/>
+      <c r="Z17"/>
+      <c r="AA17"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
+      <c r="AF17"/>
+      <c r="AG17"/>
+      <c r="AH17"/>
+      <c r="AI17"/>
+      <c r="AJ17"/>
+      <c r="AK17"/>
+      <c r="AL17"/>
+      <c r="AM17"/>
+      <c r="AN17"/>
+      <c r="AO17"/>
+      <c r="AP17"/>
+      <c r="AQ17"/>
+      <c r="AR17"/>
+      <c r="AS17"/>
+      <c r="AT17"/>
+      <c r="AU17"/>
+      <c r="AV17"/>
+      <c r="AW17"/>
+      <c r="AX17"/>
+      <c r="AY17"/>
+      <c r="AZ17"/>
+      <c r="BA17"/>
+      <c r="BB17"/>
+      <c r="BC17"/>
+      <c r="BD17"/>
+      <c r="BE17"/>
+      <c r="BF17"/>
+      <c r="BG17"/>
+      <c r="BH17"/>
+      <c r="BI17"/>
+      <c r="BJ17"/>
+      <c r="BK17"/>
+      <c r="BL17"/>
+      <c r="BM17"/>
+      <c r="BN17"/>
+      <c r="BO17"/>
+      <c r="BP17"/>
+      <c r="BQ17"/>
+      <c r="BR17"/>
+      <c r="BS17"/>
+      <c r="BT17"/>
+      <c r="BU17"/>
+      <c r="BV17"/>
+      <c r="BW17"/>
+      <c r="BX17"/>
+      <c r="BY17"/>
+      <c r="BZ17"/>
+      <c r="CA17"/>
+      <c r="CB17"/>
+      <c r="CC17"/>
+      <c r="CD17"/>
+      <c r="CE17"/>
+      <c r="CF17"/>
+      <c r="CG17"/>
+      <c r="CH17"/>
+      <c r="CI17"/>
+      <c r="CJ17"/>
+      <c r="CK17"/>
+      <c r="CL17"/>
+      <c r="CM17"/>
+      <c r="CN17"/>
+      <c r="CO17"/>
+      <c r="CP17"/>
+      <c r="CQ17"/>
+      <c r="CR17"/>
+      <c r="CS17"/>
+      <c r="CT17"/>
+      <c r="CU17"/>
+      <c r="CV17"/>
+      <c r="CW17"/>
+      <c r="CX17"/>
+      <c r="CY17"/>
+      <c r="CZ17"/>
+      <c r="DA17"/>
+      <c r="DB17"/>
+      <c r="DC17"/>
+      <c r="DD17"/>
+      <c r="DE17"/>
+      <c r="DF17"/>
+      <c r="DG17"/>
+      <c r="DH17"/>
+      <c r="DI17"/>
+      <c r="DJ17"/>
+      <c r="DK17"/>
+      <c r="DL17"/>
+      <c r="DM17"/>
+      <c r="DN17"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="e" vm="17">
+    <row r="18" spans="1:118" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2">
+      <c r="B18" s="23"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23">
         <v>18</v>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2">
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23">
         <v>8.5</v>
       </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2">
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23">
         <v>1</v>
       </c>
-      <c r="O18" s="2">
+      <c r="O18" s="23">
         <f t="shared" si="1"/>
         <v>26.5</v>
       </c>
-      <c r="P18" s="14" cm="1">
+      <c r="P18" s="24" cm="1">
         <f t="array" ref="P18">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>991.4</v>
       </c>
+      <c r="Q18"/>
+      <c r="R18"/>
+      <c r="S18"/>
+      <c r="T18"/>
+      <c r="U18"/>
+      <c r="V18"/>
+      <c r="W18"/>
+      <c r="X18"/>
+      <c r="Y18"/>
+      <c r="Z18"/>
+      <c r="AA18"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18"/>
+      <c r="AF18"/>
+      <c r="AG18"/>
+      <c r="AH18"/>
+      <c r="AI18"/>
+      <c r="AJ18"/>
+      <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18"/>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+      <c r="AR18"/>
+      <c r="AS18"/>
+      <c r="AT18"/>
+      <c r="AU18"/>
+      <c r="AV18"/>
+      <c r="AW18"/>
+      <c r="AX18"/>
+      <c r="AY18"/>
+      <c r="AZ18"/>
+      <c r="BA18"/>
+      <c r="BB18"/>
+      <c r="BC18"/>
+      <c r="BD18"/>
+      <c r="BE18"/>
+      <c r="BF18"/>
+      <c r="BG18"/>
+      <c r="BH18"/>
+      <c r="BI18"/>
+      <c r="BJ18"/>
+      <c r="BK18"/>
+      <c r="BL18"/>
+      <c r="BM18"/>
+      <c r="BN18"/>
+      <c r="BO18"/>
+      <c r="BP18"/>
+      <c r="BQ18"/>
+      <c r="BR18"/>
+      <c r="BS18"/>
+      <c r="BT18"/>
+      <c r="BU18"/>
+      <c r="BV18"/>
+      <c r="BW18"/>
+      <c r="BX18"/>
+      <c r="BY18"/>
+      <c r="BZ18"/>
+      <c r="CA18"/>
+      <c r="CB18"/>
+      <c r="CC18"/>
+      <c r="CD18"/>
+      <c r="CE18"/>
+      <c r="CF18"/>
+      <c r="CG18"/>
+      <c r="CH18"/>
+      <c r="CI18"/>
+      <c r="CJ18"/>
+      <c r="CK18"/>
+      <c r="CL18"/>
+      <c r="CM18"/>
+      <c r="CN18"/>
+      <c r="CO18"/>
+      <c r="CP18"/>
+      <c r="CQ18"/>
+      <c r="CR18"/>
+      <c r="CS18"/>
+      <c r="CT18"/>
+      <c r="CU18"/>
+      <c r="CV18"/>
+      <c r="CW18"/>
+      <c r="CX18"/>
+      <c r="CY18"/>
+      <c r="CZ18"/>
+      <c r="DA18"/>
+      <c r="DB18"/>
+      <c r="DC18"/>
+      <c r="DD18"/>
+      <c r="DE18"/>
+      <c r="DF18"/>
+      <c r="DG18"/>
+      <c r="DH18"/>
+      <c r="DI18"/>
+      <c r="DJ18"/>
+      <c r="DK18"/>
+      <c r="DL18"/>
+      <c r="DM18"/>
+      <c r="DN18"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="e" vm="18">
+    <row r="19" spans="1:118" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1">
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19">
         <v>0.46</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1">
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19">
         <v>0.46</v>
       </c>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1">
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19">
         <v>0.46</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1">
+      <c r="K19" s="19"/>
+      <c r="L19" s="19"/>
+      <c r="M19" s="19">
         <v>0.46</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N19" s="19">
         <v>1</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O19" s="19">
         <f>SUM(B19:M19)*N19</f>
         <v>1.84</v>
       </c>
-      <c r="P19" s="12" cm="1">
+      <c r="P19" s="30" cm="1">
         <f t="array" ref="P19">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
         <v>14.81</v>
       </c>
+      <c r="Q19"/>
+      <c r="R19"/>
+      <c r="S19"/>
+      <c r="T19"/>
+      <c r="U19"/>
+      <c r="V19"/>
+      <c r="W19"/>
+      <c r="X19"/>
+      <c r="Y19"/>
+      <c r="Z19"/>
+      <c r="AA19"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19"/>
+      <c r="AF19"/>
+      <c r="AG19"/>
+      <c r="AH19"/>
+      <c r="AI19"/>
+      <c r="AJ19"/>
+      <c r="AK19"/>
+      <c r="AL19"/>
+      <c r="AM19"/>
+      <c r="AN19"/>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+      <c r="AR19"/>
+      <c r="AS19"/>
+      <c r="AT19"/>
+      <c r="AU19"/>
+      <c r="AV19"/>
+      <c r="AW19"/>
+      <c r="AX19"/>
+      <c r="AY19"/>
+      <c r="AZ19"/>
+      <c r="BA19"/>
+      <c r="BB19"/>
+      <c r="BC19"/>
+      <c r="BD19"/>
+      <c r="BE19"/>
+      <c r="BF19"/>
+      <c r="BG19"/>
+      <c r="BH19"/>
+      <c r="BI19"/>
+      <c r="BJ19"/>
+      <c r="BK19"/>
+      <c r="BL19"/>
+      <c r="BM19"/>
+      <c r="BN19"/>
+      <c r="BO19"/>
+      <c r="BP19"/>
+      <c r="BQ19"/>
+      <c r="BR19"/>
+      <c r="BS19"/>
+      <c r="BT19"/>
+      <c r="BU19"/>
+      <c r="BV19"/>
+      <c r="BW19"/>
+      <c r="BX19"/>
+      <c r="BY19"/>
+      <c r="BZ19"/>
+      <c r="CA19"/>
+      <c r="CB19"/>
+      <c r="CC19"/>
+      <c r="CD19"/>
+      <c r="CE19"/>
+      <c r="CF19"/>
+      <c r="CG19"/>
+      <c r="CH19"/>
+      <c r="CI19"/>
+      <c r="CJ19"/>
+      <c r="CK19"/>
+      <c r="CL19"/>
+      <c r="CM19"/>
+      <c r="CN19"/>
+      <c r="CO19"/>
+      <c r="CP19"/>
+      <c r="CQ19"/>
+      <c r="CR19"/>
+      <c r="CS19"/>
+      <c r="CT19"/>
+      <c r="CU19"/>
+      <c r="CV19"/>
+      <c r="CW19"/>
+      <c r="CX19"/>
+      <c r="CY19"/>
+      <c r="CZ19"/>
+      <c r="DA19"/>
+      <c r="DB19"/>
+      <c r="DC19"/>
+      <c r="DD19"/>
+      <c r="DE19"/>
+      <c r="DF19"/>
+      <c r="DG19"/>
+      <c r="DH19"/>
+      <c r="DI19"/>
+      <c r="DJ19"/>
+      <c r="DK19"/>
+      <c r="DL19"/>
+      <c r="DM19"/>
+      <c r="DN19"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="11"/>
+    <row r="20" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A20" s="42"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="20">
-        <f>B2*N2+B3*N3+B4*N4+B5*N5+B6*N6+B7*N7+B8*N8+B9*N9+B10*N10+B11*N11+B12*N12+B13*N13+B14*N14+B15*N15+B16*N16+B17*N17+B18*N18+B19*N19</f>
+      <c r="B21" s="15">
+        <f>B2*N2+B3*N3+B4*N4+B17*N17+B6*N6+B12*N12+B8*N8+B9*N9+B16*N16+B5*N5+B11*N11+B10*N10+B7*N7+B13*N13+B14*N14+B15*N15+B18*N18+B19*N19</f>
         <v>5</v>
       </c>
       <c r="C21" s="3">
-        <f>C2*N2+C3*N3+C4*N4+C5*N5+C6*N6+C7*N7+C8*N8+C9*N9+C10*N10+C11*N11+C12*N12+C13*N13+C14*N14+C15*N15+C16*N16+C17*N17+C18*N18+C19*N19</f>
+        <f>C2*N2+C3*N3+C4*N4+C17*N17+C6*N6+C12*N12+C8*N8+C9*N9+C16*N16+C5*N5+C11*N11+C10*N10+C7*N7+C13*N13+C14*N14+C15*N15+C18*N18+C19*N19</f>
         <v>13.25</v>
       </c>
       <c r="D21" s="3">
-        <f>D2*N2+D3*N3+D4*N4+D5*N5+D6*N6+D7*N7+D8*N8+D9*N9+D10*N10+D11*N11+D12*N12+D13*N13+D14*N14+D15*N15+D16*N16+D17*N17+D18*N18+D19*N19</f>
+        <f>D2*N2+D3*N3+D4*N4+D17*N17+D6*N6+D12*N12+D8*N8+D9*N9+D16*N16+D5*N5+D11*N11+D10*N10+D7*N7+D13*N13+D14*N14+D15*N15+D18*N18+D19*N19</f>
         <v>18.46</v>
       </c>
       <c r="E21" s="3">
-        <f>E2*N2+E3*N3+E4*N4+E5*N5+E6*N6+E7*N7+E8*N8+E9*N9+E10*N10+E11*N11+E12*N12+E13*N13+E14*N14+E15*N15+E16*N16+E17*N17+E18*N18+E19*N19</f>
+        <f>E2*N2+E3*N3+E4*N4+E17*N17+E6*N6+E12*N12+E8*N8+E9*N9+E16*N16+E5*N5+E11*N11+E10*N10+E7*N7+E13*N13+E14*N14+E15*N15+E18*N18+E19*N19</f>
         <v>23.75</v>
       </c>
       <c r="F21" s="3">
-        <f>F2*N2+F3*N3+F4*N4+F5*N5+F6*N6+F7*N7+F8*N8+F9*N9+F10*N10+F11*N11+F12*N12+F13*N13+F14*N14+F15*N15+F16*N16+F17*N17+F18*N18+F19*N19</f>
+        <f>F2*N2+F3*N3+F4*N4+F17*N17+F6*N6+F12*N12+F8*N8+F9*N9+F16*N16+F5*N5+F11*N11+F10*N10+F7*N7+F13*N13+F14*N14+F15*N15+F18*N18+F19*N19</f>
         <v>34.35</v>
       </c>
       <c r="G21" s="3">
-        <f>G2*N2+G3*N3+G4*N4+G5*N5+G6*N6+G7*N7+G8*N8+G9*N9+G10*N10+G11*N11+G12*N12+G13*N13+G14*N14+G15*N15+G16*N16+G17*N17+G18*N18+G19*N19</f>
+        <f>G2*N2+G3*N3+G4*N4+G17*N17+G6*N6+G12*N12+G8*N8+G9*N9+G16*N16+G5*N5+G11*N11+G10*N10+G7*N7+G13*N13+G14*N14+G15*N15+G18*N18+G19*N19</f>
         <v>1.56</v>
       </c>
       <c r="H21" s="3">
-        <f>H2*N2+H3*N3+H4*N4+H5*N5+H6*N6+H7*N7+H8*N8+H9*N9+H10*N10+H11*N11+H12*N12+H13*N13+H14*N14+H15*N15+H16*N16+H17*N17+H18*N18+H19*N19</f>
+        <f>H2*N2+H3*N3+H4*N4+H17*N17+H6*N6+H12*N12+H8*N8+H9*N9+H16*N16+H5*N5+H11*N11+H10*N10+H7*N7+H13*N13+H14*N14+H15*N15+H18*N18+H19*N19</f>
         <v>5</v>
       </c>
       <c r="I21" s="3">
-        <f>I2*N2+I3*N3+I4*N4+I5*N5+I6*N6+I7*N7+I8*N8+I9*N9+I10*N10+I11*N11+I12*N12+I13*N13+I14*N14+I15*N15+I16*N16+I17*N17+I18*N18+I19*N19</f>
+        <f>I2*N2+I3*N3+I4*N4+I17*N17+I6*N6+I12*N12+I8*N8+I9*N9+I16*N16+I5*N5+I11*N11+I10*N10+I7*N7+I13*N13+I14*N14+I15*N15+I18*N18+I19*N19</f>
         <v>13.25</v>
       </c>
       <c r="J21" s="3">
-        <f>J2*N2+J3*N3+J4*N4+J5*N5+J6*N6+J7*N7+J8*N8+J9*N9+J10*N10+J11*N11+J12*N12+J13*N13+J14*N14+J15*N15+J16*N16+J17*N17+J18*N18+J19*N19</f>
+        <f>J2*N2+J3*N3+J4*N4+J17*N17+J6*N6+J12*N12+J8*N8+J9*N9+J16*N16+J5*N5+J11*N11+J10*N10+J7*N7+J13*N13+J14*N14+J15*N15+J18*N18+J19*N19</f>
         <v>8.9600000000000009</v>
       </c>
       <c r="K21" s="3">
-        <f>K2*N2+K3*N3+K4*N4+K5*N5+K6*N6+K7*N7+K8*N8+K9*N9+K10*N10+K11*N11+K12*N12+K13*N13+K14*N14+K15*N15+K16*N16+K17*N17+K18*N18+K19*N19</f>
+        <f>K2*N2+K3*N3+K4*N4+K17*N17+K6*N6+K12*N12+K8*N8+K9*N9+K16*N16+K5*N5+K11*N11+K10*N10+K7*N7+K13*N13+K14*N14+K15*N15+K18*N18+K19*N19</f>
         <v>5.75</v>
       </c>
       <c r="L21" s="3">
-        <f>L2*N2+L3*N3+L4*N4+L5*N5+L6*N6+L7*N7+L8*N8+L9*N9+L10*N10+L11*N11+L12*N12+L13*N13+L14*N14+L15*N15+L16*N16+L17*N17+L18*N18+L19*N19</f>
+        <f>L2*N2+L3*N3+L4*N4+L17*N17+L6*N6+L12*N12+L8*N8+L9*N9+L16*N16+L5*N5+L11*N11+L10*N10+L7*N7+L13*N13+L14*N14+L15*N15+L18*N18+L19*N19</f>
         <v>30.1</v>
       </c>
       <c r="M21" s="3">
-        <f>M2*N2+M3*N3+M4*N4+M5*N5+M6*N6+M7*N7+M8*N8+M9*N9+M10*N10+M11*N11+M12*N12+M13*N13+M14*N14+M15*N15+M16*N16+M17*N17+M18*N18+M19*N19</f>
+        <f>M2*N2+M3*N3+M4*N4+M17*N17+M6*N6+M12*N12+M8*N8+M9*N9+M16*N16+M5*N5+M11*N11+M10*N10+M7*N7+M13*N13+M14*N14+M15*N15+M18*N18+M19*N19</f>
         <v>1.56</v>
       </c>
       <c r="N21" s="3">
@@ -7823,1173 +8832,659 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10BA0FA-7F5A-4054-944A-818344D765CC}">
   <sheetPr codeName="Blad2"/>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s">
+      <c r="S1" s="10" t="s">
         <v>34</v>
       </c>
+      <c r="T1" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="16">
-        <f>Overview!B17</f>
-        <v>0</v>
-      </c>
-      <c r="C2" s="16">
-        <f>Overview!C17</f>
-        <v>0</v>
-      </c>
-      <c r="D2" s="16">
-        <f>Overview!D17</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="16">
-        <f>Overview!E17</f>
-        <v>14</v>
-      </c>
-      <c r="F2" s="16">
-        <f>Overview!F17</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="16">
-        <f>Overview!G17</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="16">
-        <f>Overview!H17</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="16">
-        <f>Overview!I17</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="16">
-        <f>Overview!J17</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="16">
-        <f>Overview!K17</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="16">
-        <f>Overview!L17</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="16">
-        <f>Overview!M17</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="16">
-        <f>Overview!N17</f>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="11">
+        <f>Overview!B2</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <f>Overview!C2</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="11">
+        <f>Overview!D2</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="11">
+        <f>Overview!E2</f>
+        <v>0.75</v>
+      </c>
+      <c r="F2" s="11">
+        <f>Overview!F2</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="11">
+        <f>Overview!G2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="11">
+        <f>Overview!H2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11">
+        <f>Overview!I2</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="11">
+        <f>Overview!J2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="11">
+        <f>Overview!K2</f>
+        <v>0.75</v>
+      </c>
+      <c r="L2" s="11">
+        <f>Overview!L2</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="11">
+        <f>Overview!M2</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="11">
+        <f>Overview!N2</f>
         <v>1</v>
       </c>
-      <c r="O2" s="16">
-        <f>Overview!O17</f>
-        <v>14</v>
-      </c>
-      <c r="P2" s="14">
-        <f>Overview!P17</f>
-        <v>133.38</v>
-      </c>
-      <c r="U2">
-        <f>SUM(O2:O18)</f>
-        <v>159.15</v>
+      <c r="O2" s="11">
+        <f>Overview!O2</f>
+        <v>1.5</v>
+      </c>
+      <c r="P2" s="39">
+        <f>Overview!P2</f>
+        <v>86.46</v>
+      </c>
+      <c r="S2">
+        <v>2</v>
+      </c>
+      <c r="T2">
+        <v>2000</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="2">
         <f>Overview!B3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="2">
         <f>Overview!C3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="2">
         <f>Overview!D3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="2">
         <f>Overview!E3</f>
         <v>0</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="2">
         <f>Overview!F3</f>
         <v>4.8499999999999996</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="2">
         <f>Overview!G3</f>
         <v>0</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="2">
         <f>Overview!H3</f>
         <v>0</v>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="2">
         <f>Overview!I3</f>
         <v>0</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="2">
         <f>Overview!J3</f>
         <v>0</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="2">
         <f>Overview!K3</f>
         <v>0</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="2">
         <f>Overview!L3</f>
         <v>4.8499999999999996</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="2">
         <f>Overview!M3</f>
         <v>0</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="2">
         <f>Overview!N3</f>
         <v>1</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="2">
         <f>Overview!O3</f>
         <v>9.6999999999999993</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="9">
         <f>Overview!P3</f>
         <v>137.65</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="18">
-        <f>Overview!B18</f>
-        <v>0</v>
-      </c>
-      <c r="C4" s="18">
-        <f>Overview!C18</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="18">
-        <f>Overview!D18</f>
-        <v>18</v>
-      </c>
-      <c r="E4" s="18">
-        <f>Overview!E18</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="18">
-        <f>Overview!F18</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="18">
-        <f>Overview!G18</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="18">
-        <f>Overview!H18</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="18">
-        <f>Overview!I18</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="18">
-        <f>Overview!J18</f>
-        <v>8.5</v>
-      </c>
-      <c r="K4" s="18">
-        <f>Overview!K18</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="18">
-        <f>Overview!L18</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="18">
-        <f>Overview!M18</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="18">
-        <f>Overview!N18</f>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1">
+        <f>Overview!B4</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="1">
+        <f>Overview!C4</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1">
+        <f>Overview!D4</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="1">
+        <f>Overview!E4</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="1">
+        <f>Overview!F4</f>
+        <v>8</v>
+      </c>
+      <c r="G4" s="1">
+        <f>Overview!G4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="1">
+        <f>Overview!H4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="1">
+        <f>Overview!I4</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="1">
+        <f>Overview!J4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <f>Overview!K4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="1">
+        <f>Overview!L4</f>
+        <v>4</v>
+      </c>
+      <c r="M4" s="1">
+        <f>Overview!M4</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <f>Overview!N4</f>
         <v>1</v>
       </c>
-      <c r="O4" s="18">
-        <f>Overview!O18</f>
-        <v>26.5</v>
-      </c>
-      <c r="P4" s="14">
-        <f>Overview!P18</f>
-        <v>991.4</v>
+      <c r="O4" s="1">
+        <f>Overview!O4</f>
+        <v>12</v>
+      </c>
+      <c r="P4" s="39">
+        <f>Overview!P4</f>
+        <v>506.2</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="13">
+        <f>Overview!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="13">
+        <f>Overview!C5</f>
+        <v>5.5</v>
+      </c>
+      <c r="D5" s="13">
+        <f>Overview!D5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="13">
+        <f>Overview!E5</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="13">
+        <f>Overview!F5</f>
+        <v>5.5</v>
+      </c>
+      <c r="G5" s="13">
+        <f>Overview!G5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
+        <f>Overview!H5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="13">
+        <f>Overview!I5</f>
+        <v>5.5</v>
+      </c>
+      <c r="J5" s="13">
+        <f>Overview!J5</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="13">
+        <f>Overview!K5</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="13">
+        <f>Overview!L5</f>
+        <v>5.5</v>
+      </c>
+      <c r="M5" s="13">
+        <f>Overview!M5</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="13">
+        <f>Overview!N5</f>
+        <v>1</v>
+      </c>
+      <c r="O5" s="13">
+        <f>Overview!O5</f>
+        <v>22</v>
+      </c>
+      <c r="P5" s="8">
+        <f>Overview!P5</f>
+        <v>595</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1">
+        <f>Overview!B6</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="1">
+        <f>Overview!C6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <f>Overview!D6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <f>Overview!E6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <f>Overview!F6</f>
+        <v>4</v>
+      </c>
+      <c r="G6" s="1">
+        <f>Overview!G6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <f>Overview!H6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <f>Overview!I6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <f>Overview!J6</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <f>Overview!K6</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <f>Overview!L6</f>
+        <v>4</v>
+      </c>
+      <c r="M6" s="1">
+        <f>Overview!M6</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <f>Overview!N6</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="1">
+        <f>Overview!O6</f>
+        <v>8</v>
+      </c>
+      <c r="P6" s="39">
+        <f>Overview!P6</f>
+        <v>263.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="2">
+        <f>Overview!B7</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <f>Overview!C7</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="2">
+        <f>Overview!D7</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <f>Overview!E7</f>
+        <v>3.15</v>
+      </c>
+      <c r="F7" s="2">
+        <f>Overview!F7</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="2">
+        <f>Overview!G7</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <f>Overview!H7</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <f>Overview!I7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="2">
+        <f>Overview!J7</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="2">
+        <f>Overview!K7</f>
+        <v>3.15</v>
+      </c>
+      <c r="L7" s="2">
+        <f>Overview!L7</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <f>Overview!M7</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
+        <f>Overview!N7</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <f>Overview!O7</f>
+        <v>0</v>
+      </c>
+      <c r="P7" s="9">
+        <f>Overview!P7</f>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B8" s="11">
         <f>Overview!B8</f>
         <v>0</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C8" s="11">
         <f>Overview!C8</f>
         <v>6</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D8" s="11">
         <f>Overview!D8</f>
         <v>0</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E8" s="11">
         <f>Overview!E8</f>
         <v>0</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F8" s="11">
         <f>Overview!F8</f>
         <v>6</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G8" s="11">
         <f>Overview!G8</f>
         <v>0</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H8" s="11">
         <f>Overview!H8</f>
         <v>0</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I8" s="11">
         <f>Overview!I8</f>
         <v>6</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J8" s="11">
         <f>Overview!J8</f>
         <v>0</v>
       </c>
-      <c r="K5" s="18">
+      <c r="K8" s="11">
         <f>Overview!K8</f>
         <v>0</v>
       </c>
-      <c r="L5" s="18">
+      <c r="L8" s="11">
         <f>Overview!L8</f>
         <v>6</v>
       </c>
-      <c r="M5" s="18">
+      <c r="M8" s="11">
         <f>Overview!M8</f>
         <v>0</v>
       </c>
-      <c r="N5" s="18">
+      <c r="N8" s="11">
         <f>Overview!N8</f>
         <v>1</v>
       </c>
-      <c r="O5" s="18">
+      <c r="O8" s="11">
         <f>Overview!O8</f>
         <v>24</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P8" s="39">
         <f>Overview!P8</f>
         <v>305.7</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="18">
-        <f>Overview!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="18">
-        <f>Overview!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="18">
-        <f>Overview!D12</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="18">
-        <f>Overview!E12</f>
-        <v>4</v>
-      </c>
-      <c r="F6" s="18">
-        <f>Overview!F12</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="18">
-        <f>Overview!G12</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="18">
-        <f>Overview!H12</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="18">
-        <f>Overview!I12</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="18">
-        <f>Overview!J12</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="18">
-        <f>Overview!K12</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="18">
-        <f>Overview!L12</f>
-        <v>4</v>
-      </c>
-      <c r="M6" s="18">
-        <f>Overview!M12</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="18">
-        <f>Overview!N12</f>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="2">
+        <f>Overview!B9</f>
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <f>Overview!C9</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <f>Overview!D9</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <f>Overview!E9</f>
+        <v>5</v>
+      </c>
+      <c r="F9" s="2">
+        <f>Overview!F9</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <f>Overview!G9</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <f>Overview!H9</f>
+        <v>5</v>
+      </c>
+      <c r="I9" s="2">
+        <f>Overview!I9</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <f>Overview!J9</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="2">
+        <f>Overview!K9</f>
+        <v>5</v>
+      </c>
+      <c r="L9" s="2">
+        <f>Overview!L9</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
+        <f>Overview!M9</f>
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
+        <f>Overview!N9</f>
         <v>1</v>
       </c>
-      <c r="O6" s="18">
-        <f>Overview!O12</f>
-        <v>8</v>
-      </c>
-      <c r="P6" s="14">
-        <f>Overview!P12</f>
-        <v>161</v>
+      <c r="O9" s="2">
+        <f>Overview!O9</f>
+        <v>20</v>
+      </c>
+      <c r="P9" s="9">
+        <f>Overview!P9</f>
+        <v>301.3</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="18">
-        <f>Overview!B2</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="18">
-        <f>Overview!C2</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="18">
-        <f>Overview!D2</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="18">
-        <f>Overview!E2</f>
-        <v>0.75</v>
-      </c>
-      <c r="F7" s="18">
-        <f>Overview!F2</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="18">
-        <f>Overview!G2</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="18">
-        <f>Overview!H2</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="18">
-        <f>Overview!I2</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="18">
-        <f>Overview!J2</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="18">
-        <f>Overview!K2</f>
-        <v>0.75</v>
-      </c>
-      <c r="L7" s="18">
-        <f>Overview!L2</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="18">
-        <f>Overview!M2</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="18">
-        <f>Overview!N2</f>
-        <v>1</v>
-      </c>
-      <c r="O7" s="18">
-        <f>Overview!O2</f>
-        <v>1.5</v>
-      </c>
-      <c r="P7" s="14">
-        <f>Overview!P2</f>
-        <v>86.46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="16">
-        <f>Overview!B7</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="16">
-        <f>Overview!C7</f>
-        <v>1.75</v>
-      </c>
-      <c r="D8" s="16">
-        <f>Overview!D7</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="16">
-        <f>Overview!E7</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="16">
-        <f>Overview!F7</f>
-        <v>1.75</v>
-      </c>
-      <c r="G8" s="16">
-        <f>Overview!G7</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="16">
-        <f>Overview!H7</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="16">
-        <f>Overview!I7</f>
-        <v>1.75</v>
-      </c>
-      <c r="J8" s="16">
-        <f>Overview!J7</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="16">
-        <f>Overview!K7</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="16">
-        <f>Overview!L7</f>
-        <v>1.75</v>
-      </c>
-      <c r="M8" s="16">
-        <f>Overview!M7</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="16">
-        <f>Overview!N7</f>
-        <v>1</v>
-      </c>
-      <c r="O8" s="16">
-        <f>Overview!O7</f>
-        <v>7</v>
-      </c>
-      <c r="P8" s="14">
-        <f>Overview!P7</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="16">
-        <f>Overview!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="16">
-        <f>Overview!C5</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="16">
-        <f>Overview!D5</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="16">
-        <f>Overview!E5</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="16">
-        <f>Overview!F5</f>
-        <v>2</v>
-      </c>
-      <c r="G9" s="16">
-        <f>Overview!G5</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="16">
-        <f>Overview!H5</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="16">
-        <f>Overview!I5</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="16">
-        <f>Overview!J5</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="16">
-        <f>Overview!K5</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="16">
-        <f>Overview!L5</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="16">
-        <f>Overview!M5</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="16">
-        <f>Overview!N5</f>
-        <v>1</v>
-      </c>
-      <c r="O9" s="16">
-        <f>Overview!O5</f>
-        <v>2</v>
-      </c>
-      <c r="P9" s="14">
-        <f>Overview!P5</f>
-        <v>26.46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="18">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="1">
         <f>Overview!B10</f>
         <v>0</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="1">
         <f>Overview!C10</f>
         <v>0</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="1">
         <f>Overview!D10</f>
         <v>0</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="1">
         <f>Overview!E10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="1">
         <f>Overview!F10</f>
-        <v>2.25</v>
-      </c>
-      <c r="G10" s="18">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
         <f>Overview!G10</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="H10" s="1">
         <f>Overview!H10</f>
         <v>0</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="1">
         <f>Overview!I10</f>
         <v>0</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="1">
         <f>Overview!J10</f>
         <v>0</v>
       </c>
-      <c r="K10" s="18">
+      <c r="K10" s="1">
         <f>Overview!K10</f>
         <v>0</v>
       </c>
-      <c r="L10" s="18">
+      <c r="L10" s="1">
         <f>Overview!L10</f>
         <v>0</v>
       </c>
-      <c r="M10" s="18">
+      <c r="M10" s="1">
         <f>Overview!M10</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="N10" s="1">
         <f>Overview!N10</f>
         <v>1</v>
       </c>
-      <c r="O10" s="18">
+      <c r="O10" s="1">
         <f>Overview!O10</f>
-        <v>2.25</v>
-      </c>
-      <c r="P10" s="14">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="P10" s="39">
         <f>Overview!P10</f>
-        <v>172.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="16">
-        <f>Overview!B9</f>
-        <v>5</v>
-      </c>
-      <c r="C11" s="16">
-        <f>Overview!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="16">
-        <f>Overview!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="16">
-        <f>Overview!E9</f>
-        <v>5</v>
-      </c>
-      <c r="F11" s="16">
-        <f>Overview!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="16">
-        <f>Overview!G9</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="16">
-        <f>Overview!H9</f>
-        <v>5</v>
-      </c>
-      <c r="I11" s="16">
-        <f>Overview!I9</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="16">
-        <f>Overview!J9</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="16">
-        <f>Overview!K9</f>
-        <v>5</v>
-      </c>
-      <c r="L11" s="16">
-        <f>Overview!L9</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="16">
-        <f>Overview!M9</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="16">
-        <f>Overview!N9</f>
-        <v>1</v>
-      </c>
-      <c r="O11" s="16">
-        <f>Overview!O9</f>
-        <v>20</v>
-      </c>
-      <c r="P11" s="13">
-        <f>Overview!P9</f>
-        <v>301.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="18">
-        <f>Overview!B4</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="18">
-        <f>Overview!C4</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="18">
-        <f>Overview!D4</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="18">
-        <f>Overview!E4</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="18">
-        <f>Overview!F4</f>
-        <v>8</v>
-      </c>
-      <c r="G12" s="18">
-        <f>Overview!G4</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="18">
-        <f>Overview!H4</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
-        <f>Overview!I4</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
-        <f>Overview!J4</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="18">
-        <f>Overview!K4</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="18">
-        <f>Overview!L4</f>
-        <v>4</v>
-      </c>
-      <c r="M12" s="18">
-        <f>Overview!M4</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <f>Overview!N4</f>
-        <v>1</v>
-      </c>
-      <c r="O12" s="18">
-        <f>Overview!O4</f>
-        <v>12</v>
-      </c>
-      <c r="P12" s="14">
-        <f>Overview!P4</f>
-        <v>506.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="16">
-        <f>Overview!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="16">
-        <f>Overview!C13</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="16">
-        <f>Overview!D13</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <f>Overview!E13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
-        <f>Overview!F13</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="16">
-        <f>Overview!G13</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H13" s="16">
-        <f>Overview!H13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="16">
-        <f>Overview!I13</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="16">
-        <f>Overview!J13</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="16">
-        <f>Overview!K13</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="16">
-        <f>Overview!L13</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="16">
-        <f>Overview!M13</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="N13" s="16">
-        <f>Overview!N13</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="16">
-        <f>Overview!O13</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P13" s="14">
-        <f>Overview!P13</f>
         <v>184.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="16">
-        <f>Overview!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="16">
-        <f>Overview!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="16">
-        <f>Overview!D15</f>
-        <v>3.25</v>
-      </c>
-      <c r="E14" s="16">
-        <f>Overview!E15</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="16">
-        <f>Overview!F15</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="16">
-        <f>Overview!G15</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="16">
-        <f>Overview!H15</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="16">
-        <f>Overview!I15</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="16">
-        <f>Overview!J15</f>
-        <v>3.25</v>
-      </c>
-      <c r="K14" s="16">
-        <f>Overview!K15</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="16">
-        <f>Overview!L15</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="16">
-        <f>Overview!M15</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="16">
-        <f>Overview!N15</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="16">
-        <f>Overview!O15</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f>Overview!P15</f>
-        <v>176.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="18">
-        <f>Overview!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="18">
-        <f>Overview!C16</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="18">
-        <f>Overview!D16</f>
-        <v>3.5</v>
-      </c>
-      <c r="E15" s="18">
-        <f>Overview!E16</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="18">
-        <f>Overview!F16</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="18">
-        <f>Overview!G16</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="18">
-        <f>Overview!H16</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <f>Overview!I16</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="18">
-        <f>Overview!J16</f>
-        <v>3.5</v>
-      </c>
-      <c r="K15" s="18">
-        <f>Overview!K16</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <f>Overview!L16</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="18">
-        <f>Overview!M16</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <f>Overview!N16</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="18">
-        <f>Overview!O16</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="14">
-        <f>Overview!P16</f>
-        <v>201.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="18">
-        <f>Overview!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="18">
-        <f>Overview!C6</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="18">
-        <f>Overview!D6</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="18">
-        <f>Overview!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="18">
-        <f>Overview!F6</f>
-        <v>4</v>
-      </c>
-      <c r="G16" s="18">
-        <f>Overview!G6</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="18">
-        <f>Overview!H6</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="18">
-        <f>Overview!I6</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="18">
-        <f>Overview!J6</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="18">
-        <f>Overview!K6</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="18">
-        <f>Overview!L6</f>
-        <v>4</v>
-      </c>
-      <c r="M16" s="18">
-        <f>Overview!M6</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="18">
-        <f>Overview!N6</f>
-        <v>1</v>
-      </c>
-      <c r="O16" s="18">
-        <f>Overview!O6</f>
-        <v>8</v>
-      </c>
-      <c r="P16" s="14">
-        <f>Overview!P6</f>
-        <v>263.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="18">
-        <f>Overview!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="18">
-        <f>Overview!C14</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="18">
-        <f>Overview!D14</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="18">
-        <f>Overview!E14</f>
-        <v>3.15</v>
-      </c>
-      <c r="F17" s="18">
-        <f>Overview!F14</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="18">
-        <f>Overview!G14</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="18">
-        <f>Overview!H14</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="18">
-        <f>Overview!I14</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="18">
-        <f>Overview!J14</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="18">
-        <f>Overview!K14</f>
-        <v>3.15</v>
-      </c>
-      <c r="L17" s="18">
-        <f>Overview!L14</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="18">
-        <f>Overview!M14</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="18">
-        <f>Overview!N14</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="18">
-        <f>Overview!O14</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="14">
-        <f>Overview!P14</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="16">
-        <f>Overview!B11</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="16">
-        <f>Overview!C11</f>
-        <v>5.5</v>
-      </c>
-      <c r="D18" s="16">
-        <f>Overview!D11</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="16">
-        <f>Overview!E11</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="16">
-        <f>Overview!F11</f>
-        <v>5.5</v>
-      </c>
-      <c r="G18" s="16">
-        <f>Overview!G11</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="16">
-        <f>Overview!H11</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="16">
-        <f>Overview!I11</f>
-        <v>5.5</v>
-      </c>
-      <c r="J18" s="16">
-        <f>Overview!J11</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="16">
-        <f>Overview!K11</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="16">
-        <f>Overview!L11</f>
-        <v>5.5</v>
-      </c>
-      <c r="M18" s="16">
-        <f>Overview!M11</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="16">
-        <f>Overview!N11</f>
-        <v>1</v>
-      </c>
-      <c r="O18" s="16">
-        <f>Overview!O11</f>
-        <v>22</v>
-      </c>
-      <c r="P18" s="14">
-        <f>Overview!P11</f>
-        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -8999,1173 +9494,659 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1485E3A-19D0-47B9-867F-49E3EDE141F8}">
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="J1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="15" t="s">
+      <c r="K1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="M1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="15" t="s">
+      <c r="O1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="U1" t="s">
+      <c r="S1" s="10" t="s">
         <v>34</v>
       </c>
+      <c r="T1" s="10" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="19">
+        <f>Overview!B11</f>
+        <v>0</v>
+      </c>
+      <c r="C2" s="19">
+        <f>Overview!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D2" s="19">
+        <f>Overview!D11</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="19">
+        <f>Overview!E11</f>
+        <v>4</v>
+      </c>
+      <c r="F2" s="19">
+        <f>Overview!F11</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="19">
+        <f>Overview!G11</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="19">
+        <f>Overview!H11</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="19">
+        <f>Overview!I11</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="19">
+        <f>Overview!J11</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="19">
+        <f>Overview!K11</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="19">
+        <f>Overview!L11</f>
+        <v>4</v>
+      </c>
+      <c r="M2" s="19">
+        <f>Overview!M11</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="19">
+        <f>Overview!N11</f>
+        <v>1</v>
+      </c>
+      <c r="O2" s="19">
+        <f>Overview!O11</f>
+        <v>8</v>
+      </c>
+      <c r="P2" s="20">
+        <f>Overview!P11</f>
+        <v>161</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="23">
+        <f>Overview!B12</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="23">
+        <f>Overview!C12</f>
+        <v>1.75</v>
+      </c>
+      <c r="D3" s="23">
+        <f>Overview!D12</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="23">
+        <f>Overview!E12</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="23">
+        <f>Overview!F12</f>
+        <v>1.75</v>
+      </c>
+      <c r="G3" s="23">
+        <f>Overview!G12</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="23">
+        <f>Overview!H12</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="23">
+        <f>Overview!I12</f>
+        <v>1.75</v>
+      </c>
+      <c r="J3" s="23">
+        <f>Overview!J12</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="23">
+        <f>Overview!K12</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="23">
+        <f>Overview!L12</f>
+        <v>1.75</v>
+      </c>
+      <c r="M3" s="23">
+        <f>Overview!M12</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="23">
+        <f>Overview!N12</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="23">
+        <f>Overview!O12</f>
+        <v>7</v>
+      </c>
+      <c r="P3" s="24">
+        <f>Overview!P12</f>
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="19">
+        <f>Overview!B13</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="19">
+        <f>Overview!C13</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="19">
+        <f>Overview!D13</f>
+        <v>3.25</v>
+      </c>
+      <c r="E4" s="19">
+        <f>Overview!E13</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="19">
+        <f>Overview!F13</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="19">
+        <f>Overview!G13</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="19">
+        <f>Overview!H13</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="19">
+        <f>Overview!I13</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="19">
+        <f>Overview!J13</f>
+        <v>3.25</v>
+      </c>
+      <c r="K4" s="19">
+        <f>Overview!K13</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="19">
+        <f>Overview!L13</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="19">
+        <f>Overview!M13</f>
+        <v>0</v>
+      </c>
+      <c r="N4" s="19">
+        <f>Overview!N13</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="19">
+        <f>Overview!O13</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="20">
+        <f>Overview!P13</f>
+        <v>176.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="23">
+        <f>Overview!B14</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="23">
+        <f>Overview!C14</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="23">
+        <f>Overview!D14</f>
+        <v>3.5</v>
+      </c>
+      <c r="E5" s="23">
+        <f>Overview!E14</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="23">
+        <f>Overview!F14</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="23">
+        <f>Overview!G14</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="23">
+        <f>Overview!H14</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="23">
+        <f>Overview!I14</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="23">
+        <f>Overview!J14</f>
+        <v>3.5</v>
+      </c>
+      <c r="K5" s="23">
+        <f>Overview!K14</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="23">
+        <f>Overview!L14</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="23">
+        <f>Overview!M14</f>
+        <v>0</v>
+      </c>
+      <c r="N5" s="23">
+        <f>Overview!N14</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="23">
+        <f>Overview!O14</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="35">
+        <f>Overview!P14</f>
+        <v>201.8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="16">
+      <c r="B6" s="19">
+        <f>Overview!B15</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="19">
+        <f>Overview!C15</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="19">
+        <f>Overview!D15</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="19">
+        <f>Overview!E15</f>
+        <v>14</v>
+      </c>
+      <c r="F6" s="19">
+        <f>Overview!F15</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="19">
+        <f>Overview!G15</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="19">
+        <f>Overview!H15</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="19">
+        <f>Overview!I15</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="19">
+        <f>Overview!J15</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="19">
+        <f>Overview!K15</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="19">
+        <f>Overview!L15</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="19">
+        <f>Overview!M15</f>
+        <v>0</v>
+      </c>
+      <c r="N6" s="19">
+        <f>Overview!N15</f>
+        <v>1</v>
+      </c>
+      <c r="O6" s="19">
+        <f>Overview!O15</f>
+        <v>14</v>
+      </c>
+      <c r="P6" s="20">
+        <f>Overview!P15</f>
+        <v>133.38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="23">
+        <f>Overview!B16</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="23">
+        <f>Overview!C16</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="23">
+        <f>Overview!D16</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="23">
+        <f>Overview!E16</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="23">
+        <f>Overview!F16</f>
+        <v>2.25</v>
+      </c>
+      <c r="G7" s="23">
+        <f>Overview!G16</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="23">
+        <f>Overview!H16</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="23">
+        <f>Overview!I16</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="23">
+        <f>Overview!J16</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="23">
+        <f>Overview!K16</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="23">
+        <f>Overview!L16</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="23">
+        <f>Overview!M16</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="23">
+        <f>Overview!N16</f>
+        <v>1</v>
+      </c>
+      <c r="O7" s="23">
+        <f>Overview!O16</f>
+        <v>2.25</v>
+      </c>
+      <c r="P7" s="24">
+        <f>Overview!P16</f>
+        <v>172.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="19">
         <f>Overview!B17</f>
         <v>0</v>
       </c>
-      <c r="C2" s="16">
+      <c r="C8" s="19">
         <f>Overview!C17</f>
         <v>0</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D8" s="19">
         <f>Overview!D17</f>
         <v>0</v>
       </c>
-      <c r="E2" s="16">
+      <c r="E8" s="19">
         <f>Overview!E17</f>
-        <v>14</v>
-      </c>
-      <c r="F2" s="16">
+        <v>0</v>
+      </c>
+      <c r="F8" s="19">
         <f>Overview!F17</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="16">
+        <v>2</v>
+      </c>
+      <c r="G8" s="19">
         <f>Overview!G17</f>
         <v>0</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H8" s="19">
         <f>Overview!H17</f>
         <v>0</v>
       </c>
-      <c r="I2" s="16">
+      <c r="I8" s="19">
         <f>Overview!I17</f>
         <v>0</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J8" s="19">
         <f>Overview!J17</f>
         <v>0</v>
       </c>
-      <c r="K2" s="16">
+      <c r="K8" s="19">
         <f>Overview!K17</f>
         <v>0</v>
       </c>
-      <c r="L2" s="16">
+      <c r="L8" s="19">
         <f>Overview!L17</f>
         <v>0</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M8" s="19">
         <f>Overview!M17</f>
         <v>0</v>
       </c>
-      <c r="N2" s="16">
+      <c r="N8" s="19">
         <f>Overview!N17</f>
         <v>1</v>
       </c>
-      <c r="O2" s="16">
+      <c r="O8" s="19">
         <f>Overview!O17</f>
-        <v>14</v>
-      </c>
-      <c r="P2" s="14">
+        <v>2</v>
+      </c>
+      <c r="P8" s="20">
         <f>Overview!P17</f>
-        <v>133.38</v>
-      </c>
-      <c r="U2">
-        <f>SUM(O2:O18)</f>
-        <v>159.15</v>
+        <v>26.46</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="16">
-        <f>Overview!B3</f>
-        <v>0</v>
-      </c>
-      <c r="C3" s="16">
-        <f>Overview!C3</f>
-        <v>0</v>
-      </c>
-      <c r="D3" s="16">
-        <f>Overview!D3</f>
-        <v>0</v>
-      </c>
-      <c r="E3" s="16">
-        <f>Overview!E3</f>
-        <v>0</v>
-      </c>
-      <c r="F3" s="16">
-        <f>Overview!F3</f>
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="G3" s="16">
-        <f>Overview!G3</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
-        <f>Overview!H3</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="16">
-        <f>Overview!I3</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="16">
-        <f>Overview!J3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="16">
-        <f>Overview!K3</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="16">
-        <f>Overview!L3</f>
-        <v>4.8499999999999996</v>
-      </c>
-      <c r="M3" s="16">
-        <f>Overview!M3</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="16">
-        <f>Overview!N3</f>
-        <v>1</v>
-      </c>
-      <c r="O3" s="16">
-        <f>Overview!O3</f>
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="P3" s="14">
-        <f>Overview!P3</f>
-        <v>137.65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B9" s="23">
         <f>Overview!B18</f>
         <v>0</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C9" s="23">
         <f>Overview!C18</f>
         <v>0</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D9" s="23">
         <f>Overview!D18</f>
         <v>18</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E9" s="23">
         <f>Overview!E18</f>
         <v>0</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F9" s="23">
         <f>Overview!F18</f>
         <v>0</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G9" s="23">
         <f>Overview!G18</f>
         <v>0</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H9" s="23">
         <f>Overview!H18</f>
         <v>0</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I9" s="23">
         <f>Overview!I18</f>
         <v>0</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J9" s="23">
         <f>Overview!J18</f>
         <v>8.5</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K9" s="23">
         <f>Overview!K18</f>
         <v>0</v>
       </c>
-      <c r="L4" s="18">
+      <c r="L9" s="23">
         <f>Overview!L18</f>
         <v>0</v>
       </c>
-      <c r="M4" s="18">
+      <c r="M9" s="23">
         <f>Overview!M18</f>
         <v>0</v>
       </c>
-      <c r="N4" s="18">
+      <c r="N9" s="23">
         <f>Overview!N18</f>
         <v>1</v>
       </c>
-      <c r="O4" s="18">
+      <c r="O9" s="23">
         <f>Overview!O18</f>
         <v>26.5</v>
       </c>
-      <c r="P4" s="14">
+      <c r="P9" s="24">
         <f>Overview!P18</f>
         <v>991.4</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="18">
-        <f>Overview!B8</f>
-        <v>0</v>
-      </c>
-      <c r="C5" s="18">
-        <f>Overview!C8</f>
-        <v>6</v>
-      </c>
-      <c r="D5" s="18">
-        <f>Overview!D8</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="18">
-        <f>Overview!E8</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="18">
-        <f>Overview!F8</f>
-        <v>6</v>
-      </c>
-      <c r="G5" s="18">
-        <f>Overview!G8</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="18">
-        <f>Overview!H8</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="18">
-        <f>Overview!I8</f>
-        <v>6</v>
-      </c>
-      <c r="J5" s="18">
-        <f>Overview!J8</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="18">
-        <f>Overview!K8</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="18">
-        <f>Overview!L8</f>
-        <v>6</v>
-      </c>
-      <c r="M5" s="18">
-        <f>Overview!M8</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="18">
-        <f>Overview!N8</f>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" s="33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="19">
+        <f>Overview!B19</f>
+        <v>0</v>
+      </c>
+      <c r="C10" s="19">
+        <f>Overview!C19</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="19">
+        <f>Overview!D19</f>
+        <v>0.46</v>
+      </c>
+      <c r="E10" s="19">
+        <f>Overview!E19</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="19">
+        <f>Overview!F19</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="19">
+        <f>Overview!G19</f>
+        <v>0.46</v>
+      </c>
+      <c r="H10" s="19">
+        <f>Overview!H19</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="19">
+        <f>Overview!I19</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="19">
+        <f>Overview!J19</f>
+        <v>0.46</v>
+      </c>
+      <c r="K10" s="19">
+        <f>Overview!K19</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="19">
+        <f>Overview!L19</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="19">
+        <f>Overview!M19</f>
+        <v>0.46</v>
+      </c>
+      <c r="N10" s="19">
+        <f>Overview!N19</f>
         <v>1</v>
       </c>
-      <c r="O5" s="18">
-        <f>Overview!O8</f>
-        <v>24</v>
-      </c>
-      <c r="P5" s="13">
-        <f>Overview!P8</f>
-        <v>305.7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="18">
-        <f>Overview!B12</f>
-        <v>0</v>
-      </c>
-      <c r="C6" s="18">
-        <f>Overview!C12</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="18">
-        <f>Overview!D12</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="18">
-        <f>Overview!E12</f>
-        <v>4</v>
-      </c>
-      <c r="F6" s="18">
-        <f>Overview!F12</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="18">
-        <f>Overview!G12</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="18">
-        <f>Overview!H12</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="18">
-        <f>Overview!I12</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="18">
-        <f>Overview!J12</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="18">
-        <f>Overview!K12</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="18">
-        <f>Overview!L12</f>
-        <v>4</v>
-      </c>
-      <c r="M6" s="18">
-        <f>Overview!M12</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="18">
-        <f>Overview!N12</f>
-        <v>1</v>
-      </c>
-      <c r="O6" s="18">
-        <f>Overview!O12</f>
-        <v>8</v>
-      </c>
-      <c r="P6" s="14">
-        <f>Overview!P12</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="18">
-        <f>Overview!B2</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="18">
-        <f>Overview!C2</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="18">
-        <f>Overview!D2</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="18">
-        <f>Overview!E2</f>
-        <v>0.75</v>
-      </c>
-      <c r="F7" s="18">
-        <f>Overview!F2</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="18">
-        <f>Overview!G2</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="18">
-        <f>Overview!H2</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="18">
-        <f>Overview!I2</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="18">
-        <f>Overview!J2</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="18">
-        <f>Overview!K2</f>
-        <v>0.75</v>
-      </c>
-      <c r="L7" s="18">
-        <f>Overview!L2</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="18">
-        <f>Overview!M2</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="18">
-        <f>Overview!N2</f>
-        <v>1</v>
-      </c>
-      <c r="O7" s="18">
-        <f>Overview!O2</f>
-        <v>1.5</v>
-      </c>
-      <c r="P7" s="14">
-        <f>Overview!P2</f>
-        <v>86.46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="16">
-        <f>Overview!B7</f>
-        <v>0</v>
-      </c>
-      <c r="C8" s="16">
-        <f>Overview!C7</f>
-        <v>1.75</v>
-      </c>
-      <c r="D8" s="16">
-        <f>Overview!D7</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="16">
-        <f>Overview!E7</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="16">
-        <f>Overview!F7</f>
-        <v>1.75</v>
-      </c>
-      <c r="G8" s="16">
-        <f>Overview!G7</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="16">
-        <f>Overview!H7</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="16">
-        <f>Overview!I7</f>
-        <v>1.75</v>
-      </c>
-      <c r="J8" s="16">
-        <f>Overview!J7</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="16">
-        <f>Overview!K7</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="16">
-        <f>Overview!L7</f>
-        <v>1.75</v>
-      </c>
-      <c r="M8" s="16">
-        <f>Overview!M7</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="16">
-        <f>Overview!N7</f>
-        <v>1</v>
-      </c>
-      <c r="O8" s="16">
-        <f>Overview!O7</f>
-        <v>7</v>
-      </c>
-      <c r="P8" s="14">
-        <f>Overview!P7</f>
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="16">
-        <f>Overview!B5</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="16">
-        <f>Overview!C5</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="16">
-        <f>Overview!D5</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="16">
-        <f>Overview!E5</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="16">
-        <f>Overview!F5</f>
-        <v>2</v>
-      </c>
-      <c r="G9" s="16">
-        <f>Overview!G5</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="16">
-        <f>Overview!H5</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="16">
-        <f>Overview!I5</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="16">
-        <f>Overview!J5</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="16">
-        <f>Overview!K5</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="16">
-        <f>Overview!L5</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="16">
-        <f>Overview!M5</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="16">
-        <f>Overview!N5</f>
-        <v>1</v>
-      </c>
-      <c r="O9" s="16">
-        <f>Overview!O5</f>
-        <v>2</v>
-      </c>
-      <c r="P9" s="14">
-        <f>Overview!P5</f>
-        <v>26.46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="18">
-        <f>Overview!B10</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="18">
-        <f>Overview!C10</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="18">
-        <f>Overview!D10</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="18">
-        <f>Overview!E10</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="18">
-        <f>Overview!F10</f>
-        <v>2.25</v>
-      </c>
-      <c r="G10" s="18">
-        <f>Overview!G10</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="18">
-        <f>Overview!H10</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="18">
-        <f>Overview!I10</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="18">
-        <f>Overview!J10</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="18">
-        <f>Overview!K10</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="18">
-        <f>Overview!L10</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="18">
-        <f>Overview!M10</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="18">
-        <f>Overview!N10</f>
-        <v>1</v>
-      </c>
-      <c r="O10" s="18">
-        <f>Overview!O10</f>
-        <v>2.25</v>
-      </c>
-      <c r="P10" s="14">
-        <f>Overview!P10</f>
-        <v>172.3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="16">
-        <f>Overview!B9</f>
-        <v>5</v>
-      </c>
-      <c r="C11" s="16">
-        <f>Overview!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="16">
-        <f>Overview!D9</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="16">
-        <f>Overview!E9</f>
-        <v>5</v>
-      </c>
-      <c r="F11" s="16">
-        <f>Overview!F9</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="16">
-        <f>Overview!G9</f>
-        <v>0</v>
-      </c>
-      <c r="H11" s="16">
-        <f>Overview!H9</f>
-        <v>5</v>
-      </c>
-      <c r="I11" s="16">
-        <f>Overview!I9</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="16">
-        <f>Overview!J9</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="16">
-        <f>Overview!K9</f>
-        <v>5</v>
-      </c>
-      <c r="L11" s="16">
-        <f>Overview!L9</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="16">
-        <f>Overview!M9</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="16">
-        <f>Overview!N9</f>
-        <v>1</v>
-      </c>
-      <c r="O11" s="16">
-        <f>Overview!O9</f>
-        <v>20</v>
-      </c>
-      <c r="P11" s="13">
-        <f>Overview!P9</f>
-        <v>301.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="18">
-        <f>Overview!B4</f>
-        <v>0</v>
-      </c>
-      <c r="C12" s="18">
-        <f>Overview!C4</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="18">
-        <f>Overview!D4</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="18">
-        <f>Overview!E4</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="18">
-        <f>Overview!F4</f>
-        <v>8</v>
-      </c>
-      <c r="G12" s="18">
-        <f>Overview!G4</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="18">
-        <f>Overview!H4</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="18">
-        <f>Overview!I4</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="18">
-        <f>Overview!J4</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="18">
-        <f>Overview!K4</f>
-        <v>0</v>
-      </c>
-      <c r="L12" s="18">
-        <f>Overview!L4</f>
-        <v>4</v>
-      </c>
-      <c r="M12" s="18">
-        <f>Overview!M4</f>
-        <v>0</v>
-      </c>
-      <c r="N12" s="18">
-        <f>Overview!N4</f>
-        <v>1</v>
-      </c>
-      <c r="O12" s="18">
-        <f>Overview!O4</f>
-        <v>12</v>
-      </c>
-      <c r="P12" s="14">
-        <f>Overview!P4</f>
-        <v>506.2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="16">
-        <f>Overview!B13</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="16">
-        <f>Overview!C13</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="16">
-        <f>Overview!D13</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="16">
-        <f>Overview!E13</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="16">
-        <f>Overview!F13</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="16">
-        <f>Overview!G13</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="H13" s="16">
-        <f>Overview!H13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="16">
-        <f>Overview!I13</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="16">
-        <f>Overview!J13</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="16">
-        <f>Overview!K13</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="16">
-        <f>Overview!L13</f>
-        <v>0</v>
-      </c>
-      <c r="M13" s="16">
-        <f>Overview!M13</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="N13" s="16">
-        <f>Overview!N13</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="16">
-        <f>Overview!O13</f>
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="P13" s="14">
-        <f>Overview!P13</f>
-        <v>184.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="16">
-        <f>Overview!B15</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="16">
-        <f>Overview!C15</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="16">
-        <f>Overview!D15</f>
-        <v>3.25</v>
-      </c>
-      <c r="E14" s="16">
-        <f>Overview!E15</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="16">
-        <f>Overview!F15</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="16">
-        <f>Overview!G15</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="16">
-        <f>Overview!H15</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="16">
-        <f>Overview!I15</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="16">
-        <f>Overview!J15</f>
-        <v>3.25</v>
-      </c>
-      <c r="K14" s="16">
-        <f>Overview!K15</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="16">
-        <f>Overview!L15</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="16">
-        <f>Overview!M15</f>
-        <v>0</v>
-      </c>
-      <c r="N14" s="16">
-        <f>Overview!N15</f>
-        <v>0</v>
-      </c>
-      <c r="O14" s="16">
-        <f>Overview!O15</f>
-        <v>0</v>
-      </c>
-      <c r="P14" s="14">
-        <f>Overview!P15</f>
-        <v>176.2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="18">
-        <f>Overview!B16</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="18">
-        <f>Overview!C16</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="18">
-        <f>Overview!D16</f>
-        <v>3.5</v>
-      </c>
-      <c r="E15" s="18">
-        <f>Overview!E16</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="18">
-        <f>Overview!F16</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="18">
-        <f>Overview!G16</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="18">
-        <f>Overview!H16</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="18">
-        <f>Overview!I16</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="18">
-        <f>Overview!J16</f>
-        <v>3.5</v>
-      </c>
-      <c r="K15" s="18">
-        <f>Overview!K16</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="18">
-        <f>Overview!L16</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="18">
-        <f>Overview!M16</f>
-        <v>0</v>
-      </c>
-      <c r="N15" s="18">
-        <f>Overview!N16</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="18">
-        <f>Overview!O16</f>
-        <v>0</v>
-      </c>
-      <c r="P15" s="14">
-        <f>Overview!P16</f>
-        <v>201.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="18">
-        <f>Overview!B6</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="18">
-        <f>Overview!C6</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="18">
-        <f>Overview!D6</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="18">
-        <f>Overview!E6</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="18">
-        <f>Overview!F6</f>
-        <v>4</v>
-      </c>
-      <c r="G16" s="18">
-        <f>Overview!G6</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="18">
-        <f>Overview!H6</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="18">
-        <f>Overview!I6</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="18">
-        <f>Overview!J6</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="18">
-        <f>Overview!K6</f>
-        <v>0</v>
-      </c>
-      <c r="L16" s="18">
-        <f>Overview!L6</f>
-        <v>4</v>
-      </c>
-      <c r="M16" s="18">
-        <f>Overview!M6</f>
-        <v>0</v>
-      </c>
-      <c r="N16" s="18">
-        <f>Overview!N6</f>
-        <v>1</v>
-      </c>
-      <c r="O16" s="18">
-        <f>Overview!O6</f>
-        <v>8</v>
-      </c>
-      <c r="P16" s="14">
-        <f>Overview!P6</f>
-        <v>263.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="18">
-        <f>Overview!B14</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="18">
-        <f>Overview!C14</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="18">
-        <f>Overview!D14</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="18">
-        <f>Overview!E14</f>
-        <v>3.15</v>
-      </c>
-      <c r="F17" s="18">
-        <f>Overview!F14</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="18">
-        <f>Overview!G14</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="18">
-        <f>Overview!H14</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="18">
-        <f>Overview!I14</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="18">
-        <f>Overview!J14</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="18">
-        <f>Overview!K14</f>
-        <v>3.15</v>
-      </c>
-      <c r="L17" s="18">
-        <f>Overview!L14</f>
-        <v>0</v>
-      </c>
-      <c r="M17" s="18">
-        <f>Overview!M14</f>
-        <v>0</v>
-      </c>
-      <c r="N17" s="18">
-        <f>Overview!N14</f>
-        <v>0</v>
-      </c>
-      <c r="O17" s="18">
-        <f>Overview!O14</f>
-        <v>0</v>
-      </c>
-      <c r="P17" s="14">
-        <f>Overview!P14</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="16">
-        <f>Overview!B11</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="16">
-        <f>Overview!C11</f>
-        <v>5.5</v>
-      </c>
-      <c r="D18" s="16">
-        <f>Overview!D11</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="16">
-        <f>Overview!E11</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="16">
-        <f>Overview!F11</f>
-        <v>5.5</v>
-      </c>
-      <c r="G18" s="16">
-        <f>Overview!G11</f>
-        <v>0</v>
-      </c>
-      <c r="H18" s="16">
-        <f>Overview!H11</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="16">
-        <f>Overview!I11</f>
-        <v>5.5</v>
-      </c>
-      <c r="J18" s="16">
-        <f>Overview!J11</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="16">
-        <f>Overview!K11</f>
-        <v>0</v>
-      </c>
-      <c r="L18" s="16">
-        <f>Overview!L11</f>
-        <v>5.5</v>
-      </c>
-      <c r="M18" s="16">
-        <f>Overview!M11</f>
-        <v>0</v>
-      </c>
-      <c r="N18" s="16">
-        <f>Overview!N11</f>
-        <v>1</v>
-      </c>
-      <c r="O18" s="16">
-        <f>Overview!O11</f>
-        <v>22</v>
-      </c>
-      <c r="P18" s="14">
-        <f>Overview!P11</f>
-        <v>595</v>
+      <c r="O10" s="19">
+        <f>Overview!O19</f>
+        <v>1.84</v>
+      </c>
+      <c r="P10" s="20">
+        <f>Overview!P19</f>
+        <v>14.81</v>
       </c>
     </row>
   </sheetData>

--- a/Aktie_Utdelning.xlsx
+++ b/Aktie_Utdelning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="23029"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC3F2A8-FA06-4142-88E2-FA384C51E867}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09853B7-325C-470E-86D0-A67C8790B4F9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Python2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -239,7 +240,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="35">
   <si>
     <t>Feb</t>
   </si>
@@ -343,12 +344,6 @@
     <t>ASTRAZENECA PLC (XSTO:AZN)</t>
   </si>
   <si>
-    <t>Magic Number</t>
-  </si>
-  <si>
-    <t>Bank</t>
-  </si>
-  <si>
     <t>Klovern AB (XSTO:KLOV B)</t>
   </si>
 </sst>
@@ -357,7 +352,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_-* #,##0.00\ [$kr-41D]_-;\-* #,##0.00\ [$kr-41D]_-;_-* &quot;-&quot;??\ [$kr-41D]_-;_-@_-"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
@@ -580,7 +575,7 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="1" fillId="4" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -629,7 +624,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" xfId="6" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -640,7 +635,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="168" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="1" fillId="3" borderId="4" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="5" xfId="7" applyBorder="1"/>
   </cellXfs>
@@ -950,6 +945,13 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="thin">
           <color auto="1"/>
         </left>
@@ -959,13 +961,6 @@
         <top style="thin">
           <color auto="1"/>
         </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
@@ -1691,37 +1686,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>1.5</c:v>
+                  <c:v>42</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.6999999999999993</c:v>
+                  <c:v>164.89999999999998</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12</c:v>
+                  <c:v>36</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>24</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.2000000000000002</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>8</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -1730,19 +1725,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.25</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2</c:v>
+                  <c:v>68</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>26.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.84</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2548,37 +2543,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
@@ -2587,19 +2582,19 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1</c:v>
+                  <c:v>34</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4200,8 +4195,8 @@
     <v>1</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_a7bbcf0fee31ae26f887a64a8aa6bd95&amp;qlt=95</v>
     <v>2</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=ericsson</v>
@@ -4271,8 +4266,8 @@
     <v>7</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_49aa44dce555e968f8570942e0a037aa&amp;qlt=95</v>
     <v>8</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=h%26m</v>
@@ -4342,8 +4337,8 @@
     <v>13</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_fc6f4e6d6b085c143f2892c35e7a85ba&amp;qlt=95</v>
     <v>14</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=investor+ab</v>
@@ -4361,10 +4356,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>7</v>
+    <v>8</v>
     <v>Investor AB (XSTO:INVE B)</v>
     <v>3</v>
-    <v>8</v>
+    <v>9</v>
     <v>Finance</v>
     <v>5</v>
     <v>0.98440000000000005</v>
@@ -4413,10 +4408,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>9</v>
+    <v>10</v>
     <v>AUTOLIV, INC. (XSTO:ALIV SDB)</v>
-    <v>10</v>
     <v>11</v>
+    <v>12</v>
     <v>Finance</v>
     <v>5</v>
     <v>837.8</v>
@@ -4469,8 +4464,8 @@
     <v>23</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_91527f154a43f44fef65f55713150b01&amp;qlt=95</v>
     <v>24</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=investment+ab+kinnevik</v>
@@ -4540,8 +4535,8 @@
     <v>29</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_f691da07efc984db49409ee18e3268d9&amp;qlt=95</v>
     <v>30</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=atlas+copco</v>
@@ -4613,12 +4608,12 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>12</v>
+    <v>13</v>
     <v>OMEGA HEALTHCARE INVESTORS, INC. (XNYS:OHI)</v>
-    <v>10</v>
-    <v>13</v>
+    <v>11</v>
+    <v>14</v>
     <v>Finance</v>
-    <v>14</v>
+    <v>15</v>
     <v>45.22</v>
     <v>13.33</v>
     <v>0.83640000000000003</v>
@@ -4663,8 +4658,8 @@
     <v>38</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_22edc37b3d4ca713a66f23973844e621&amp;qlt=95</v>
     <v>39</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=at%26t</v>
@@ -4682,12 +4677,12 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>15</v>
+    <v>16</v>
     <v>AT&amp;T INC. (XNYS:T)</v>
     <v>3</v>
-    <v>16</v>
+    <v>17</v>
     <v>Finance</v>
-    <v>14</v>
+    <v>15</v>
     <v>39.700000000000003</v>
     <v>26.08</v>
     <v>0.67849999999999999</v>
@@ -4735,10 +4730,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>17</v>
+    <v>18</v>
     <v>EQT AB (XSTO:EQT)</v>
-    <v>10</v>
-    <v>18</v>
+    <v>11</v>
+    <v>19</v>
     <v>Finance</v>
     <v>5</v>
     <v>4.0999999999999996</v>
@@ -4783,8 +4778,8 @@
     <v>47</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_9ac417b9b0065d55837f5565b53ff1d3&amp;qlt=95</v>
     <v>48</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=ncc+ab</v>
@@ -4856,12 +4851,12 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>19</v>
+    <v>20</v>
     <v>Vastsvensk Logistik AB (publ) (XSTO:VASLOG)</v>
-    <v>10</v>
-    <v>20</v>
+    <v>11</v>
+    <v>21</v>
     <v>Finance</v>
-    <v>21</v>
+    <v>22</v>
     <v>107</v>
     <v>58</v>
     <v>0.5</v>
@@ -4904,10 +4899,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
+    <v>23</v>
     <v>Castellum AB (XSTO:CAST)</v>
-    <v>10</v>
-    <v>23</v>
+    <v>11</v>
+    <v>24</v>
     <v>Finance</v>
     <v>5</v>
     <v>257</v>
@@ -4955,8 +4950,8 @@
     <v>59</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_0fc289fa19d264b8292a937ab061bb33&amp;qlt=95</v>
     <v>60</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=axfood</v>
@@ -5030,8 +5025,8 @@
     <v>66</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_813800af8ea77f18dfa72731ec0cc818&amp;qlt=95</v>
     <v>67</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=swedbank</v>
@@ -5103,10 +5098,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
+    <v>23</v>
     <v>Investment AB Latour (XSTO:LATO B)</v>
-    <v>10</v>
-    <v>23</v>
+    <v>11</v>
+    <v>24</v>
     <v>Finance</v>
     <v>5</v>
     <v>183.8</v>
@@ -5156,10 +5151,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
+    <v>23</v>
     <v>Ratos AB (XSTO:RATO B)</v>
-    <v>10</v>
-    <v>23</v>
+    <v>11</v>
+    <v>24</v>
     <v>Finance</v>
     <v>5</v>
     <v>37.72</v>
@@ -5207,8 +5202,8 @@
     <v>78</v>
   </rv>
   <rv s="2">
-    <v>Powered by Refinitiv</v>
     <v>6</v>
+    <v>7</v>
     <v>https://www.bing.com/th?id=AMMS_b2cce4675a6d7507fb76f31542e0dd93&amp;qlt=95</v>
     <v>79</v>
     <v>https://www.bing.com/images/search?form=xlimg&amp;q=astrazeneca</v>
@@ -5226,10 +5221,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>24</v>
+    <v>25</v>
     <v>ASTRAZENECA PLC (XSTO:AZN)</v>
     <v>3</v>
-    <v>25</v>
+    <v>26</v>
     <v>Finance</v>
     <v>5</v>
     <v>1083.2</v>
@@ -5281,10 +5276,10 @@
     <v>268435457</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>22</v>
+    <v>23</v>
     <v>Klovern AB (XSTO:KLOV B)</v>
-    <v>10</v>
-    <v>23</v>
+    <v>11</v>
+    <v>24</v>
     <v>Finance</v>
     <v>5</v>
     <v>27.58</v>
@@ -5337,8 +5332,8 @@
     <k n="Source" t="r"/>
   </s>
   <s t="_imageurl">
-    <k n="%ProviderInfo" t="s"/>
     <k n="_Flags" t="spb"/>
+    <k n="_Provider" t="spb"/>
     <k n="Address" t="s"/>
     <k n="Attribution" t="r"/>
     <k n="More Images Address" t="s"/>
@@ -6171,7 +6166,7 @@
       <v t="s">_Display</v>
     </a>
   </spbArrays>
-  <spbData count="26">
+  <spbData count="27">
     <spb s="0">
       <v>0</v>
     </spb>
@@ -6229,10 +6224,13 @@
     <spb s="6">
       <v>2</v>
     </spb>
+    <spb s="7">
+      <v>Powered by Refinitiv</v>
+    </spb>
     <spb s="0">
       <v>1</v>
     </spb>
-    <spb s="7">
+    <spb s="8">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -6259,12 +6257,12 @@
     <spb s="0">
       <v>2</v>
     </spb>
-    <spb s="8">
+    <spb s="9">
       <v>2</v>
       <v>2</v>
       <v>2</v>
     </spb>
-    <spb s="9">
+    <spb s="10">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -6293,7 +6291,7 @@
     <spb s="0">
       <v>3</v>
     </spb>
-    <spb s="10">
+    <spb s="11">
       <v>13</v>
       <v>2</v>
       <v>2</v>
@@ -6317,7 +6315,7 @@
       <v>10</v>
       <v>5</v>
     </spb>
-    <spb s="11">
+    <spb s="12">
       <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -6327,7 +6325,7 @@
     <spb s="0">
       <v>4</v>
     </spb>
-    <spb s="12">
+    <spb s="13">
       <v>13</v>
       <v>2</v>
       <v>2</v>
@@ -6355,7 +6353,7 @@
     <spb s="0">
       <v>5</v>
     </spb>
-    <spb s="13">
+    <spb s="14">
       <v>1</v>
       <v>2</v>
       <v>1</v>
@@ -6380,7 +6378,7 @@
     <spb s="0">
       <v>6</v>
     </spb>
-    <spb s="14">
+    <spb s="15">
       <v>1</v>
       <v>1</v>
       <v>3</v>
@@ -6400,7 +6398,7 @@
       <v>5</v>
       <v>1</v>
     </spb>
-    <spb s="15">
+    <spb s="16">
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -6411,7 +6409,7 @@
     <spb s="0">
       <v>7</v>
     </spb>
-    <spb s="16">
+    <spb s="17">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -6439,7 +6437,7 @@
     <spb s="0">
       <v>8</v>
     </spb>
-    <spb s="17">
+    <spb s="18">
       <v>1</v>
       <v>2</v>
       <v>2</v>
@@ -6471,7 +6469,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="18">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="19">
   <s>
     <k n="^Order" t="spba"/>
   </s>
@@ -6528,6 +6526,9 @@
   </s>
   <s>
     <k n="%ProviderInfo" t="spb"/>
+  </s>
+  <s>
+    <k n="name" t="s"/>
   </s>
   <s>
     <k n="Low" t="i"/>
@@ -6770,13 +6771,13 @@
       <x:numFmt numFmtId="2" formatCode="0.00"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="165" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
+      <x:numFmt numFmtId="166" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="1" formatCode="0"/>
     </x:dxf>
     <x:dxf>
-      <x:numFmt numFmtId="166" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
+      <x:numFmt numFmtId="165" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="164" formatCode="_([$€-2]\ * #,##0_);_([$€-2]\ * \(#,##0\);_([$€-2]\ * &quot;-&quot;_);_(@_)"/>
@@ -6813,7 +6814,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE52A48A-72C8-4108-976A-A1B959AD3695}" name="Tabell1" displayName="Tabell1" ref="A1:P20" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16" headerRowCellStyle="Neutral" dataCellStyle="60 % - Dekorfärg3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BE52A48A-72C8-4108-976A-A1B959AD3695}" name="Tabell1" displayName="Tabell1" ref="A1:P20" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="17" tableBorderDxfId="18" totalsRowBorderDxfId="16" headerRowCellStyle="Neutral" dataCellStyle="60 % - Dekorfärg3">
   <autoFilter ref="A1:P20" xr:uid="{1F38F5D2-2C32-4A11-8AF6-D2E7C4910877}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{E53D5D7B-8DFB-4A62-9DCA-8BE3FEB62C87}" name="Aktie" dataDxfId="15" dataCellStyle="60 % - Dekorfärg3"/>
@@ -7252,11 +7253,11 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O2" s="2">
         <f t="shared" ref="O2:O9" si="0">SUM(B2:M2)*N2</f>
-        <v>1.5</v>
+        <v>42</v>
       </c>
       <c r="P2" s="9" cm="1">
         <f t="array" ref="P2">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7284,11 +7285,11 @@
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O3" s="1">
         <f t="shared" si="0"/>
-        <v>9.6999999999999993</v>
+        <v>164.89999999999998</v>
       </c>
       <c r="P3" s="39" cm="1">
         <f t="array" ref="P3">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7316,11 +7317,11 @@
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4" s="2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="P4" s="9" cm="1">
         <f t="array" ref="P4">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7352,11 +7353,11 @@
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="17">
         <f>SUM(B5:M5)*N5</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P5" s="41" cm="1">
         <f t="array" ref="P5">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7384,11 +7385,11 @@
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O6" s="2">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="P6" s="9" cm="1">
         <f t="array" ref="P6">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7554,11 +7555,11 @@
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="2">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P8" s="8" cm="1">
         <f t="array" ref="P8">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)*10</f>
@@ -7590,11 +7591,11 @@
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P9" s="40" cm="1">
         <f t="array" ref="P9">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)*10</f>
@@ -7622,11 +7623,11 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="N10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="2">
         <f>SUM(B10:M10)*N10</f>
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="P10" s="9" cm="1">
         <f t="array" ref="P10">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7756,11 +7757,11 @@
       </c>
       <c r="M11" s="19"/>
       <c r="N11" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O11" s="19">
         <f t="shared" ref="O11:O18" si="1">SUM(B11:M11)*N11</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P11" s="20" cm="1">
         <f t="array" ref="P11">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -7792,11 +7793,11 @@
       </c>
       <c r="M12" s="23"/>
       <c r="N12" s="23">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O12" s="23">
         <f>SUM(B12:M12)*N12</f>
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="P12" s="24" cm="1">
         <f t="array" ref="P12">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -8090,11 +8091,11 @@
       <c r="L15" s="19"/>
       <c r="M15" s="19"/>
       <c r="N15" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15" s="19">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P15" s="20" cm="1">
         <f t="array" ref="P15">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -8222,11 +8223,11 @@
       <c r="L16" s="27"/>
       <c r="M16" s="27"/>
       <c r="N16" s="27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="27">
         <f>SUM(B16:M16)*N16</f>
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P16" s="28" cm="1">
         <f t="array" ref="P16">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -8354,11 +8355,11 @@
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
       <c r="N17" s="19">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="O17" s="19">
         <f>SUM(B17:M17)*N17</f>
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="P17" s="20" cm="1">
         <f t="array" ref="P17">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -8488,11 +8489,11 @@
       <c r="L18" s="23"/>
       <c r="M18" s="23"/>
       <c r="N18" s="23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="23">
         <f t="shared" si="1"/>
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="P18" s="24" cm="1">
         <f t="array" ref="P18">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -8626,11 +8627,11 @@
         <v>0.46</v>
       </c>
       <c r="N19" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19" s="19">
         <f>SUM(B19:M19)*N19</f>
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="P19" s="30" cm="1">
         <f t="array" ref="P19">_FV(Tabell1[[#This Row],[Aktie]],"Previous close",TRUE)</f>
@@ -8763,59 +8764,59 @@
       </c>
       <c r="B21" s="15">
         <f>B2*N2+B3*N3+B4*N4+B17*N17+B6*N6+B12*N12+B8*N8+B9*N9+B16*N16+B5*N5+B11*N11+B10*N10+B7*N7+B13*N13+B14*N14+B15*N15+B18*N18+B19*N19</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C21" s="3">
         <f>C2*N2+C3*N3+C4*N4+C17*N17+C6*N6+C12*N12+C8*N8+C9*N9+C16*N16+C5*N5+C11*N11+C10*N10+C7*N7+C13*N13+C14*N14+C15*N15+C18*N18+C19*N19</f>
-        <v>13.25</v>
+        <v>19.25</v>
       </c>
       <c r="D21" s="3">
         <f>D2*N2+D3*N3+D4*N4+D17*N17+D6*N6+D12*N12+D8*N8+D9*N9+D16*N16+D5*N5+D11*N11+D10*N10+D7*N7+D13*N13+D14*N14+D15*N15+D18*N18+D19*N19</f>
-        <v>18.46</v>
+        <v>0</v>
       </c>
       <c r="E21" s="3">
         <f>E2*N2+E3*N3+E4*N4+E17*N17+E6*N6+E12*N12+E8*N8+E9*N9+E16*N16+E5*N5+E11*N11+E10*N10+E7*N7+E13*N13+E14*N14+E15*N15+E18*N18+E19*N19</f>
-        <v>23.75</v>
+        <v>21</v>
       </c>
       <c r="F21" s="3">
         <f>F2*N2+F3*N3+F4*N4+F17*N17+F6*N6+F12*N12+F8*N8+F9*N9+F16*N16+F5*N5+F11*N11+F10*N10+F7*N7+F13*N13+F14*N14+F15*N15+F18*N18+F19*N19</f>
-        <v>34.35</v>
+        <v>229.7</v>
       </c>
       <c r="G21" s="3">
         <f>G2*N2+G3*N3+G4*N4+G17*N17+G6*N6+G12*N12+G8*N8+G9*N9+G16*N16+G5*N5+G11*N11+G10*N10+G7*N7+G13*N13+G14*N14+G15*N15+G18*N18+G19*N19</f>
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <f>H2*N2+H3*N3+H4*N4+H17*N17+H6*N6+H12*N12+H8*N8+H9*N9+H16*N16+H5*N5+H11*N11+H10*N10+H7*N7+H13*N13+H14*N14+H15*N15+H18*N18+H19*N19</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I21" s="3">
         <f>I2*N2+I3*N3+I4*N4+I17*N17+I6*N6+I12*N12+I8*N8+I9*N9+I16*N16+I5*N5+I11*N11+I10*N10+I7*N7+I13*N13+I14*N14+I15*N15+I18*N18+I19*N19</f>
-        <v>13.25</v>
+        <v>19.25</v>
       </c>
       <c r="J21" s="3">
         <f>J2*N2+J3*N3+J4*N4+J17*N17+J6*N6+J12*N12+J8*N8+J9*N9+J16*N16+J5*N5+J11*N11+J10*N10+J7*N7+J13*N13+J14*N14+J15*N15+J18*N18+J19*N19</f>
-        <v>8.9600000000000009</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <f>K2*N2+K3*N3+K4*N4+K17*N17+K6*N6+K12*N12+K8*N8+K9*N9+K16*N16+K5*N5+K11*N11+K10*N10+K7*N7+K13*N13+K14*N14+K15*N15+K18*N18+K19*N19</f>
-        <v>5.75</v>
+        <v>21</v>
       </c>
       <c r="L21" s="3">
         <f>L2*N2+L3*N3+L4*N4+L17*N17+L6*N6+L12*N12+L8*N8+L9*N9+L16*N16+L5*N5+L11*N11+L10*N10+L7*N7+L13*N13+L14*N14+L15*N15+L18*N18+L19*N19</f>
-        <v>30.1</v>
+        <v>149.69999999999999</v>
       </c>
       <c r="M21" s="3">
         <f>M2*N2+M3*N3+M4*N4+M17*N17+M6*N6+M12*N12+M8*N8+M9*N9+M16*N16+M5*N5+M11*N11+M10*N10+M7*N7+M13*N13+M14*N14+M15*N15+M18*N18+M19*N19</f>
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="N21" s="3">
         <f>SUM(N2:N20)</f>
-        <v>15</v>
+        <v>102</v>
       </c>
       <c r="O21" s="3">
         <f>SUM(O2:O19)</f>
-        <v>160.99</v>
+        <v>459.9</v>
       </c>
     </row>
   </sheetData>
@@ -8832,7 +8833,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A10BA0FA-7F5A-4054-944A-818344D765CC}">
   <sheetPr codeName="Blad2"/>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
@@ -8840,7 +8841,7 @@
     <col min="19" max="19" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
@@ -8889,14 +8890,8 @@
       <c r="P1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>19</v>
       </c>
@@ -8950,24 +8945,18 @@
       </c>
       <c r="N2" s="11">
         <f>Overview!N2</f>
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="O2" s="11">
         <f>Overview!O2</f>
-        <v>1.5</v>
+        <v>42</v>
       </c>
       <c r="P2" s="39">
         <f>Overview!P2</f>
         <v>86.46</v>
       </c>
-      <c r="S2">
-        <v>2</v>
-      </c>
-      <c r="T2">
-        <v>2000</v>
-      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
         <v>18</v>
       </c>
@@ -9021,18 +9010,18 @@
       </c>
       <c r="N3" s="2">
         <f>Overview!N3</f>
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="O3" s="2">
         <f>Overview!O3</f>
-        <v>9.6999999999999993</v>
+        <v>164.89999999999998</v>
       </c>
       <c r="P3" s="9">
         <f>Overview!P3</f>
         <v>137.65</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
         <v>23</v>
       </c>
@@ -9086,18 +9075,18 @@
       </c>
       <c r="N4" s="1">
         <f>Overview!N4</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O4" s="1">
         <f>Overview!O4</f>
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="P4" s="39">
         <f>Overview!P4</f>
         <v>506.2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>24</v>
       </c>
@@ -9151,18 +9140,18 @@
       </c>
       <c r="N5" s="13">
         <f>Overview!N5</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O5" s="13">
         <f>Overview!O5</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="P5" s="8">
         <f>Overview!P5</f>
         <v>595</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
         <v>25</v>
       </c>
@@ -9216,18 +9205,18 @@
       </c>
       <c r="N6" s="1">
         <f>Overview!N6</f>
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O6" s="1">
         <f>Overview!O6</f>
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="P6" s="39">
         <f>Overview!P6</f>
         <v>263.3</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="38" t="s">
         <v>29</v>
       </c>
@@ -9292,7 +9281,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>17</v>
       </c>
@@ -9346,18 +9335,18 @@
       </c>
       <c r="N8" s="11">
         <f>Overview!N8</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" s="11">
         <f>Overview!O8</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="P8" s="39">
         <f>Overview!P8</f>
         <v>305.7</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="38" t="s">
         <v>22</v>
       </c>
@@ -9411,18 +9400,18 @@
       </c>
       <c r="N9" s="2">
         <f>Overview!N9</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="2">
         <f>Overview!O9</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P9" s="9">
         <f>Overview!P9</f>
         <v>301.3</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
         <v>28</v>
       </c>
@@ -9476,11 +9465,11 @@
       </c>
       <c r="N10" s="1">
         <f>Overview!N10</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="1">
         <f>Overview!O10</f>
-        <v>2.2000000000000002</v>
+        <v>0</v>
       </c>
       <c r="P10" s="39">
         <f>Overview!P10</f>
@@ -9494,7 +9483,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1485E3A-19D0-47B9-867F-49E3EDE141F8}">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48.28515625" bestFit="1" customWidth="1"/>
@@ -9502,7 +9491,7 @@
     <col min="19" max="19" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
         <v>14</v>
       </c>
@@ -9551,14 +9540,8 @@
       <c r="P1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="T1" s="10" t="s">
-        <v>35</v>
-      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
         <v>27</v>
       </c>
@@ -9612,24 +9595,18 @@
       </c>
       <c r="N2" s="19">
         <f>Overview!N11</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" s="19">
         <f>Overview!O11</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P2" s="20">
         <f>Overview!P11</f>
         <v>161</v>
       </c>
-      <c r="S2">
-        <v>1</v>
-      </c>
-      <c r="T2">
-        <v>2000</v>
-      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
         <v>26</v>
       </c>
@@ -9683,18 +9660,18 @@
       </c>
       <c r="N3" s="23">
         <f>Overview!N12</f>
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O3" s="23">
         <f>Overview!O12</f>
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="P3" s="24">
         <f>Overview!P12</f>
         <v>80</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
         <v>30</v>
       </c>
@@ -9759,7 +9736,7 @@
         <v>176.2</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
         <v>31</v>
       </c>
@@ -9824,7 +9801,7 @@
         <v>201.8</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
         <v>32</v>
       </c>
@@ -9878,18 +9855,18 @@
       </c>
       <c r="N6" s="19">
         <f>Overview!N15</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" s="19">
         <f>Overview!O15</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P6" s="20">
         <f>Overview!P15</f>
         <v>133.38</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="36" t="s">
         <v>21</v>
       </c>
@@ -9943,18 +9920,18 @@
       </c>
       <c r="N7" s="23">
         <f>Overview!N16</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" s="23">
         <f>Overview!O16</f>
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P7" s="24">
         <f>Overview!P16</f>
         <v>172.3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
         <v>20</v>
       </c>
@@ -10008,18 +9985,18 @@
       </c>
       <c r="N8" s="19">
         <f>Overview!N17</f>
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="O8" s="19">
         <f>Overview!O17</f>
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="P8" s="20">
         <f>Overview!P17</f>
         <v>26.46</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>33</v>
       </c>
@@ -10073,20 +10050,20 @@
       </c>
       <c r="N9" s="23">
         <f>Overview!N18</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="23">
         <f>Overview!O18</f>
-        <v>26.5</v>
+        <v>0</v>
       </c>
       <c r="P9" s="24">
         <f>Overview!P18</f>
         <v>991.4</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" s="19">
         <f>Overview!B19</f>
@@ -10138,11 +10115,11 @@
       </c>
       <c r="N10" s="19">
         <f>Overview!N19</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10" s="19">
         <f>Overview!O19</f>
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="P10" s="20">
         <f>Overview!P19</f>
